--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6176" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16898" uniqueCount="674">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16898" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20391" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -2036,6 +2036,321 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wensday_80464\fracture\Fracture_20251119_175941_8_2.csv</t>
+  </si>
+  <si>
+    <t>wednesday_10440</t>
+  </si>
+  <si>
+    <t>wednesday_10441</t>
+  </si>
+  <si>
+    <t>wednesday_10446</t>
+  </si>
+  <si>
+    <t>wednesday_10453</t>
+  </si>
+  <si>
+    <t>wednesday_80464</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\tension\TENSION_20250409_135843_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\tension\TENSION_20250409_135843_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\fracture\Fracture_20250410_154733_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\tension\TENSION_20250409_81808_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\tension\TENSION_20250409_81808_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250410_124314_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\tension\TENSION_20250409_135843_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\tension\TENSION_20250409_135843_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\tension\TENSION_20250409_81808_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\tension\TENSION_20250409_81808_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250407_85345_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\compression\COMPRESSION_20251119_182203_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\compression\COMPRESSION_20251119_182203_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\tension\TENSION_20251119_183903_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\tension\TENSION_20251119_183903_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_8_2.csv</t>
   </si>
 </sst>
 </file>
@@ -2087,12 +2402,12 @@
     <col min="1" max="1" width="14.08984375" customWidth="true"/>
     <col min="2" max="2" width="6.54296875" customWidth="true"/>
     <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="14.26953125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
     <col min="5" max="5" width="11.81640625" customWidth="true"/>
     <col min="6" max="6" width="11.90625" customWidth="true"/>
     <col min="7" max="7" width="7.90625" customWidth="true"/>
     <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="165.453125" customWidth="true"/>
+    <col min="9" max="9" width="167.54296875" customWidth="true"/>
     <col min="10" max="10" width="10.453125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -4827,7 +5142,7 @@
         <v>501</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E86" s="0" t="s">
         <v>25</v>
@@ -4842,7 +5157,7 @@
         <v>507</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>566</v>
+        <v>679</v>
       </c>
       <c r="J86" s="0">
         <v>10897.75</v>
@@ -4859,7 +5174,7 @@
         <v>501</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E87" s="0" t="s">
         <v>25</v>
@@ -4874,7 +5189,7 @@
         <v>508</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>567</v>
+        <v>680</v>
       </c>
       <c r="J87" s="0">
         <v>5963.8306000000002</v>
@@ -4891,7 +5206,7 @@
         <v>501</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E88" s="0" t="s">
         <v>26</v>
@@ -4906,7 +5221,7 @@
         <v>509</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>568</v>
+        <v>681</v>
       </c>
       <c r="J88" s="0">
         <v>1364.115</v>
@@ -4923,7 +5238,7 @@
         <v>501</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>26</v>
@@ -4938,7 +5253,7 @@
         <v>510</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>569</v>
+        <v>682</v>
       </c>
       <c r="J89" s="0">
         <v>1002.6719000000001</v>
@@ -4955,7 +5270,7 @@
         <v>501</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E90" s="0" t="s">
         <v>27</v>
@@ -4970,7 +5285,7 @@
         <v>511</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>570</v>
+        <v>683</v>
       </c>
       <c r="J90" s="0">
         <v>557.97879999999998</v>
@@ -4987,7 +5302,7 @@
         <v>501</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E91" s="0" t="s">
         <v>27</v>
@@ -5002,7 +5317,7 @@
         <v>512</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>571</v>
+        <v>684</v>
       </c>
       <c r="J91" s="0">
         <v>511.4341</v>
@@ -5019,7 +5334,7 @@
         <v>501</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>27</v>
@@ -5034,7 +5349,7 @@
         <v>513</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>572</v>
+        <v>685</v>
       </c>
       <c r="J92" s="0">
         <v>485.53699999999998</v>
@@ -5051,7 +5366,7 @@
         <v>501</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>27</v>
@@ -5066,7 +5381,7 @@
         <v>514</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>573</v>
+        <v>686</v>
       </c>
       <c r="J93" s="0">
         <v>456.29579999999999</v>
@@ -5083,7 +5398,7 @@
         <v>501</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E94" s="0" t="s">
         <v>27</v>
@@ -5098,7 +5413,7 @@
         <v>515</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>574</v>
+        <v>687</v>
       </c>
       <c r="J94" s="0">
         <v>403.62130000000002</v>
@@ -5115,7 +5430,7 @@
         <v>501</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E95" s="0" t="s">
         <v>27</v>
@@ -5130,7 +5445,7 @@
         <v>516</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>575</v>
+        <v>688</v>
       </c>
       <c r="J95" s="0">
         <v>384.92849999999999</v>
@@ -5147,7 +5462,7 @@
         <v>501</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E96" s="0" t="s">
         <v>27</v>
@@ -5162,7 +5477,7 @@
         <v>517</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>576</v>
+        <v>689</v>
       </c>
       <c r="J96" s="0">
         <v>345.9332</v>
@@ -5179,7 +5494,7 @@
         <v>501</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E97" s="0" t="s">
         <v>27</v>
@@ -5194,7 +5509,7 @@
         <v>518</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>577</v>
+        <v>690</v>
       </c>
       <c r="J97" s="0">
         <v>329.33870000000002</v>
@@ -5211,7 +5526,7 @@
         <v>501</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E98" s="0" t="s">
         <v>25</v>
@@ -5226,7 +5541,7 @@
         <v>519</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>578</v>
+        <v>691</v>
       </c>
       <c r="J98" s="0">
         <v>9494.3554999999997</v>
@@ -5243,7 +5558,7 @@
         <v>501</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E99" s="0" t="s">
         <v>25</v>
@@ -5258,7 +5573,7 @@
         <v>520</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>579</v>
+        <v>692</v>
       </c>
       <c r="J99" s="0">
         <v>6959.3242</v>
@@ -5275,7 +5590,7 @@
         <v>501</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E100" s="0" t="s">
         <v>26</v>
@@ -5290,7 +5605,7 @@
         <v>521</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>580</v>
+        <v>693</v>
       </c>
       <c r="J100" s="0">
         <v>989.73109999999997</v>
@@ -5307,7 +5622,7 @@
         <v>501</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E101" s="0" t="s">
         <v>26</v>
@@ -5322,7 +5637,7 @@
         <v>522</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>581</v>
+        <v>694</v>
       </c>
       <c r="J101" s="0">
         <v>709.46839999999998</v>
@@ -5339,7 +5654,7 @@
         <v>501</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E102" s="0" t="s">
         <v>27</v>
@@ -5354,7 +5669,7 @@
         <v>523</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>582</v>
+        <v>695</v>
       </c>
       <c r="J102" s="0">
         <v>528.32619999999997</v>
@@ -5371,7 +5686,7 @@
         <v>501</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E103" s="0" t="s">
         <v>27</v>
@@ -5386,7 +5701,7 @@
         <v>524</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>583</v>
+        <v>696</v>
       </c>
       <c r="J103" s="0">
         <v>502.16129999999998</v>
@@ -5403,7 +5718,7 @@
         <v>501</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E104" s="0" t="s">
         <v>27</v>
@@ -5418,7 +5733,7 @@
         <v>525</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>584</v>
+        <v>697</v>
       </c>
       <c r="J104" s="0">
         <v>468.14839999999998</v>
@@ -5435,7 +5750,7 @@
         <v>501</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E105" s="0" t="s">
         <v>27</v>
@@ -5450,7 +5765,7 @@
         <v>526</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>585</v>
+        <v>698</v>
       </c>
       <c r="J105" s="0">
         <v>413.35890000000001</v>
@@ -5467,7 +5782,7 @@
         <v>501</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E106" s="0" t="s">
         <v>27</v>
@@ -5482,7 +5797,7 @@
         <v>527</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>586</v>
+        <v>699</v>
       </c>
       <c r="J106" s="0">
         <v>410.47199999999998</v>
@@ -5499,7 +5814,7 @@
         <v>501</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E107" s="0" t="s">
         <v>27</v>
@@ -5514,7 +5829,7 @@
         <v>528</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>587</v>
+        <v>700</v>
       </c>
       <c r="J107" s="0">
         <v>371.8809</v>
@@ -5531,7 +5846,7 @@
         <v>501</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E108" s="0" t="s">
         <v>27</v>
@@ -5546,7 +5861,7 @@
         <v>529</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>588</v>
+        <v>701</v>
       </c>
       <c r="J108" s="0">
         <v>347.0478</v>
@@ -5563,7 +5878,7 @@
         <v>501</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E109" s="0" t="s">
         <v>27</v>
@@ -5578,7 +5893,7 @@
         <v>530</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>589</v>
+        <v>702</v>
       </c>
       <c r="J109" s="0">
         <v>302.97559999999999</v>
@@ -5595,7 +5910,7 @@
         <v>501</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>25</v>
@@ -5610,7 +5925,7 @@
         <v>531</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>590</v>
+        <v>703</v>
       </c>
       <c r="J110" s="0">
         <v>8923.2001999999993</v>
@@ -5627,7 +5942,7 @@
         <v>501</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E111" s="0" t="s">
         <v>25</v>
@@ -5642,7 +5957,7 @@
         <v>532</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="J111" s="0">
         <v>7434.9364999999998</v>
@@ -5659,7 +5974,7 @@
         <v>501</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E112" s="0" t="s">
         <v>26</v>
@@ -5674,7 +5989,7 @@
         <v>533</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="J112" s="0">
         <v>1198.5989</v>
@@ -5691,7 +6006,7 @@
         <v>501</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E113" s="0" t="s">
         <v>26</v>
@@ -5706,7 +6021,7 @@
         <v>534</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>593</v>
+        <v>706</v>
       </c>
       <c r="J113" s="0">
         <v>1016.6576</v>
@@ -5723,7 +6038,7 @@
         <v>501</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E114" s="0" t="s">
         <v>27</v>
@@ -5738,7 +6053,7 @@
         <v>535</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>594</v>
+        <v>707</v>
       </c>
       <c r="J114" s="0">
         <v>783.98929999999996</v>
@@ -5755,7 +6070,7 @@
         <v>501</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E115" s="0" t="s">
         <v>27</v>
@@ -5770,7 +6085,7 @@
         <v>536</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>595</v>
+        <v>708</v>
       </c>
       <c r="J115" s="0">
         <v>765.39179999999999</v>
@@ -5787,7 +6102,7 @@
         <v>501</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E116" s="0" t="s">
         <v>27</v>
@@ -5802,7 +6117,7 @@
         <v>537</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>596</v>
+        <v>709</v>
       </c>
       <c r="J116" s="0">
         <v>763.20230000000004</v>
@@ -5819,7 +6134,7 @@
         <v>501</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E117" s="0" t="s">
         <v>27</v>
@@ -5834,7 +6149,7 @@
         <v>538</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>597</v>
+        <v>710</v>
       </c>
       <c r="J117" s="0">
         <v>706.49959999999999</v>
@@ -5851,7 +6166,7 @@
         <v>501</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E118" s="0" t="s">
         <v>27</v>
@@ -5866,7 +6181,7 @@
         <v>539</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>598</v>
+        <v>711</v>
       </c>
       <c r="J118" s="0">
         <v>532.22119999999995</v>
@@ -5883,7 +6198,7 @@
         <v>501</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E119" s="0" t="s">
         <v>27</v>
@@ -5898,7 +6213,7 @@
         <v>540</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>599</v>
+        <v>712</v>
       </c>
       <c r="J119" s="0">
         <v>499.38260000000002</v>
@@ -5915,7 +6230,7 @@
         <v>501</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E120" s="0" t="s">
         <v>27</v>
@@ -5930,7 +6245,7 @@
         <v>541</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>600</v>
+        <v>713</v>
       </c>
       <c r="J120" s="0">
         <v>487.96170000000001</v>
@@ -5947,7 +6262,7 @@
         <v>501</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E121" s="0" t="s">
         <v>27</v>
@@ -5962,7 +6277,7 @@
         <v>542</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>601</v>
+        <v>714</v>
       </c>
       <c r="J121" s="0">
         <v>471.42149999999998</v>
@@ -5979,7 +6294,7 @@
         <v>501</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E122" s="0" t="s">
         <v>25</v>
@@ -5994,7 +6309,7 @@
         <v>543</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="J122" s="0">
         <v>10363.415999999999</v>
@@ -6011,7 +6326,7 @@
         <v>501</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>25</v>
@@ -6026,7 +6341,7 @@
         <v>544</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>603</v>
+        <v>716</v>
       </c>
       <c r="J123" s="0">
         <v>8731.0702999999994</v>
@@ -6043,7 +6358,7 @@
         <v>501</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>26</v>
@@ -6058,7 +6373,7 @@
         <v>545</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>604</v>
+        <v>717</v>
       </c>
       <c r="J124" s="0">
         <v>848.39120000000003</v>
@@ -6075,7 +6390,7 @@
         <v>501</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>26</v>
@@ -6090,7 +6405,7 @@
         <v>546</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>605</v>
+        <v>718</v>
       </c>
       <c r="J125" s="0">
         <v>740.85990000000004</v>
@@ -6107,7 +6422,7 @@
         <v>501</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>27</v>
@@ -6122,7 +6437,7 @@
         <v>547</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>606</v>
+        <v>719</v>
       </c>
       <c r="J126" s="0">
         <v>509.65910000000002</v>
@@ -6139,7 +6454,7 @@
         <v>501</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>27</v>
@@ -6154,7 +6469,7 @@
         <v>548</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>607</v>
+        <v>720</v>
       </c>
       <c r="J127" s="0">
         <v>473.81920000000002</v>
@@ -6171,7 +6486,7 @@
         <v>501</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E128" s="0" t="s">
         <v>27</v>
@@ -6186,7 +6501,7 @@
         <v>549</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>608</v>
+        <v>721</v>
       </c>
       <c r="J128" s="0">
         <v>386.12639999999999</v>
@@ -6203,7 +6518,7 @@
         <v>501</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E129" s="0" t="s">
         <v>27</v>
@@ -6218,7 +6533,7 @@
         <v>550</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>609</v>
+        <v>722</v>
       </c>
       <c r="J129" s="0">
         <v>381.40570000000002</v>
@@ -6235,7 +6550,7 @@
         <v>501</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E130" s="0" t="s">
         <v>27</v>
@@ -6250,7 +6565,7 @@
         <v>551</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>610</v>
+        <v>723</v>
       </c>
       <c r="J130" s="0">
         <v>371.59660000000002</v>
@@ -6267,7 +6582,7 @@
         <v>501</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E131" s="0" t="s">
         <v>27</v>
@@ -6282,7 +6597,7 @@
         <v>552</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>611</v>
+        <v>724</v>
       </c>
       <c r="J131" s="0">
         <v>364.02569999999997</v>
@@ -6299,7 +6614,7 @@
         <v>501</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E132" s="0" t="s">
         <v>27</v>
@@ -6314,7 +6629,7 @@
         <v>146</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>612</v>
+        <v>725</v>
       </c>
       <c r="J132" s="0">
         <v>342.74220000000003</v>
@@ -6331,7 +6646,7 @@
         <v>501</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>27</v>
@@ -6346,7 +6661,7 @@
         <v>553</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>613</v>
+        <v>726</v>
       </c>
       <c r="J133" s="0">
         <v>331.7552</v>
@@ -9959,13 +10274,13 @@
         <v>43</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J246" s="0">
-        <v>662.97000000000003</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="247">
@@ -9991,13 +10306,13 @@
         <v>43</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J247" s="0">
-        <v>489.01900000000001</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10023,13 +10338,13 @@
         <v>43</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J248" s="0">
-        <v>486.78719999999999</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="249">
@@ -10055,13 +10370,13 @@
         <v>43</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J249" s="0">
-        <v>478.59969999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="250">
@@ -10087,13 +10402,13 @@
         <v>44</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J250" s="0">
-        <v>456.38220000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="251">
@@ -10119,13 +10434,13 @@
         <v>44</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J251" s="0">
-        <v>361.197</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="252">
@@ -10151,13 +10466,13 @@
         <v>44</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J252" s="0">
-        <v>350.10750000000002</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="253">
@@ -10171,25 +10486,25 @@
         <v>7</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J253" s="0">
-        <v>332.8802</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="254">
@@ -10209,19 +10524,19 @@
         <v>25</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J254" s="0">
-        <v>9850.5967000000001</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="255">
@@ -10238,22 +10553,22 @@
         <v>16</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J255" s="0">
-        <v>8299.1229999999996</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="256">
@@ -10273,19 +10588,19 @@
         <v>26</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J256" s="0">
-        <v>1061.2550000000001</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="257">
@@ -10302,22 +10617,22 @@
         <v>16</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J257" s="0">
-        <v>863.95190000000002</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="258">
@@ -10337,19 +10652,19 @@
         <v>27</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J258" s="0">
-        <v>537.24440000000004</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="259">
@@ -10369,19 +10684,19 @@
         <v>27</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J259" s="0">
-        <v>512.39139999999998</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="260">
@@ -10401,19 +10716,19 @@
         <v>27</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J260" s="0">
-        <v>461.678</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="261">
@@ -10433,19 +10748,19 @@
         <v>27</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J261" s="0">
-        <v>446.13510000000002</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="262">
@@ -10465,19 +10780,19 @@
         <v>27</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J262" s="0">
-        <v>416.1148</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="263">
@@ -10497,19 +10812,19 @@
         <v>27</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J263" s="0">
-        <v>385.80329999999998</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="264">
@@ -10529,19 +10844,19 @@
         <v>27</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J264" s="0">
-        <v>376.43869999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="265">
@@ -10555,25 +10870,25 @@
         <v>7</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J265" s="0">
-        <v>340.64490000000001</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="266">
@@ -10593,19 +10908,19 @@
         <v>25</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J266" s="0">
-        <v>9114.7715000000008</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="267">
@@ -10622,22 +10937,22 @@
         <v>17</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J267" s="0">
-        <v>7656.0316999999996</v>
+        <v>1088.5953</v>
       </c>
     </row>
     <row r="268">
@@ -10657,19 +10972,19 @@
         <v>26</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J268" s="0">
-        <v>1088.5953</v>
+        <v>1085.6431</v>
       </c>
     </row>
     <row r="269">
@@ -10689,19 +11004,19 @@
         <v>26</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J269" s="0">
-        <v>1085.6431</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="270">
@@ -10721,19 +11036,19 @@
         <v>26</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J270" s="0">
-        <v>542.5788</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="271">
@@ -10753,19 +11068,19 @@
         <v>26</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J271" s="0">
-        <v>534.76580000000001</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="272">
@@ -10785,19 +11100,19 @@
         <v>26</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J272" s="0">
-        <v>484.83710000000002</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="273">
@@ -10817,19 +11132,19 @@
         <v>26</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J273" s="0">
-        <v>468.87529999999998</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="274">
@@ -10849,19 +11164,19 @@
         <v>26</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J274" s="0">
-        <v>398.83769999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="275">
@@ -10881,19 +11196,19 @@
         <v>26</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J275" s="0">
-        <v>337.36939999999999</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="276">
@@ -10913,19 +11228,19 @@
         <v>26</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J276" s="0">
-        <v>311.84429999999998</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="277">
@@ -10939,25 +11254,25 @@
         <v>7</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J277" s="0">
-        <v>245.285</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="278">
@@ -10977,19 +11292,19 @@
         <v>25</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J278" s="0">
-        <v>2887.6174000000001</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="279">
@@ -11006,22 +11321,22 @@
         <v>23</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J279" s="0">
-        <v>2872.1073999999999</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="280">
@@ -11041,19 +11356,19 @@
         <v>26</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J280" s="0">
-        <v>975.3777</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="281">
@@ -11070,22 +11385,22 @@
         <v>23</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J281" s="0">
-        <v>616.08360000000005</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="282">
@@ -11105,19 +11420,19 @@
         <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J282" s="0">
-        <v>465.53719999999999</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="283">
@@ -11137,19 +11452,19 @@
         <v>27</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J283" s="0">
-        <v>436.18400000000003</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="284">
@@ -11169,19 +11484,19 @@
         <v>27</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J284" s="0">
-        <v>415.78980000000001</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="285">
@@ -11201,19 +11516,19 @@
         <v>27</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J285" s="0">
-        <v>391.16430000000003</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="286">
@@ -11233,19 +11548,19 @@
         <v>27</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J286" s="0">
-        <v>362.91770000000002</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="287">
@@ -11265,19 +11580,19 @@
         <v>27</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J287" s="0">
-        <v>315.58260000000001</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="288">
@@ -11297,19 +11612,19 @@
         <v>27</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J288" s="0">
-        <v>315.33229999999998</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="289">
@@ -11320,28 +11635,28 @@
         <v>4</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>207</v>
+        <v>507</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>451</v>
+        <v>727</v>
       </c>
       <c r="J289" s="0">
-        <v>254.02879999999999</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="290">
@@ -11355,25 +11670,25 @@
         <v>501</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E290" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>614</v>
+        <v>728</v>
       </c>
       <c r="J290" s="0">
-        <v>10897.75</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="291">
@@ -11387,25 +11702,25 @@
         <v>501</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>615</v>
+        <v>729</v>
       </c>
       <c r="J291" s="0">
-        <v>5963.8306000000002</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="292">
@@ -11419,25 +11734,25 @@
         <v>501</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E292" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>616</v>
+        <v>730</v>
       </c>
       <c r="J292" s="0">
-        <v>1364.115</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="293">
@@ -11451,25 +11766,25 @@
         <v>501</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>617</v>
+        <v>731</v>
       </c>
       <c r="J293" s="0">
-        <v>1002.6719000000001</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="294">
@@ -11483,25 +11798,25 @@
         <v>501</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E294" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>618</v>
+        <v>732</v>
       </c>
       <c r="J294" s="0">
-        <v>557.97879999999998</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="295">
@@ -11515,25 +11830,25 @@
         <v>501</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E295" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>619</v>
+        <v>733</v>
       </c>
       <c r="J295" s="0">
-        <v>511.4341</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="296">
@@ -11547,25 +11862,25 @@
         <v>501</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E296" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>620</v>
+        <v>734</v>
       </c>
       <c r="J296" s="0">
-        <v>485.53699999999998</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="297">
@@ -11579,25 +11894,25 @@
         <v>501</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E297" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>621</v>
+        <v>735</v>
       </c>
       <c r="J297" s="0">
-        <v>456.29579999999999</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="298">
@@ -11611,25 +11926,25 @@
         <v>501</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E298" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>622</v>
+        <v>736</v>
       </c>
       <c r="J298" s="0">
-        <v>403.62130000000002</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="299">
@@ -11643,25 +11958,25 @@
         <v>501</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E299" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>623</v>
+        <v>737</v>
       </c>
       <c r="J299" s="0">
-        <v>384.92849999999999</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="300">
@@ -11675,25 +11990,25 @@
         <v>501</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>502</v>
+        <v>674</v>
       </c>
       <c r="E300" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>624</v>
+        <v>738</v>
       </c>
       <c r="J300" s="0">
-        <v>345.9332</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="301">
@@ -11707,25 +12022,25 @@
         <v>501</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>502</v>
+        <v>675</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>625</v>
+        <v>739</v>
       </c>
       <c r="J301" s="0">
-        <v>329.33870000000002</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="302">
@@ -11739,25 +12054,25 @@
         <v>501</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E302" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>626</v>
+        <v>740</v>
       </c>
       <c r="J302" s="0">
-        <v>9494.3554999999997</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="303">
@@ -11771,25 +12086,25 @@
         <v>501</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>627</v>
+        <v>741</v>
       </c>
       <c r="J303" s="0">
-        <v>6959.3242</v>
+        <v>989.73109999999997</v>
       </c>
     </row>
     <row r="304">
@@ -11803,25 +12118,25 @@
         <v>501</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E304" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>628</v>
+        <v>742</v>
       </c>
       <c r="J304" s="0">
-        <v>989.73109999999997</v>
+        <v>709.46839999999998</v>
       </c>
     </row>
     <row r="305">
@@ -11835,25 +12150,25 @@
         <v>501</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>629</v>
+        <v>743</v>
       </c>
       <c r="J305" s="0">
-        <v>709.46839999999998</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="306">
@@ -11867,25 +12182,25 @@
         <v>501</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E306" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>630</v>
+        <v>744</v>
       </c>
       <c r="J306" s="0">
-        <v>528.32619999999997</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="307">
@@ -11899,25 +12214,25 @@
         <v>501</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E307" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>631</v>
+        <v>745</v>
       </c>
       <c r="J307" s="0">
-        <v>502.16129999999998</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="308">
@@ -11931,25 +12246,25 @@
         <v>501</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E308" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>632</v>
+        <v>746</v>
       </c>
       <c r="J308" s="0">
-        <v>468.14839999999998</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="309">
@@ -11963,25 +12278,25 @@
         <v>501</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E309" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>633</v>
+        <v>747</v>
       </c>
       <c r="J309" s="0">
-        <v>413.35890000000001</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="310">
@@ -11995,25 +12310,25 @@
         <v>501</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E310" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>634</v>
+        <v>748</v>
       </c>
       <c r="J310" s="0">
-        <v>410.47199999999998</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="311">
@@ -12027,25 +12342,25 @@
         <v>501</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E311" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>635</v>
+        <v>749</v>
       </c>
       <c r="J311" s="0">
-        <v>371.8809</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="312">
@@ -12059,25 +12374,25 @@
         <v>501</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>503</v>
+        <v>675</v>
       </c>
       <c r="E312" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>636</v>
+        <v>750</v>
       </c>
       <c r="J312" s="0">
-        <v>347.0478</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="313">
@@ -12091,25 +12406,25 @@
         <v>501</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>503</v>
+        <v>676</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>637</v>
+        <v>751</v>
       </c>
       <c r="J313" s="0">
-        <v>302.97559999999999</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="314">
@@ -12123,25 +12438,25 @@
         <v>501</v>
       </c>
       <c r="D314" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E314" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>638</v>
+        <v>752</v>
       </c>
       <c r="J314" s="0">
-        <v>8923.2001999999993</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="315">
@@ -12155,25 +12470,25 @@
         <v>501</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>639</v>
+        <v>753</v>
       </c>
       <c r="J315" s="0">
-        <v>7434.9364999999998</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="316">
@@ -12187,25 +12502,25 @@
         <v>501</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>504</v>
+        <v>676</v>
       </c>
       <c r="E316" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>640</v>
+        <v>754</v>
       </c>
       <c r="J316" s="0">
-        <v>1198.5989</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="317">
@@ -12219,25 +12534,25 @@
         <v>501</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>641</v>
+        <v>755</v>
       </c>
       <c r="J317" s="0">
-        <v>1016.6576</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="318">
@@ -12251,25 +12566,25 @@
         <v>501</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>642</v>
+        <v>756</v>
       </c>
       <c r="J318" s="0">
-        <v>783.98929999999996</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="319">
@@ -12283,25 +12598,25 @@
         <v>501</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>643</v>
+        <v>757</v>
       </c>
       <c r="J319" s="0">
-        <v>765.39179999999999</v>
+        <v>848.39120000000003</v>
       </c>
     </row>
     <row r="320">
@@ -12315,25 +12630,25 @@
         <v>501</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>644</v>
+        <v>758</v>
       </c>
       <c r="J320" s="0">
-        <v>763.20230000000004</v>
+        <v>740.85990000000004</v>
       </c>
     </row>
     <row r="321">
@@ -12347,25 +12662,25 @@
         <v>501</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E321" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>645</v>
+        <v>759</v>
       </c>
       <c r="J321" s="0">
-        <v>706.49959999999999</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="322">
@@ -12379,25 +12694,25 @@
         <v>501</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E322" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>539</v>
+        <v>64</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>646</v>
+        <v>760</v>
       </c>
       <c r="J322" s="0">
-        <v>532.22119999999995</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="323">
@@ -12411,25 +12726,25 @@
         <v>501</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E323" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G323" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>647</v>
+        <v>761</v>
       </c>
       <c r="J323" s="0">
-        <v>499.38260000000002</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="324">
@@ -12443,25 +12758,25 @@
         <v>501</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E324" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>648</v>
+        <v>762</v>
       </c>
       <c r="J324" s="0">
-        <v>487.96170000000001</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="325">
@@ -12475,25 +12790,25 @@
         <v>501</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>504</v>
+        <v>677</v>
       </c>
       <c r="E325" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>649</v>
+        <v>763</v>
       </c>
       <c r="J325" s="0">
-        <v>471.42149999999998</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="326">
@@ -12507,25 +12822,25 @@
         <v>501</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E326" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>650</v>
+        <v>764</v>
       </c>
       <c r="J326" s="0">
-        <v>10363.415999999999</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="327">
@@ -12539,25 +12854,25 @@
         <v>501</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>651</v>
+        <v>765</v>
       </c>
       <c r="J327" s="0">
-        <v>8731.0702999999994</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="328">
@@ -12571,25 +12886,25 @@
         <v>501</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="E328" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>652</v>
+        <v>766</v>
       </c>
       <c r="J328" s="0">
-        <v>848.39120000000003</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="329">
@@ -12603,25 +12918,25 @@
         <v>501</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>653</v>
+        <v>767</v>
       </c>
       <c r="J329" s="0">
-        <v>740.85990000000004</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="330">
@@ -12635,25 +12950,25 @@
         <v>501</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>654</v>
+        <v>768</v>
       </c>
       <c r="J330" s="0">
-        <v>509.65910000000002</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="331">
@@ -12667,25 +12982,25 @@
         <v>501</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>64</v>
+        <v>556</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>655</v>
+        <v>769</v>
       </c>
       <c r="J331" s="0">
-        <v>497.6062</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="332">
@@ -12699,25 +13014,25 @@
         <v>501</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>656</v>
+        <v>770</v>
       </c>
       <c r="J332" s="0">
-        <v>473.81920000000002</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="333">
@@ -12731,25 +13046,25 @@
         <v>501</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E333" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>657</v>
+        <v>771</v>
       </c>
       <c r="J333" s="0">
-        <v>386.12639999999999</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="334">
@@ -12763,25 +13078,25 @@
         <v>501</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E334" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G334" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>658</v>
+        <v>772</v>
       </c>
       <c r="J334" s="0">
-        <v>381.40570000000002</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="335">
@@ -12795,25 +13110,25 @@
         <v>501</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E335" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>659</v>
+        <v>773</v>
       </c>
       <c r="J335" s="0">
-        <v>371.59660000000002</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="336">
@@ -12827,25 +13142,25 @@
         <v>501</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E336" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G336" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="J336" s="0">
-        <v>364.02569999999997</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="337">
@@ -12859,25 +13174,25 @@
         <v>501</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>505</v>
+        <v>678</v>
       </c>
       <c r="E337" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>661</v>
+        <v>775</v>
       </c>
       <c r="J337" s="0">
-        <v>331.7552</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="338">
@@ -12891,25 +13206,25 @@
         <v>501</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>506</v>
+        <v>678</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>662</v>
+        <v>776</v>
       </c>
       <c r="J338" s="0">
-        <v>1621.762</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="339">
@@ -12923,25 +13238,25 @@
         <v>501</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>506</v>
+        <v>678</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>663</v>
+        <v>777</v>
       </c>
       <c r="J339" s="0">
-        <v>1023.5883</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="340">
@@ -12955,25 +13270,25 @@
         <v>501</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>506</v>
+        <v>678</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G340" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>664</v>
+        <v>778</v>
       </c>
       <c r="J340" s="0">
-        <v>634.67409999999995</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="341">
@@ -12984,28 +13299,28 @@
         <v>4</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>557</v>
+        <v>129</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>665</v>
+        <v>452</v>
       </c>
       <c r="J341" s="0">
-        <v>589.45230000000004</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="342">
@@ -13016,28 +13331,28 @@
         <v>4</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>666</v>
+        <v>453</v>
       </c>
       <c r="J342" s="0">
-        <v>441.32260000000002</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="343">
@@ -13048,28 +13363,28 @@
         <v>4</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>559</v>
+        <v>208</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>667</v>
+        <v>454</v>
       </c>
       <c r="J343" s="0">
-        <v>406.00639999999999</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="344">
@@ -13080,28 +13395,28 @@
         <v>4</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G344" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>560</v>
+        <v>209</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>668</v>
+        <v>455</v>
       </c>
       <c r="J344" s="0">
-        <v>404.98939999999999</v>
+        <v>981.88890000000004</v>
       </c>
     </row>
     <row r="345">
@@ -13112,28 +13427,28 @@
         <v>4</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E345" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>561</v>
+        <v>133</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>669</v>
+        <v>456</v>
       </c>
       <c r="J345" s="0">
-        <v>356.87450000000001</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="346">
@@ -13144,28 +13459,28 @@
         <v>4</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E346" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G346" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>562</v>
+        <v>134</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>670</v>
+        <v>457</v>
       </c>
       <c r="J346" s="0">
-        <v>326.86750000000001</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="347">
@@ -13176,28 +13491,28 @@
         <v>4</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E347" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G347" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>563</v>
+        <v>135</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>671</v>
+        <v>458</v>
       </c>
       <c r="J347" s="0">
-        <v>313.15320000000003</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="348">
@@ -13208,28 +13523,28 @@
         <v>4</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E348" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G348" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>564</v>
+        <v>136</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>672</v>
+        <v>459</v>
       </c>
       <c r="J348" s="0">
-        <v>302.25330000000002</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="349">
@@ -13240,28 +13555,28 @@
         <v>4</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="E349" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>565</v>
+        <v>137</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>673</v>
+        <v>460</v>
       </c>
       <c r="J349" s="0">
-        <v>241.7327</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="350">
@@ -13278,22 +13593,22 @@
         <v>18</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="J350" s="0">
-        <v>8389.2909999999993</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="351">
@@ -13310,22 +13625,22 @@
         <v>18</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="J351" s="0">
-        <v>8068.0429999999997</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="352">
@@ -13342,22 +13657,22 @@
         <v>18</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="J352" s="0">
-        <v>1304.9119000000001</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="353">
@@ -13371,25 +13686,25 @@
         <v>8</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>209</v>
+        <v>58</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="J353" s="0">
-        <v>981.88890000000004</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="354">
@@ -13403,25 +13718,25 @@
         <v>8</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="J354" s="0">
-        <v>528.16520000000003</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="355">
@@ -13435,25 +13750,25 @@
         <v>8</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="J355" s="0">
-        <v>464.43889999999999</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="356">
@@ -13467,25 +13782,25 @@
         <v>8</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G356" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="J356" s="0">
-        <v>449.87619999999998</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="357">
@@ -13499,25 +13814,25 @@
         <v>8</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E357" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="J357" s="0">
-        <v>447.66699999999997</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="358">
@@ -13531,25 +13846,25 @@
         <v>8</v>
       </c>
       <c r="D358" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E358" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="J358" s="0">
-        <v>391.69869999999997</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="359">
@@ -13563,25 +13878,25 @@
         <v>8</v>
       </c>
       <c r="D359" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E359" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G359" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="J359" s="0">
-        <v>372.4153</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13595,25 +13910,25 @@
         <v>8</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E360" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="J360" s="0">
-        <v>366.97289999999998</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="361">
@@ -13627,25 +13942,25 @@
         <v>8</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E361" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="J361" s="0">
-        <v>329.11259999999999</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="362">
@@ -13662,22 +13977,22 @@
         <v>19</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G362" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="J362" s="0">
-        <v>9741.5614999999998</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="363">
@@ -13694,22 +14009,22 @@
         <v>19</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="J363" s="0">
-        <v>8198.8974999999991</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="364">
@@ -13726,22 +14041,22 @@
         <v>19</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="J364" s="0">
-        <v>1259.1116</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="365">
@@ -13752,28 +14067,28 @@
         <v>4</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G365" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="J365" s="0">
-        <v>964.0145</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="366">
@@ -13784,28 +14099,28 @@
         <v>4</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="J366" s="0">
-        <v>539.45429999999999</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="367">
@@ -13816,28 +14131,28 @@
         <v>4</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="J367" s="0">
-        <v>485.64830000000001</v>
+        <v>829.46619999999996</v>
       </c>
     </row>
     <row r="368">
@@ -13848,28 +14163,28 @@
         <v>4</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D368" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G368" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="J368" s="0">
-        <v>457.39609999999999</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="369">
@@ -13880,28 +14195,28 @@
         <v>4</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D369" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E369" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="J369" s="0">
-        <v>454.66460000000001</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="370">
@@ -13912,28 +14227,28 @@
         <v>4</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D370" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E370" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G370" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="J370" s="0">
-        <v>368.51979999999998</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="371">
@@ -13944,28 +14259,28 @@
         <v>4</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D371" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E371" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G371" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="J371" s="0">
-        <v>342.74220000000003</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="372">
@@ -13976,28 +14291,28 @@
         <v>4</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E372" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G372" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="J372" s="0">
-        <v>302.46800000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="373">
@@ -14008,28 +14323,28 @@
         <v>4</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D373" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E373" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="J373" s="0">
-        <v>300.47250000000003</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="374">
@@ -14046,22 +14361,22 @@
         <v>20</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="J374" s="0">
-        <v>10892.9414</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="375">
@@ -14078,22 +14393,22 @@
         <v>20</v>
       </c>
       <c r="E375" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="J375" s="0">
-        <v>5918.6806999999999</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="376">
@@ -14110,22 +14425,22 @@
         <v>20</v>
       </c>
       <c r="E376" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G376" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="J376" s="0">
-        <v>829.46619999999996</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="377">
@@ -14139,25 +14454,25 @@
         <v>9</v>
       </c>
       <c r="D377" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F377" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G377" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="J377" s="0">
-        <v>726.14110000000005</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="378">
@@ -14171,25 +14486,25 @@
         <v>9</v>
       </c>
       <c r="D378" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F378" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G378" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="J378" s="0">
-        <v>498.3132</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="379">
@@ -14203,25 +14518,25 @@
         <v>9</v>
       </c>
       <c r="D379" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="J379" s="0">
-        <v>487.10520000000002</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="380">
@@ -14235,25 +14550,25 @@
         <v>9</v>
       </c>
       <c r="D380" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F380" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G380" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="J380" s="0">
-        <v>485.66770000000002</v>
+        <v>893.57759999999996</v>
       </c>
     </row>
     <row r="381">
@@ -14267,25 +14582,25 @@
         <v>9</v>
       </c>
       <c r="D381" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E381" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G381" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="J381" s="0">
-        <v>478.11529999999999</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="382">
@@ -14299,25 +14614,25 @@
         <v>9</v>
       </c>
       <c r="D382" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E382" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F382" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G382" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="J382" s="0">
-        <v>375.48970000000003</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="383">
@@ -14331,25 +14646,25 @@
         <v>9</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E383" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G383" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="J383" s="0">
-        <v>359.0838</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="384">
@@ -14363,25 +14678,25 @@
         <v>9</v>
       </c>
       <c r="D384" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E384" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G384" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H384" s="0" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="J384" s="0">
-        <v>338.9837</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="385">
@@ -14395,25 +14710,25 @@
         <v>9</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E385" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G385" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H385" s="0" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="J385" s="0">
-        <v>293.55579999999998</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="386">
@@ -14430,22 +14745,22 @@
         <v>21</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="J386" s="0">
-        <v>9826.1103999999996</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="387">
@@ -14462,22 +14777,22 @@
         <v>21</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F387" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G387" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="J387" s="0">
-        <v>7957.9004000000004</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="388">
@@ -14494,22 +14809,22 @@
         <v>21</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G388" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H388" s="0" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="J388" s="0">
-        <v>1958.7829999999999</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="389">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30600" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37370" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -8697,7 +8697,7 @@
         <v>13</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>29</v>
@@ -8706,13 +8706,13 @@
         <v>43</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J197" s="0">
-        <v>5932.7479999999996</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="198">
@@ -8732,19 +8732,19 @@
         <v>26</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J198" s="0">
-        <v>901.9991</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="199">
@@ -8761,22 +8761,22 @@
         <v>13</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J199" s="0">
-        <v>893.56960000000004</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="200">
@@ -8796,19 +8796,19 @@
         <v>27</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J200" s="0">
-        <v>549.74869999999999</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="201">
@@ -8828,19 +8828,19 @@
         <v>27</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J201" s="0">
-        <v>530.14729999999997</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="202">
@@ -8860,19 +8860,19 @@
         <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J202" s="0">
-        <v>489.4966</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="203">
@@ -8892,19 +8892,19 @@
         <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J203" s="0">
-        <v>482.49549999999999</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="204">
@@ -8924,19 +8924,19 @@
         <v>27</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J204" s="0">
-        <v>378.9196</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="205">
@@ -8956,19 +8956,19 @@
         <v>27</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J205" s="0">
-        <v>366.15300000000002</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="206">
@@ -8988,19 +8988,19 @@
         <v>27</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J206" s="0">
-        <v>340.57749999999999</v>
+        <v>329.09449999999998</v>
       </c>
     </row>
     <row r="207">
@@ -9014,25 +9014,25 @@
         <v>6</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J207" s="0">
-        <v>329.09449999999998</v>
+        <v>4307.7025999999996</v>
       </c>
     </row>
     <row r="208">
@@ -9052,19 +9052,19 @@
         <v>25</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J208" s="0">
-        <v>4307.7025999999996</v>
+        <v>1837.0477000000001</v>
       </c>
     </row>
     <row r="209">
@@ -9081,22 +9081,22 @@
         <v>22</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J209" s="0">
-        <v>1837.0477000000001</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="210">
@@ -9116,19 +9116,19 @@
         <v>26</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J210" s="0">
-        <v>616.08360000000005</v>
+        <v>552.42719999999997</v>
       </c>
     </row>
     <row r="211">
@@ -9145,22 +9145,22 @@
         <v>22</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J211" s="0">
-        <v>552.42719999999997</v>
+        <v>399.44740000000002</v>
       </c>
     </row>
     <row r="212">
@@ -9180,19 +9180,19 @@
         <v>27</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J212" s="0">
-        <v>399.44740000000002</v>
+        <v>377.98289999999997</v>
       </c>
     </row>
     <row r="213">
@@ -9212,19 +9212,19 @@
         <v>27</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J213" s="0">
-        <v>377.98289999999997</v>
+        <v>376.71690000000001</v>
       </c>
     </row>
     <row r="214">
@@ -9244,19 +9244,19 @@
         <v>27</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J214" s="0">
-        <v>376.71690000000001</v>
+        <v>375.52019999999999</v>
       </c>
     </row>
     <row r="215">
@@ -9276,19 +9276,19 @@
         <v>27</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J215" s="0">
-        <v>375.52019999999999</v>
+        <v>370.8648</v>
       </c>
     </row>
     <row r="216">
@@ -9308,19 +9308,19 @@
         <v>27</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J216" s="0">
-        <v>370.8648</v>
+        <v>342.89479999999998</v>
       </c>
     </row>
     <row r="217">
@@ -9340,19 +9340,19 @@
         <v>27</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J217" s="0">
-        <v>342.89479999999998</v>
+        <v>307.26029999999997</v>
       </c>
     </row>
     <row r="218">
@@ -9372,19 +9372,19 @@
         <v>27</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J218" s="0">
-        <v>307.26029999999997</v>
+        <v>261.58179999999999</v>
       </c>
     </row>
     <row r="219">
@@ -9395,28 +9395,28 @@
         <v>4</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J219" s="0">
-        <v>261.58179999999999</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="220">
@@ -9436,19 +9436,19 @@
         <v>25</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J220" s="0">
-        <v>10466.208000000001</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="221">
@@ -9465,22 +9465,22 @@
         <v>14</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J221" s="0">
-        <v>7328.0029000000004</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="222">
@@ -9500,19 +9500,19 @@
         <v>26</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J222" s="0">
-        <v>1015.5606</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="223">
@@ -9532,19 +9532,19 @@
         <v>26</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J223" s="0">
-        <v>908.67830000000004</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="224">
@@ -9564,19 +9564,19 @@
         <v>26</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J224" s="0">
-        <v>520.97770000000003</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="225">
@@ -9596,19 +9596,19 @@
         <v>26</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J225" s="0">
-        <v>488.97149999999999</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="226">
@@ -9628,19 +9628,19 @@
         <v>26</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J226" s="0">
-        <v>484.75029999999998</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="227">
@@ -9660,19 +9660,19 @@
         <v>26</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J227" s="0">
-        <v>438.36930000000001</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="228">
@@ -9692,19 +9692,19 @@
         <v>26</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J228" s="0">
-        <v>369.10219999999998</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="229">
@@ -9724,19 +9724,19 @@
         <v>26</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J229" s="0">
-        <v>342.30680000000001</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="230">
@@ -9756,19 +9756,19 @@
         <v>26</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J230" s="0">
-        <v>280.75409999999999</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="231">
@@ -9782,25 +9782,25 @@
         <v>7</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J231" s="0">
-        <v>270.84679999999997</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="232">
@@ -9820,19 +9820,19 @@
         <v>25</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J232" s="0">
-        <v>8934.2567999999992</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="233">
@@ -9849,22 +9849,22 @@
         <v>15</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J233" s="0">
-        <v>7192.2339000000002</v>
+        <v>1017.6188</v>
       </c>
     </row>
     <row r="234">
@@ -9884,19 +9884,19 @@
         <v>26</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J234" s="0">
-        <v>1017.6188</v>
+        <v>892.98720000000003</v>
       </c>
     </row>
     <row r="235">
@@ -9913,22 +9913,22 @@
         <v>15</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J235" s="0">
-        <v>892.98720000000003</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="236">
@@ -9948,19 +9948,19 @@
         <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J236" s="0">
-        <v>489.01900000000001</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="237">
@@ -9980,19 +9980,19 @@
         <v>27</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J237" s="0">
-        <v>486.78719999999999</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="238">
@@ -10012,19 +10012,19 @@
         <v>27</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J238" s="0">
-        <v>478.59969999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="239">
@@ -10044,19 +10044,19 @@
         <v>27</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J239" s="0">
-        <v>456.38220000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="240">
@@ -10076,19 +10076,19 @@
         <v>27</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J240" s="0">
-        <v>361.197</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="241">
@@ -10108,19 +10108,19 @@
         <v>27</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J241" s="0">
-        <v>350.10750000000002</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="242">
@@ -10134,25 +10134,25 @@
         <v>7</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J242" s="0">
-        <v>332.8802</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="243">
@@ -10172,19 +10172,19 @@
         <v>25</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J243" s="0">
-        <v>9850.5967000000001</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="244">
@@ -10201,22 +10201,22 @@
         <v>16</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J244" s="0">
-        <v>8299.1229999999996</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="245">
@@ -10236,19 +10236,19 @@
         <v>26</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J245" s="0">
-        <v>1061.2550000000001</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="246">
@@ -10265,22 +10265,22 @@
         <v>16</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J246" s="0">
-        <v>863.95190000000002</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="247">
@@ -10300,19 +10300,19 @@
         <v>27</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J247" s="0">
-        <v>537.24440000000004</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="248">
@@ -10332,19 +10332,19 @@
         <v>27</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J248" s="0">
-        <v>512.39139999999998</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="249">
@@ -10364,19 +10364,19 @@
         <v>27</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J249" s="0">
-        <v>461.678</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="250">
@@ -10396,19 +10396,19 @@
         <v>27</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J250" s="0">
-        <v>446.13510000000002</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="251">
@@ -10428,19 +10428,19 @@
         <v>27</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J251" s="0">
-        <v>416.1148</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="252">
@@ -10460,19 +10460,19 @@
         <v>27</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J252" s="0">
-        <v>385.80329999999998</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="253">
@@ -10492,19 +10492,19 @@
         <v>27</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J253" s="0">
-        <v>376.43869999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="254">
@@ -10518,25 +10518,25 @@
         <v>7</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J254" s="0">
-        <v>340.64490000000001</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="255">
@@ -10556,19 +10556,19 @@
         <v>25</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J255" s="0">
-        <v>9114.7715000000008</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="256">
@@ -10585,22 +10585,22 @@
         <v>17</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J256" s="0">
-        <v>7656.0316999999996</v>
+        <v>1088.5953</v>
       </c>
     </row>
     <row r="257">
@@ -10620,19 +10620,19 @@
         <v>26</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J257" s="0">
-        <v>1088.5953</v>
+        <v>1085.6431</v>
       </c>
     </row>
     <row r="258">
@@ -10652,19 +10652,19 @@
         <v>26</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J258" s="0">
-        <v>1085.6431</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="259">
@@ -10684,19 +10684,19 @@
         <v>26</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J259" s="0">
-        <v>542.5788</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="260">
@@ -10716,19 +10716,19 @@
         <v>26</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J260" s="0">
-        <v>534.76580000000001</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="261">
@@ -10748,19 +10748,19 @@
         <v>26</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J261" s="0">
-        <v>484.83710000000002</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="262">
@@ -10780,19 +10780,19 @@
         <v>26</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J262" s="0">
-        <v>468.87529999999998</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="263">
@@ -10812,19 +10812,19 @@
         <v>26</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J263" s="0">
-        <v>398.83769999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="264">
@@ -10844,19 +10844,19 @@
         <v>26</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J264" s="0">
-        <v>337.36939999999999</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="265">
@@ -10876,19 +10876,19 @@
         <v>26</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J265" s="0">
-        <v>311.84429999999998</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="266">
@@ -10902,25 +10902,25 @@
         <v>7</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J266" s="0">
-        <v>245.285</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="267">
@@ -10940,19 +10940,19 @@
         <v>25</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J267" s="0">
-        <v>2887.6174000000001</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="268">
@@ -10969,22 +10969,22 @@
         <v>23</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J268" s="0">
-        <v>2872.1073999999999</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="269">
@@ -11004,19 +11004,19 @@
         <v>26</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J269" s="0">
-        <v>975.3777</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="270">
@@ -11033,22 +11033,22 @@
         <v>23</v>
       </c>
       <c r="E270" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J270" s="0">
-        <v>616.08360000000005</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="271">
@@ -11068,19 +11068,19 @@
         <v>27</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J271" s="0">
-        <v>465.53719999999999</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="272">
@@ -11100,19 +11100,19 @@
         <v>27</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J272" s="0">
-        <v>436.18400000000003</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="273">
@@ -11132,19 +11132,19 @@
         <v>27</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J273" s="0">
-        <v>415.78980000000001</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="274">
@@ -11164,19 +11164,19 @@
         <v>27</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J274" s="0">
-        <v>391.16430000000003</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="275">
@@ -11196,19 +11196,19 @@
         <v>27</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J275" s="0">
-        <v>362.91770000000002</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="276">
@@ -11228,19 +11228,19 @@
         <v>27</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J276" s="0">
-        <v>315.58260000000001</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="277">
@@ -11260,19 +11260,19 @@
         <v>27</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J277" s="0">
-        <v>315.33229999999998</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="278">
@@ -11283,28 +11283,28 @@
         <v>4</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>207</v>
+        <v>507</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>451</v>
+        <v>727</v>
       </c>
       <c r="J278" s="0">
-        <v>254.02879999999999</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="279">
@@ -11324,19 +11324,19 @@
         <v>25</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J279" s="0">
-        <v>10897.75</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="280">
@@ -11353,22 +11353,22 @@
         <v>674</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J280" s="0">
-        <v>5963.8306000000002</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="281">
@@ -11388,19 +11388,19 @@
         <v>26</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J281" s="0">
-        <v>1364.115</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="282">
@@ -11417,22 +11417,22 @@
         <v>674</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J282" s="0">
-        <v>1002.6719000000001</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="283">
@@ -11452,19 +11452,19 @@
         <v>27</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J283" s="0">
-        <v>557.97879999999998</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="284">
@@ -11484,19 +11484,19 @@
         <v>27</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J284" s="0">
-        <v>511.4341</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="285">
@@ -11516,19 +11516,19 @@
         <v>27</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J285" s="0">
-        <v>485.53699999999998</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="286">
@@ -11548,19 +11548,19 @@
         <v>27</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G286" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J286" s="0">
-        <v>456.29579999999999</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="287">
@@ -11580,19 +11580,19 @@
         <v>27</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J287" s="0">
-        <v>403.62130000000002</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="288">
@@ -11612,19 +11612,19 @@
         <v>27</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J288" s="0">
-        <v>384.92849999999999</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="289">
@@ -11644,19 +11644,19 @@
         <v>27</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J289" s="0">
-        <v>345.9332</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="290">
@@ -11670,25 +11670,25 @@
         <v>501</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J290" s="0">
-        <v>329.33870000000002</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="291">
@@ -11708,19 +11708,19 @@
         <v>25</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J291" s="0">
-        <v>9494.3554999999997</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="292">
@@ -11737,22 +11737,22 @@
         <v>675</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J292" s="0">
-        <v>6959.3242</v>
+        <v>989.73109999999997</v>
       </c>
     </row>
     <row r="293">
@@ -11772,19 +11772,19 @@
         <v>26</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J293" s="0">
-        <v>989.73109999999997</v>
+        <v>709.46839999999998</v>
       </c>
     </row>
     <row r="294">
@@ -11801,22 +11801,22 @@
         <v>675</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J294" s="0">
-        <v>709.46839999999998</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="295">
@@ -11836,19 +11836,19 @@
         <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J295" s="0">
-        <v>528.32619999999997</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="296">
@@ -11868,19 +11868,19 @@
         <v>27</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J296" s="0">
-        <v>502.16129999999998</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="297">
@@ -11900,19 +11900,19 @@
         <v>27</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J297" s="0">
-        <v>468.14839999999998</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="298">
@@ -11932,19 +11932,19 @@
         <v>27</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G298" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J298" s="0">
-        <v>413.35890000000001</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="299">
@@ -11964,19 +11964,19 @@
         <v>27</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J299" s="0">
-        <v>410.47199999999998</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="300">
@@ -11996,19 +11996,19 @@
         <v>27</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J300" s="0">
-        <v>371.8809</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="301">
@@ -12028,19 +12028,19 @@
         <v>27</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J301" s="0">
-        <v>347.0478</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="302">
@@ -12054,25 +12054,25 @@
         <v>501</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J302" s="0">
-        <v>302.97559999999999</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="303">
@@ -12092,19 +12092,19 @@
         <v>25</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J303" s="0">
-        <v>8923.2001999999993</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="304">
@@ -12121,22 +12121,22 @@
         <v>676</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J304" s="0">
-        <v>7434.9364999999998</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="305">
@@ -12156,19 +12156,19 @@
         <v>26</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J305" s="0">
-        <v>1198.5989</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="306">
@@ -12182,25 +12182,25 @@
         <v>501</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J306" s="0">
-        <v>1016.6576</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="307">
@@ -12220,19 +12220,19 @@
         <v>25</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G307" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J307" s="0">
-        <v>10363.415999999999</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="308">
@@ -12249,22 +12249,22 @@
         <v>677</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G308" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J308" s="0">
-        <v>8731.0702999999994</v>
+        <v>848.39120000000003</v>
       </c>
     </row>
     <row r="309">
@@ -12284,19 +12284,19 @@
         <v>26</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J309" s="0">
-        <v>848.39120000000003</v>
+        <v>740.85990000000004</v>
       </c>
     </row>
     <row r="310">
@@ -12313,22 +12313,22 @@
         <v>677</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G310" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J310" s="0">
-        <v>740.85990000000004</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="311">
@@ -12348,19 +12348,19 @@
         <v>27</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>547</v>
+        <v>64</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J311" s="0">
-        <v>509.65910000000002</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="312">
@@ -12380,19 +12380,19 @@
         <v>27</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>64</v>
+        <v>548</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J312" s="0">
-        <v>497.6062</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="313">
@@ -12412,19 +12412,19 @@
         <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J313" s="0">
-        <v>473.81920000000002</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="314">
@@ -12444,19 +12444,19 @@
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J314" s="0">
-        <v>386.12639999999999</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="315">
@@ -12476,19 +12476,19 @@
         <v>27</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J315" s="0">
-        <v>381.40570000000002</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="316">
@@ -12508,19 +12508,19 @@
         <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J316" s="0">
-        <v>371.59660000000002</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="317">
@@ -12540,19 +12540,19 @@
         <v>27</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J317" s="0">
-        <v>364.02569999999997</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="318">
@@ -12566,25 +12566,25 @@
         <v>501</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J318" s="0">
-        <v>331.7552</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="319">
@@ -12604,19 +12604,19 @@
         <v>25</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J319" s="0">
-        <v>1621.762</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="320">
@@ -12633,22 +12633,22 @@
         <v>678</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J320" s="0">
-        <v>1023.5883</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="321">
@@ -12668,19 +12668,19 @@
         <v>26</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J321" s="0">
-        <v>634.67409999999995</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="322">
@@ -12697,22 +12697,22 @@
         <v>678</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J322" s="0">
-        <v>589.45230000000004</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="323">
@@ -12732,19 +12732,19 @@
         <v>27</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J323" s="0">
-        <v>441.32260000000002</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="324">
@@ -12764,19 +12764,19 @@
         <v>27</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J324" s="0">
-        <v>406.00639999999999</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="325">
@@ -12796,19 +12796,19 @@
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J325" s="0">
-        <v>404.98939999999999</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="326">
@@ -12828,19 +12828,19 @@
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J326" s="0">
-        <v>356.87450000000001</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="327">
@@ -12860,19 +12860,19 @@
         <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J327" s="0">
-        <v>326.86750000000001</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="328">
@@ -12892,19 +12892,19 @@
         <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J328" s="0">
-        <v>313.15320000000003</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="329">
@@ -12924,19 +12924,19 @@
         <v>27</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J329" s="0">
-        <v>302.25330000000002</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="330">
@@ -12947,28 +12947,28 @@
         <v>4</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>565</v>
+        <v>129</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>778</v>
+        <v>452</v>
       </c>
       <c r="J330" s="0">
-        <v>241.7327</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="331">
@@ -12988,19 +12988,19 @@
         <v>25</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J331" s="0">
-        <v>8389.2909999999993</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="332">
@@ -13017,22 +13017,22 @@
         <v>18</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J332" s="0">
-        <v>8068.0429999999997</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="333">
@@ -13052,19 +13052,19 @@
         <v>26</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J333" s="0">
-        <v>1304.9119000000001</v>
+        <v>981.88890000000004</v>
       </c>
     </row>
     <row r="334">
@@ -13081,22 +13081,22 @@
         <v>18</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G334" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J334" s="0">
-        <v>981.88890000000004</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="335">
@@ -13116,19 +13116,19 @@
         <v>27</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J335" s="0">
-        <v>528.16520000000003</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="336">
@@ -13148,19 +13148,19 @@
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J336" s="0">
-        <v>464.43889999999999</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="337">
@@ -13180,19 +13180,19 @@
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J337" s="0">
-        <v>449.87619999999998</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="338">
@@ -13212,19 +13212,19 @@
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J338" s="0">
-        <v>447.66699999999997</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="339">
@@ -13244,19 +13244,19 @@
         <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J339" s="0">
-        <v>391.69869999999997</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="340">
@@ -13276,19 +13276,19 @@
         <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J340" s="0">
-        <v>372.4153</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="341">
@@ -13308,19 +13308,19 @@
         <v>27</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J341" s="0">
-        <v>366.97289999999998</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="342">
@@ -13334,25 +13334,25 @@
         <v>8</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J342" s="0">
-        <v>329.11259999999999</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="343">
@@ -13372,19 +13372,19 @@
         <v>25</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G343" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J343" s="0">
-        <v>9741.5614999999998</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="344">
@@ -13401,22 +13401,22 @@
         <v>19</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G344" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J344" s="0">
-        <v>8198.8974999999991</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="345">
@@ -13436,19 +13436,19 @@
         <v>26</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J345" s="0">
-        <v>1259.1116</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="346">
@@ -13465,22 +13465,22 @@
         <v>19</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G346" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J346" s="0">
-        <v>964.0145</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="347">
@@ -13500,19 +13500,19 @@
         <v>27</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J347" s="0">
-        <v>539.45429999999999</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="348">
@@ -13532,19 +13532,19 @@
         <v>27</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J348" s="0">
-        <v>485.64830000000001</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="349">
@@ -13564,19 +13564,19 @@
         <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J349" s="0">
-        <v>457.39609999999999</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="350">
@@ -13596,19 +13596,19 @@
         <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J350" s="0">
-        <v>454.66460000000001</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="351">
@@ -13628,19 +13628,19 @@
         <v>27</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J351" s="0">
-        <v>368.51979999999998</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="352">
@@ -13660,19 +13660,19 @@
         <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J352" s="0">
-        <v>342.74220000000003</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="353">
@@ -13692,19 +13692,19 @@
         <v>27</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J353" s="0">
-        <v>302.46800000000002</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="354">
@@ -13715,28 +13715,28 @@
         <v>4</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J354" s="0">
-        <v>300.47250000000003</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="355">
@@ -13756,19 +13756,19 @@
         <v>25</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G355" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J355" s="0">
-        <v>10892.9414</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="356">
@@ -13785,22 +13785,22 @@
         <v>20</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G356" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J356" s="0">
-        <v>5918.6806999999999</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="357">
@@ -13817,7 +13817,7 @@
         <v>20</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F357" s="0" t="s">
         <v>29</v>
@@ -13826,13 +13826,13 @@
         <v>43</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J357" s="0">
-        <v>829.46619999999996</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="358">
@@ -13849,22 +13849,22 @@
         <v>20</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J358" s="0">
-        <v>726.14110000000005</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="359">
@@ -13884,19 +13884,19 @@
         <v>27</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J359" s="0">
-        <v>498.3132</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="360">
@@ -13916,19 +13916,19 @@
         <v>27</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J360" s="0">
-        <v>487.10520000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="361">
@@ -13948,19 +13948,19 @@
         <v>27</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G361" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J361" s="0">
-        <v>485.66770000000002</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="362">
@@ -13980,19 +13980,19 @@
         <v>27</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G362" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J362" s="0">
-        <v>478.11529999999999</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="363">
@@ -14012,19 +14012,19 @@
         <v>27</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J363" s="0">
-        <v>375.48970000000003</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="364">
@@ -14044,19 +14044,19 @@
         <v>27</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G364" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J364" s="0">
-        <v>359.0838</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="365">
@@ -14070,25 +14070,25 @@
         <v>9</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G365" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J365" s="0">
-        <v>338.9837</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="366">
@@ -14102,25 +14102,25 @@
         <v>9</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J366" s="0">
-        <v>293.55579999999998</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="367">
@@ -14137,7 +14137,7 @@
         <v>21</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>29</v>
@@ -14146,13 +14146,13 @@
         <v>43</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J367" s="0">
-        <v>9826.1103999999996</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="368">
@@ -14169,7 +14169,7 @@
         <v>21</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F368" s="0" t="s">
         <v>30</v>
@@ -14178,13 +14178,13 @@
         <v>44</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J368" s="0">
-        <v>7957.9004000000004</v>
+        <v>893.57759999999996</v>
       </c>
     </row>
     <row r="369">
@@ -14201,7 +14201,7 @@
         <v>21</v>
       </c>
       <c r="E369" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F369" s="0" t="s">
         <v>29</v>
@@ -14210,13 +14210,13 @@
         <v>43</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J369" s="0">
-        <v>1958.7829999999999</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="370">
@@ -14233,22 +14233,22 @@
         <v>21</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G370" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J370" s="0">
-        <v>893.57759999999996</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="371">
@@ -14268,19 +14268,19 @@
         <v>27</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J371" s="0">
-        <v>574.80640000000005</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="372">
@@ -14300,19 +14300,19 @@
         <v>27</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J372" s="0">
-        <v>532.89999999999998</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="373">
@@ -14332,19 +14332,19 @@
         <v>27</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G373" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J373" s="0">
-        <v>470.99040000000002</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="374">
@@ -14364,19 +14364,19 @@
         <v>27</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J374" s="0">
-        <v>428.05349999999999</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="375">
@@ -14396,19 +14396,19 @@
         <v>27</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J375" s="0">
-        <v>370.83409999999998</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="376">
@@ -14428,19 +14428,19 @@
         <v>27</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G376" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J376" s="0">
-        <v>361.65289999999999</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="377">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37370" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44140" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44140" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="47516" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -7938,13 +7938,13 @@
         <v>43</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J173" s="0">
-        <v>13088.609399999999</v>
+        <v>9104.8721000000005</v>
       </c>
     </row>
     <row r="174">
@@ -7961,22 +7961,22 @@
         <v>11</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J174" s="0">
-        <v>9104.8721000000005</v>
+        <v>1438.8326</v>
       </c>
     </row>
     <row r="175">
@@ -7996,19 +7996,19 @@
         <v>26</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J175" s="0">
-        <v>1438.8326</v>
+        <v>1210.5242000000001</v>
       </c>
     </row>
     <row r="176">
@@ -8025,22 +8025,22 @@
         <v>11</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J176" s="0">
-        <v>1210.5242000000001</v>
+        <v>542.07240000000002</v>
       </c>
     </row>
     <row r="177">
@@ -8060,19 +8060,19 @@
         <v>27</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J177" s="0">
-        <v>542.07240000000002</v>
+        <v>528.39120000000003</v>
       </c>
     </row>
     <row r="178">
@@ -8092,19 +8092,19 @@
         <v>27</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J178" s="0">
-        <v>528.39120000000003</v>
+        <v>519.83349999999996</v>
       </c>
     </row>
     <row r="179">
@@ -8124,19 +8124,19 @@
         <v>27</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J179" s="0">
-        <v>519.83349999999996</v>
+        <v>465.38400000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8156,19 +8156,19 @@
         <v>27</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J180" s="0">
-        <v>465.38400000000001</v>
+        <v>387.42579999999998</v>
       </c>
     </row>
     <row r="181">
@@ -8188,19 +8188,19 @@
         <v>27</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J181" s="0">
-        <v>387.42579999999998</v>
+        <v>376.01639999999998</v>
       </c>
     </row>
     <row r="182">
@@ -8220,19 +8220,19 @@
         <v>27</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J182" s="0">
-        <v>376.01639999999998</v>
+        <v>367.9187</v>
       </c>
     </row>
     <row r="183">
@@ -8252,19 +8252,19 @@
         <v>27</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J183" s="0">
-        <v>367.9187</v>
+        <v>345.6712</v>
       </c>
     </row>
     <row r="184">
@@ -8278,25 +8278,25 @@
         <v>6</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J184" s="0">
-        <v>345.6712</v>
+        <v>11026.299800000001</v>
       </c>
     </row>
     <row r="185">
@@ -8316,19 +8316,19 @@
         <v>25</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J185" s="0">
-        <v>11026.299800000001</v>
+        <v>8759.9452999999994</v>
       </c>
     </row>
     <row r="186">
@@ -8345,22 +8345,22 @@
         <v>12</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J186" s="0">
-        <v>8759.9452999999994</v>
+        <v>1159.0046</v>
       </c>
     </row>
     <row r="187">
@@ -8380,19 +8380,19 @@
         <v>26</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J187" s="0">
-        <v>1159.0046</v>
+        <v>1153.3887</v>
       </c>
     </row>
     <row r="188">
@@ -8409,22 +8409,22 @@
         <v>12</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J188" s="0">
-        <v>1153.3887</v>
+        <v>531.56039999999996</v>
       </c>
     </row>
     <row r="189">
@@ -8444,19 +8444,19 @@
         <v>27</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J189" s="0">
-        <v>531.56039999999996</v>
+        <v>513.93790000000001</v>
       </c>
     </row>
     <row r="190">
@@ -8476,19 +8476,19 @@
         <v>27</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J190" s="0">
-        <v>513.93790000000001</v>
+        <v>499.63580000000002</v>
       </c>
     </row>
     <row r="191">
@@ -8508,19 +8508,19 @@
         <v>27</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J191" s="0">
-        <v>499.63580000000002</v>
+        <v>475.38760000000002</v>
       </c>
     </row>
     <row r="192">
@@ -8540,19 +8540,19 @@
         <v>27</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J192" s="0">
-        <v>475.38760000000002</v>
+        <v>357.59019999999998</v>
       </c>
     </row>
     <row r="193">
@@ -8572,19 +8572,19 @@
         <v>27</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J193" s="0">
-        <v>357.59019999999998</v>
+        <v>346.22629999999998</v>
       </c>
     </row>
     <row r="194">
@@ -8604,19 +8604,19 @@
         <v>27</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J194" s="0">
-        <v>346.22629999999998</v>
+        <v>331.46199999999999</v>
       </c>
     </row>
     <row r="195">
@@ -8636,19 +8636,19 @@
         <v>27</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J195" s="0">
-        <v>331.46199999999999</v>
+        <v>308.1046</v>
       </c>
     </row>
     <row r="196">
@@ -8662,25 +8662,25 @@
         <v>6</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J196" s="0">
-        <v>308.1046</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="197">
@@ -8700,19 +8700,19 @@
         <v>26</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J197" s="0">
-        <v>901.9991</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="198">
@@ -8729,22 +8729,22 @@
         <v>13</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J198" s="0">
-        <v>893.56960000000004</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="199">
@@ -8764,19 +8764,19 @@
         <v>27</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J199" s="0">
-        <v>549.74869999999999</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="200">
@@ -8796,19 +8796,19 @@
         <v>27</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J200" s="0">
-        <v>530.14729999999997</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="201">
@@ -8828,19 +8828,19 @@
         <v>27</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J201" s="0">
-        <v>489.4966</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="202">
@@ -8860,19 +8860,19 @@
         <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J202" s="0">
-        <v>482.49549999999999</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="203">
@@ -8892,19 +8892,19 @@
         <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J203" s="0">
-        <v>378.9196</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="204">
@@ -8924,19 +8924,19 @@
         <v>27</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J204" s="0">
-        <v>366.15300000000002</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="205">
@@ -8956,19 +8956,19 @@
         <v>27</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J205" s="0">
-        <v>340.57749999999999</v>
+        <v>329.09449999999998</v>
       </c>
     </row>
     <row r="206">
@@ -8982,25 +8982,25 @@
         <v>6</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J206" s="0">
-        <v>329.09449999999998</v>
+        <v>4307.7025999999996</v>
       </c>
     </row>
     <row r="207">
@@ -9020,19 +9020,19 @@
         <v>25</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J207" s="0">
-        <v>4307.7025999999996</v>
+        <v>1837.0477000000001</v>
       </c>
     </row>
     <row r="208">
@@ -9049,22 +9049,22 @@
         <v>22</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J208" s="0">
-        <v>1837.0477000000001</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="209">
@@ -9084,19 +9084,19 @@
         <v>26</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J209" s="0">
-        <v>616.08360000000005</v>
+        <v>552.42719999999997</v>
       </c>
     </row>
     <row r="210">
@@ -9113,22 +9113,22 @@
         <v>22</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J210" s="0">
-        <v>552.42719999999997</v>
+        <v>399.44740000000002</v>
       </c>
     </row>
     <row r="211">
@@ -9148,19 +9148,19 @@
         <v>27</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J211" s="0">
-        <v>399.44740000000002</v>
+        <v>377.98289999999997</v>
       </c>
     </row>
     <row r="212">
@@ -9180,19 +9180,19 @@
         <v>27</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J212" s="0">
-        <v>377.98289999999997</v>
+        <v>376.71690000000001</v>
       </c>
     </row>
     <row r="213">
@@ -9212,19 +9212,19 @@
         <v>27</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J213" s="0">
-        <v>376.71690000000001</v>
+        <v>375.52019999999999</v>
       </c>
     </row>
     <row r="214">
@@ -9244,19 +9244,19 @@
         <v>27</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J214" s="0">
-        <v>375.52019999999999</v>
+        <v>370.8648</v>
       </c>
     </row>
     <row r="215">
@@ -9276,19 +9276,19 @@
         <v>27</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J215" s="0">
-        <v>370.8648</v>
+        <v>342.89479999999998</v>
       </c>
     </row>
     <row r="216">
@@ -9308,19 +9308,19 @@
         <v>27</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J216" s="0">
-        <v>342.89479999999998</v>
+        <v>307.26029999999997</v>
       </c>
     </row>
     <row r="217">
@@ -9340,19 +9340,19 @@
         <v>27</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J217" s="0">
-        <v>307.26029999999997</v>
+        <v>261.58179999999999</v>
       </c>
     </row>
     <row r="218">
@@ -9363,28 +9363,28 @@
         <v>4</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J218" s="0">
-        <v>261.58179999999999</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="219">
@@ -9404,19 +9404,19 @@
         <v>25</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J219" s="0">
-        <v>10466.208000000001</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="220">
@@ -9433,22 +9433,22 @@
         <v>14</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J220" s="0">
-        <v>7328.0029000000004</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="221">
@@ -9468,19 +9468,19 @@
         <v>26</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J221" s="0">
-        <v>1015.5606</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="222">
@@ -9500,19 +9500,19 @@
         <v>26</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J222" s="0">
-        <v>908.67830000000004</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="223">
@@ -9532,19 +9532,19 @@
         <v>26</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J223" s="0">
-        <v>520.97770000000003</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="224">
@@ -9564,19 +9564,19 @@
         <v>26</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J224" s="0">
-        <v>488.97149999999999</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="225">
@@ -9596,19 +9596,19 @@
         <v>26</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J225" s="0">
-        <v>484.75029999999998</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="226">
@@ -9628,19 +9628,19 @@
         <v>26</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J226" s="0">
-        <v>438.36930000000001</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="227">
@@ -9660,19 +9660,19 @@
         <v>26</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J227" s="0">
-        <v>369.10219999999998</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="228">
@@ -9692,19 +9692,19 @@
         <v>26</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J228" s="0">
-        <v>342.30680000000001</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="229">
@@ -9724,19 +9724,19 @@
         <v>26</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J229" s="0">
-        <v>280.75409999999999</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="230">
@@ -9750,25 +9750,25 @@
         <v>7</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J230" s="0">
-        <v>270.84679999999997</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="231">
@@ -9788,19 +9788,19 @@
         <v>25</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J231" s="0">
-        <v>8934.2567999999992</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="232">
@@ -9817,22 +9817,22 @@
         <v>15</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J232" s="0">
-        <v>7192.2339000000002</v>
+        <v>1017.6188</v>
       </c>
     </row>
     <row r="233">
@@ -9852,19 +9852,19 @@
         <v>26</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J233" s="0">
-        <v>1017.6188</v>
+        <v>892.98720000000003</v>
       </c>
     </row>
     <row r="234">
@@ -9881,22 +9881,22 @@
         <v>15</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J234" s="0">
-        <v>892.98720000000003</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="235">
@@ -9916,19 +9916,19 @@
         <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J235" s="0">
-        <v>489.01900000000001</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="236">
@@ -9948,19 +9948,19 @@
         <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J236" s="0">
-        <v>486.78719999999999</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="237">
@@ -9980,19 +9980,19 @@
         <v>27</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J237" s="0">
-        <v>478.59969999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="238">
@@ -10012,19 +10012,19 @@
         <v>27</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J238" s="0">
-        <v>456.38220000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="239">
@@ -10044,19 +10044,19 @@
         <v>27</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J239" s="0">
-        <v>361.197</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="240">
@@ -10076,19 +10076,19 @@
         <v>27</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J240" s="0">
-        <v>350.10750000000002</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="241">
@@ -10102,25 +10102,25 @@
         <v>7</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J241" s="0">
-        <v>332.8802</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="242">
@@ -10140,19 +10140,19 @@
         <v>25</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J242" s="0">
-        <v>9850.5967000000001</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="243">
@@ -10169,22 +10169,22 @@
         <v>16</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J243" s="0">
-        <v>8299.1229999999996</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="244">
@@ -10204,19 +10204,19 @@
         <v>26</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J244" s="0">
-        <v>1061.2550000000001</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="245">
@@ -10233,22 +10233,22 @@
         <v>16</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J245" s="0">
-        <v>863.95190000000002</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="246">
@@ -10268,19 +10268,19 @@
         <v>27</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J246" s="0">
-        <v>537.24440000000004</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="247">
@@ -10300,19 +10300,19 @@
         <v>27</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J247" s="0">
-        <v>512.39139999999998</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="248">
@@ -10332,19 +10332,19 @@
         <v>27</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J248" s="0">
-        <v>461.678</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="249">
@@ -10364,19 +10364,19 @@
         <v>27</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J249" s="0">
-        <v>446.13510000000002</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="250">
@@ -10396,19 +10396,19 @@
         <v>27</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J250" s="0">
-        <v>416.1148</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="251">
@@ -10428,19 +10428,19 @@
         <v>27</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J251" s="0">
-        <v>385.80329999999998</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="252">
@@ -10460,19 +10460,19 @@
         <v>27</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J252" s="0">
-        <v>376.43869999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="253">
@@ -10486,25 +10486,25 @@
         <v>7</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J253" s="0">
-        <v>340.64490000000001</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="254">
@@ -10524,19 +10524,19 @@
         <v>25</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J254" s="0">
-        <v>9114.7715000000008</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="255">
@@ -10553,22 +10553,22 @@
         <v>17</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J255" s="0">
-        <v>7656.0316999999996</v>
+        <v>1088.5953</v>
       </c>
     </row>
     <row r="256">
@@ -10588,19 +10588,19 @@
         <v>26</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J256" s="0">
-        <v>1088.5953</v>
+        <v>1085.6431</v>
       </c>
     </row>
     <row r="257">
@@ -10620,19 +10620,19 @@
         <v>26</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J257" s="0">
-        <v>1085.6431</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="258">
@@ -10652,19 +10652,19 @@
         <v>26</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J258" s="0">
-        <v>542.5788</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="259">
@@ -10684,19 +10684,19 @@
         <v>26</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J259" s="0">
-        <v>534.76580000000001</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="260">
@@ -10716,19 +10716,19 @@
         <v>26</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J260" s="0">
-        <v>484.83710000000002</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="261">
@@ -10748,19 +10748,19 @@
         <v>26</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J261" s="0">
-        <v>468.87529999999998</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="262">
@@ -10780,19 +10780,19 @@
         <v>26</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J262" s="0">
-        <v>398.83769999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="263">
@@ -10812,19 +10812,19 @@
         <v>26</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J263" s="0">
-        <v>337.36939999999999</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="264">
@@ -10844,19 +10844,19 @@
         <v>26</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J264" s="0">
-        <v>311.84429999999998</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="265">
@@ -10870,25 +10870,25 @@
         <v>7</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J265" s="0">
-        <v>245.285</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="266">
@@ -10908,19 +10908,19 @@
         <v>25</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J266" s="0">
-        <v>2887.6174000000001</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="267">
@@ -10937,22 +10937,22 @@
         <v>23</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J267" s="0">
-        <v>2872.1073999999999</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="268">
@@ -10972,19 +10972,19 @@
         <v>26</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J268" s="0">
-        <v>975.3777</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="269">
@@ -11001,22 +11001,22 @@
         <v>23</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J269" s="0">
-        <v>616.08360000000005</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="270">
@@ -11036,19 +11036,19 @@
         <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J270" s="0">
-        <v>465.53719999999999</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="271">
@@ -11068,19 +11068,19 @@
         <v>27</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J271" s="0">
-        <v>436.18400000000003</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="272">
@@ -11100,19 +11100,19 @@
         <v>27</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J272" s="0">
-        <v>415.78980000000001</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="273">
@@ -11132,19 +11132,19 @@
         <v>27</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J273" s="0">
-        <v>391.16430000000003</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="274">
@@ -11164,19 +11164,19 @@
         <v>27</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J274" s="0">
-        <v>362.91770000000002</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="275">
@@ -11196,19 +11196,19 @@
         <v>27</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J275" s="0">
-        <v>315.58260000000001</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11228,19 +11228,19 @@
         <v>27</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J276" s="0">
-        <v>315.33229999999998</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="277">
@@ -11251,28 +11251,28 @@
         <v>4</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>207</v>
+        <v>507</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>451</v>
+        <v>727</v>
       </c>
       <c r="J277" s="0">
-        <v>254.02879999999999</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="278">
@@ -11292,19 +11292,19 @@
         <v>25</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J278" s="0">
-        <v>10897.75</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="279">
@@ -11321,22 +11321,22 @@
         <v>674</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J279" s="0">
-        <v>5963.8306000000002</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="280">
@@ -11356,19 +11356,19 @@
         <v>26</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J280" s="0">
-        <v>1364.115</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="281">
@@ -11385,22 +11385,22 @@
         <v>674</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J281" s="0">
-        <v>1002.6719000000001</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="282">
@@ -11420,19 +11420,19 @@
         <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J282" s="0">
-        <v>557.97879999999998</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="283">
@@ -11452,19 +11452,19 @@
         <v>27</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J283" s="0">
-        <v>511.4341</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="284">
@@ -11484,19 +11484,19 @@
         <v>27</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J284" s="0">
-        <v>485.53699999999998</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="285">
@@ -11516,19 +11516,19 @@
         <v>27</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J285" s="0">
-        <v>456.29579999999999</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="286">
@@ -11548,19 +11548,19 @@
         <v>27</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J286" s="0">
-        <v>403.62130000000002</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="287">
@@ -11580,19 +11580,19 @@
         <v>27</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J287" s="0">
-        <v>384.92849999999999</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="288">
@@ -11612,19 +11612,19 @@
         <v>27</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J288" s="0">
-        <v>345.9332</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="289">
@@ -11638,25 +11638,25 @@
         <v>501</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J289" s="0">
-        <v>329.33870000000002</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="290">
@@ -11676,19 +11676,19 @@
         <v>25</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J290" s="0">
-        <v>9494.3554999999997</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="291">
@@ -11705,22 +11705,22 @@
         <v>675</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J291" s="0">
-        <v>6959.3242</v>
+        <v>989.73109999999997</v>
       </c>
     </row>
     <row r="292">
@@ -11740,19 +11740,19 @@
         <v>26</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J292" s="0">
-        <v>989.73109999999997</v>
+        <v>709.46839999999998</v>
       </c>
     </row>
     <row r="293">
@@ -11769,22 +11769,22 @@
         <v>675</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J293" s="0">
-        <v>709.46839999999998</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="294">
@@ -11804,19 +11804,19 @@
         <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J294" s="0">
-        <v>528.32619999999997</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="295">
@@ -11836,19 +11836,19 @@
         <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J295" s="0">
-        <v>502.16129999999998</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="296">
@@ -11868,19 +11868,19 @@
         <v>27</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J296" s="0">
-        <v>468.14839999999998</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="297">
@@ -11900,19 +11900,19 @@
         <v>27</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J297" s="0">
-        <v>413.35890000000001</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="298">
@@ -11932,19 +11932,19 @@
         <v>27</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J298" s="0">
-        <v>410.47199999999998</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="299">
@@ -11964,19 +11964,19 @@
         <v>27</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J299" s="0">
-        <v>371.8809</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="300">
@@ -11996,19 +11996,19 @@
         <v>27</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J300" s="0">
-        <v>347.0478</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="301">
@@ -12022,25 +12022,25 @@
         <v>501</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J301" s="0">
-        <v>302.97559999999999</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="302">
@@ -12060,19 +12060,19 @@
         <v>25</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J302" s="0">
-        <v>8923.2001999999993</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="303">
@@ -12089,22 +12089,22 @@
         <v>676</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J303" s="0">
-        <v>7434.9364999999998</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="304">
@@ -12124,19 +12124,19 @@
         <v>26</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J304" s="0">
-        <v>1198.5989</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="305">
@@ -12150,25 +12150,25 @@
         <v>501</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J305" s="0">
-        <v>1016.6576</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="306">
@@ -12188,19 +12188,19 @@
         <v>25</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J306" s="0">
-        <v>10363.415999999999</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="307">
@@ -12217,22 +12217,22 @@
         <v>677</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G307" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J307" s="0">
-        <v>8731.0702999999994</v>
+        <v>848.39120000000003</v>
       </c>
     </row>
     <row r="308">
@@ -12252,19 +12252,19 @@
         <v>26</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G308" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J308" s="0">
-        <v>848.39120000000003</v>
+        <v>740.85990000000004</v>
       </c>
     </row>
     <row r="309">
@@ -12281,22 +12281,22 @@
         <v>677</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J309" s="0">
-        <v>740.85990000000004</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="310">
@@ -12316,19 +12316,19 @@
         <v>27</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>547</v>
+        <v>64</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J310" s="0">
-        <v>509.65910000000002</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="311">
@@ -12348,19 +12348,19 @@
         <v>27</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>64</v>
+        <v>548</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J311" s="0">
-        <v>497.6062</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="312">
@@ -12380,19 +12380,19 @@
         <v>27</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J312" s="0">
-        <v>473.81920000000002</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="313">
@@ -12412,19 +12412,19 @@
         <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J313" s="0">
-        <v>386.12639999999999</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="314">
@@ -12444,19 +12444,19 @@
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J314" s="0">
-        <v>381.40570000000002</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="315">
@@ -12476,19 +12476,19 @@
         <v>27</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J315" s="0">
-        <v>371.59660000000002</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="316">
@@ -12508,19 +12508,19 @@
         <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J316" s="0">
-        <v>364.02569999999997</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="317">
@@ -12534,25 +12534,25 @@
         <v>501</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J317" s="0">
-        <v>331.7552</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="318">
@@ -12572,19 +12572,19 @@
         <v>25</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J318" s="0">
-        <v>1621.762</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="319">
@@ -12601,22 +12601,22 @@
         <v>678</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J319" s="0">
-        <v>1023.5883</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="320">
@@ -12636,19 +12636,19 @@
         <v>26</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J320" s="0">
-        <v>634.67409999999995</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="321">
@@ -12665,22 +12665,22 @@
         <v>678</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J321" s="0">
-        <v>589.45230000000004</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="322">
@@ -12700,19 +12700,19 @@
         <v>27</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J322" s="0">
-        <v>441.32260000000002</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="323">
@@ -12732,19 +12732,19 @@
         <v>27</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J323" s="0">
-        <v>406.00639999999999</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="324">
@@ -12764,19 +12764,19 @@
         <v>27</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J324" s="0">
-        <v>404.98939999999999</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="325">
@@ -12796,19 +12796,19 @@
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J325" s="0">
-        <v>356.87450000000001</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="326">
@@ -12828,19 +12828,19 @@
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J326" s="0">
-        <v>326.86750000000001</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="327">
@@ -12860,19 +12860,19 @@
         <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J327" s="0">
-        <v>313.15320000000003</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="328">
@@ -12892,19 +12892,19 @@
         <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J328" s="0">
-        <v>302.25330000000002</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="329">
@@ -12915,28 +12915,28 @@
         <v>4</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>565</v>
+        <v>129</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>778</v>
+        <v>452</v>
       </c>
       <c r="J329" s="0">
-        <v>241.7327</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="330">
@@ -12956,19 +12956,19 @@
         <v>25</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J330" s="0">
-        <v>8389.2909999999993</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="331">
@@ -12985,22 +12985,22 @@
         <v>18</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J331" s="0">
-        <v>8068.0429999999997</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="332">
@@ -13020,19 +13020,19 @@
         <v>26</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J332" s="0">
-        <v>1304.9119000000001</v>
+        <v>981.88890000000004</v>
       </c>
     </row>
     <row r="333">
@@ -13049,22 +13049,22 @@
         <v>18</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J333" s="0">
-        <v>981.88890000000004</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="334">
@@ -13084,19 +13084,19 @@
         <v>27</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J334" s="0">
-        <v>528.16520000000003</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="335">
@@ -13116,19 +13116,19 @@
         <v>27</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J335" s="0">
-        <v>464.43889999999999</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="336">
@@ -13148,19 +13148,19 @@
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J336" s="0">
-        <v>449.87619999999998</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="337">
@@ -13180,19 +13180,19 @@
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J337" s="0">
-        <v>447.66699999999997</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="338">
@@ -13212,19 +13212,19 @@
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J338" s="0">
-        <v>391.69869999999997</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="339">
@@ -13244,19 +13244,19 @@
         <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J339" s="0">
-        <v>372.4153</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="340">
@@ -13276,19 +13276,19 @@
         <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J340" s="0">
-        <v>366.97289999999998</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="341">
@@ -13302,25 +13302,25 @@
         <v>8</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J341" s="0">
-        <v>329.11259999999999</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="342">
@@ -13340,19 +13340,19 @@
         <v>25</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J342" s="0">
-        <v>9741.5614999999998</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="343">
@@ -13369,22 +13369,22 @@
         <v>19</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G343" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J343" s="0">
-        <v>8198.8974999999991</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="344">
@@ -13404,19 +13404,19 @@
         <v>26</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G344" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J344" s="0">
-        <v>1259.1116</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="345">
@@ -13433,22 +13433,22 @@
         <v>19</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J345" s="0">
-        <v>964.0145</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="346">
@@ -13468,19 +13468,19 @@
         <v>27</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J346" s="0">
-        <v>539.45429999999999</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="347">
@@ -13500,19 +13500,19 @@
         <v>27</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J347" s="0">
-        <v>485.64830000000001</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="348">
@@ -13532,19 +13532,19 @@
         <v>27</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J348" s="0">
-        <v>457.39609999999999</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="349">
@@ -13564,19 +13564,19 @@
         <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J349" s="0">
-        <v>454.66460000000001</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="350">
@@ -13596,19 +13596,19 @@
         <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J350" s="0">
-        <v>368.51979999999998</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="351">
@@ -13628,19 +13628,19 @@
         <v>27</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J351" s="0">
-        <v>342.74220000000003</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="352">
@@ -13660,19 +13660,19 @@
         <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J352" s="0">
-        <v>302.46800000000002</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="353">
@@ -13683,28 +13683,28 @@
         <v>4</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J353" s="0">
-        <v>300.47250000000003</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="354">
@@ -13724,19 +13724,19 @@
         <v>25</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J354" s="0">
-        <v>10892.9414</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="355">
@@ -13753,22 +13753,22 @@
         <v>20</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G355" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J355" s="0">
-        <v>5918.6806999999999</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="356">
@@ -13785,7 +13785,7 @@
         <v>20</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F356" s="0" t="s">
         <v>29</v>
@@ -13794,13 +13794,13 @@
         <v>43</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J356" s="0">
-        <v>726.14110000000005</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="357">
@@ -13820,19 +13820,19 @@
         <v>27</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J357" s="0">
-        <v>498.3132</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="358">
@@ -13852,19 +13852,19 @@
         <v>27</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J358" s="0">
-        <v>487.10520000000002</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="359">
@@ -13884,19 +13884,19 @@
         <v>27</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J359" s="0">
-        <v>485.66770000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13916,19 +13916,19 @@
         <v>27</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J360" s="0">
-        <v>478.11529999999999</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="361">
@@ -13948,19 +13948,19 @@
         <v>27</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J361" s="0">
-        <v>375.48970000000003</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="362">
@@ -13980,19 +13980,19 @@
         <v>27</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G362" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J362" s="0">
-        <v>359.0838</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="363">
@@ -14012,19 +14012,19 @@
         <v>27</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J363" s="0">
-        <v>338.9837</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="364">
@@ -14038,25 +14038,25 @@
         <v>9</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J364" s="0">
-        <v>293.55579999999998</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="365">
@@ -14076,19 +14076,19 @@
         <v>25</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G365" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J365" s="0">
-        <v>9826.1103999999996</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="366">
@@ -14105,22 +14105,22 @@
         <v>21</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J366" s="0">
-        <v>7957.9004000000004</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="367">
@@ -14140,19 +14140,19 @@
         <v>26</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G367" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J367" s="0">
-        <v>1958.7829999999999</v>
+        <v>893.57759999999996</v>
       </c>
     </row>
     <row r="368">
@@ -14169,22 +14169,22 @@
         <v>21</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G368" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J368" s="0">
-        <v>893.57759999999996</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="369">
@@ -14204,19 +14204,19 @@
         <v>27</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J369" s="0">
-        <v>574.80640000000005</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="370">
@@ -14236,19 +14236,19 @@
         <v>27</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J370" s="0">
-        <v>532.89999999999998</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="371">
@@ -14268,19 +14268,19 @@
         <v>27</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J371" s="0">
-        <v>470.99040000000002</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="372">
@@ -14300,19 +14300,19 @@
         <v>27</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G372" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J372" s="0">
-        <v>428.05349999999999</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="373">
@@ -14332,19 +14332,19 @@
         <v>27</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J373" s="0">
-        <v>370.83409999999998</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="374">
@@ -14364,19 +14364,19 @@
         <v>27</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G374" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J374" s="0">
-        <v>361.65289999999999</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="375">
@@ -14396,19 +14396,19 @@
         <v>27</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J375" s="0">
-        <v>328.18830000000003</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="376">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="47516" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="50784" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -6457,7 +6457,7 @@
         <v>18</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>29</v>
@@ -6466,13 +6466,13 @@
         <v>43</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J127" s="0">
-        <v>537.93820000000005</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="128">
@@ -6489,22 +6489,22 @@
         <v>18</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J128" s="0">
-        <v>473.31950000000001</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="129">
@@ -6524,19 +6524,19 @@
         <v>27</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J129" s="0">
-        <v>528.16520000000003</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="130">
@@ -6556,19 +6556,19 @@
         <v>27</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J130" s="0">
-        <v>464.43889999999999</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="131">
@@ -6588,19 +6588,19 @@
         <v>27</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J131" s="0">
-        <v>449.87619999999998</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="132">
@@ -6620,19 +6620,19 @@
         <v>27</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J132" s="0">
-        <v>447.66699999999997</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="133">
@@ -6652,19 +6652,19 @@
         <v>27</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J133" s="0">
-        <v>391.69869999999997</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="134">
@@ -6684,19 +6684,19 @@
         <v>27</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J134" s="0">
-        <v>372.4153</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="135">
@@ -6710,25 +6710,25 @@
         <v>8</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J135" s="0">
-        <v>366.97289999999998</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="136">
@@ -6742,25 +6742,25 @@
         <v>8</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J136" s="0">
-        <v>329.11259999999999</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="137">
@@ -6777,7 +6777,7 @@
         <v>19</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>29</v>
@@ -6786,13 +6786,13 @@
         <v>43</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J137" s="0">
-        <v>9741.5614999999998</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="138">
@@ -6809,7 +6809,7 @@
         <v>19</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F138" s="0" t="s">
         <v>30</v>
@@ -6818,13 +6818,13 @@
         <v>44</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J138" s="0">
-        <v>8198.8974999999991</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="139">
@@ -6841,7 +6841,7 @@
         <v>19</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F139" s="0" t="s">
         <v>29</v>
@@ -6850,13 +6850,13 @@
         <v>43</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J139" s="0">
-        <v>1259.1116</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="140">
@@ -6873,22 +6873,22 @@
         <v>19</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J140" s="0">
-        <v>863.95190000000002</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="141">
@@ -6908,19 +6908,19 @@
         <v>27</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J141" s="0">
-        <v>539.45429999999999</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="142">
@@ -6940,19 +6940,19 @@
         <v>27</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J142" s="0">
-        <v>485.64830000000001</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="143">
@@ -6972,19 +6972,19 @@
         <v>27</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J143" s="0">
-        <v>457.39609999999999</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="144">
@@ -7004,19 +7004,19 @@
         <v>27</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J144" s="0">
-        <v>454.66460000000001</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="145">
@@ -7036,19 +7036,19 @@
         <v>27</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J145" s="0">
-        <v>368.51979999999998</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="146">
@@ -7068,19 +7068,19 @@
         <v>27</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J146" s="0">
-        <v>342.74220000000003</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="147">
@@ -7091,28 +7091,28 @@
         <v>3</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J147" s="0">
-        <v>302.46800000000002</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="148">
@@ -7123,28 +7123,28 @@
         <v>3</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J148" s="0">
-        <v>300.47250000000003</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="149">
@@ -7161,7 +7161,7 @@
         <v>20</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>29</v>
@@ -7170,13 +7170,13 @@
         <v>43</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J149" s="0">
-        <v>10892.9414</v>
+        <v>829.46619999999996</v>
       </c>
     </row>
     <row r="150">
@@ -7193,7 +7193,7 @@
         <v>20</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F150" s="0" t="s">
         <v>30</v>
@@ -7202,13 +7202,13 @@
         <v>44</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J150" s="0">
-        <v>5918.6806999999999</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="151">
@@ -7225,7 +7225,7 @@
         <v>20</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F151" s="0" t="s">
         <v>29</v>
@@ -7234,13 +7234,13 @@
         <v>43</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J151" s="0">
-        <v>829.46619999999996</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="152">
@@ -7257,22 +7257,22 @@
         <v>20</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J152" s="0">
-        <v>726.14110000000005</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="153">
@@ -7292,19 +7292,19 @@
         <v>27</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J153" s="0">
-        <v>498.3132</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="154">
@@ -7324,19 +7324,19 @@
         <v>27</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J154" s="0">
-        <v>487.10520000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="155">
@@ -7356,19 +7356,19 @@
         <v>27</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J155" s="0">
-        <v>485.66770000000002</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="156">
@@ -7388,19 +7388,19 @@
         <v>27</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J156" s="0">
-        <v>478.11529999999999</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="157">
@@ -7420,19 +7420,19 @@
         <v>27</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J157" s="0">
-        <v>375.48970000000003</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="158">
@@ -7452,19 +7452,19 @@
         <v>27</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J158" s="0">
-        <v>359.0838</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="159">
@@ -7478,25 +7478,25 @@
         <v>9</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J159" s="0">
-        <v>338.9837</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="160">
@@ -7510,25 +7510,25 @@
         <v>9</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J160" s="0">
-        <v>293.55579999999998</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="161">
@@ -7545,7 +7545,7 @@
         <v>21</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F161" s="0" t="s">
         <v>29</v>
@@ -7554,13 +7554,13 @@
         <v>43</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J161" s="0">
-        <v>9826.1103999999996</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="162">
@@ -7577,7 +7577,7 @@
         <v>21</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F162" s="0" t="s">
         <v>30</v>
@@ -7586,13 +7586,13 @@
         <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J162" s="0">
-        <v>7957.9004000000004</v>
+        <v>893.57759999999996</v>
       </c>
     </row>
     <row r="163">
@@ -7609,7 +7609,7 @@
         <v>21</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>29</v>
@@ -7618,13 +7618,13 @@
         <v>43</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J163" s="0">
-        <v>1958.7829999999999</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="164">
@@ -7641,22 +7641,22 @@
         <v>21</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J164" s="0">
-        <v>893.57759999999996</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="165">
@@ -7676,19 +7676,19 @@
         <v>27</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J165" s="0">
-        <v>574.80640000000005</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="166">
@@ -7708,19 +7708,19 @@
         <v>27</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J166" s="0">
-        <v>532.89999999999998</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="167">
@@ -7740,19 +7740,19 @@
         <v>27</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J167" s="0">
-        <v>470.99040000000002</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="168">
@@ -7772,19 +7772,19 @@
         <v>27</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J168" s="0">
-        <v>428.05349999999999</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="169">
@@ -7804,19 +7804,19 @@
         <v>27</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J169" s="0">
-        <v>370.83409999999998</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="170">
@@ -7836,19 +7836,19 @@
         <v>27</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J170" s="0">
-        <v>361.65289999999999</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="171">
@@ -7856,31 +7856,31 @@
         <v>1</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J171" s="0">
-        <v>328.18830000000003</v>
+        <v>9104.8721000000005</v>
       </c>
     </row>
     <row r="172">
@@ -7888,31 +7888,31 @@
         <v>1</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J172" s="0">
-        <v>313.28399999999999</v>
+        <v>1438.8326</v>
       </c>
     </row>
     <row r="173">
@@ -7929,22 +7929,22 @@
         <v>11</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J173" s="0">
-        <v>9104.8721000000005</v>
+        <v>1210.5242000000001</v>
       </c>
     </row>
     <row r="174">
@@ -7961,7 +7961,7 @@
         <v>11</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>29</v>
@@ -7970,13 +7970,13 @@
         <v>43</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J174" s="0">
-        <v>1438.8326</v>
+        <v>542.07240000000002</v>
       </c>
     </row>
     <row r="175">
@@ -7993,22 +7993,22 @@
         <v>11</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J175" s="0">
-        <v>1210.5242000000001</v>
+        <v>528.39120000000003</v>
       </c>
     </row>
     <row r="176">
@@ -8028,19 +8028,19 @@
         <v>27</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J176" s="0">
-        <v>542.07240000000002</v>
+        <v>519.83349999999996</v>
       </c>
     </row>
     <row r="177">
@@ -8060,19 +8060,19 @@
         <v>27</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J177" s="0">
-        <v>528.39120000000003</v>
+        <v>465.38400000000001</v>
       </c>
     </row>
     <row r="178">
@@ -8092,19 +8092,19 @@
         <v>27</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J178" s="0">
-        <v>519.83349999999996</v>
+        <v>387.42579999999998</v>
       </c>
     </row>
     <row r="179">
@@ -8124,19 +8124,19 @@
         <v>27</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J179" s="0">
-        <v>465.38400000000001</v>
+        <v>376.01639999999998</v>
       </c>
     </row>
     <row r="180">
@@ -8156,19 +8156,19 @@
         <v>27</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J180" s="0">
-        <v>387.42579999999998</v>
+        <v>367.9187</v>
       </c>
     </row>
     <row r="181">
@@ -8188,19 +8188,19 @@
         <v>27</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J181" s="0">
-        <v>376.01639999999998</v>
+        <v>345.6712</v>
       </c>
     </row>
     <row r="182">
@@ -8214,25 +8214,25 @@
         <v>6</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J182" s="0">
-        <v>367.9187</v>
+        <v>11026.299800000001</v>
       </c>
     </row>
     <row r="183">
@@ -8246,25 +8246,25 @@
         <v>6</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J183" s="0">
-        <v>345.6712</v>
+        <v>8759.9452999999994</v>
       </c>
     </row>
     <row r="184">
@@ -8281,7 +8281,7 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>29</v>
@@ -8290,13 +8290,13 @@
         <v>43</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J184" s="0">
-        <v>11026.299800000001</v>
+        <v>1159.0046</v>
       </c>
     </row>
     <row r="185">
@@ -8313,7 +8313,7 @@
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>30</v>
@@ -8322,13 +8322,13 @@
         <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J185" s="0">
-        <v>8759.9452999999994</v>
+        <v>1153.3887</v>
       </c>
     </row>
     <row r="186">
@@ -8345,7 +8345,7 @@
         <v>12</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>29</v>
@@ -8354,13 +8354,13 @@
         <v>43</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J186" s="0">
-        <v>1159.0046</v>
+        <v>531.56039999999996</v>
       </c>
     </row>
     <row r="187">
@@ -8377,22 +8377,22 @@
         <v>12</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J187" s="0">
-        <v>1153.3887</v>
+        <v>513.93790000000001</v>
       </c>
     </row>
     <row r="188">
@@ -8412,19 +8412,19 @@
         <v>27</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J188" s="0">
-        <v>531.56039999999996</v>
+        <v>499.63580000000002</v>
       </c>
     </row>
     <row r="189">
@@ -8444,19 +8444,19 @@
         <v>27</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J189" s="0">
-        <v>513.93790000000001</v>
+        <v>475.38760000000002</v>
       </c>
     </row>
     <row r="190">
@@ -8476,19 +8476,19 @@
         <v>27</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J190" s="0">
-        <v>499.63580000000002</v>
+        <v>357.59019999999998</v>
       </c>
     </row>
     <row r="191">
@@ -8508,19 +8508,19 @@
         <v>27</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J191" s="0">
-        <v>475.38760000000002</v>
+        <v>346.22629999999998</v>
       </c>
     </row>
     <row r="192">
@@ -8540,19 +8540,19 @@
         <v>27</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J192" s="0">
-        <v>357.59019999999998</v>
+        <v>331.46199999999999</v>
       </c>
     </row>
     <row r="193">
@@ -8572,19 +8572,19 @@
         <v>27</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J193" s="0">
-        <v>346.22629999999998</v>
+        <v>308.1046</v>
       </c>
     </row>
     <row r="194">
@@ -8598,25 +8598,25 @@
         <v>6</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="J194" s="0">
-        <v>331.46199999999999</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="195">
@@ -8630,25 +8630,25 @@
         <v>6</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J195" s="0">
-        <v>308.1046</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="196">
@@ -8665,7 +8665,7 @@
         <v>13</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>29</v>
@@ -8674,13 +8674,13 @@
         <v>43</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J196" s="0">
-        <v>901.9991</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="197">
@@ -8697,22 +8697,22 @@
         <v>13</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J197" s="0">
-        <v>893.56960000000004</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="198">
@@ -8732,19 +8732,19 @@
         <v>27</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J198" s="0">
-        <v>549.74869999999999</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="199">
@@ -8764,19 +8764,19 @@
         <v>27</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J199" s="0">
-        <v>530.14729999999997</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="200">
@@ -8796,19 +8796,19 @@
         <v>27</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J200" s="0">
-        <v>489.4966</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="201">
@@ -8828,19 +8828,19 @@
         <v>27</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J201" s="0">
-        <v>482.49549999999999</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="202">
@@ -8860,19 +8860,19 @@
         <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J202" s="0">
-        <v>378.9196</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="203">
@@ -8892,19 +8892,19 @@
         <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J203" s="0">
-        <v>366.15300000000002</v>
+        <v>329.09449999999998</v>
       </c>
     </row>
     <row r="204">
@@ -8918,25 +8918,25 @@
         <v>6</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J204" s="0">
-        <v>340.57749999999999</v>
+        <v>4307.7025999999996</v>
       </c>
     </row>
     <row r="205">
@@ -8950,25 +8950,25 @@
         <v>6</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J205" s="0">
-        <v>329.09449999999998</v>
+        <v>1837.0477000000001</v>
       </c>
     </row>
     <row r="206">
@@ -8985,7 +8985,7 @@
         <v>22</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>29</v>
@@ -8994,13 +8994,13 @@
         <v>43</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J206" s="0">
-        <v>4307.7025999999996</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="207">
@@ -9017,7 +9017,7 @@
         <v>22</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>30</v>
@@ -9026,13 +9026,13 @@
         <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J207" s="0">
-        <v>1837.0477000000001</v>
+        <v>552.42719999999997</v>
       </c>
     </row>
     <row r="208">
@@ -9049,7 +9049,7 @@
         <v>22</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>29</v>
@@ -9058,13 +9058,13 @@
         <v>43</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J208" s="0">
-        <v>616.08360000000005</v>
+        <v>399.44740000000002</v>
       </c>
     </row>
     <row r="209">
@@ -9081,22 +9081,22 @@
         <v>22</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J209" s="0">
-        <v>552.42719999999997</v>
+        <v>377.98289999999997</v>
       </c>
     </row>
     <row r="210">
@@ -9116,19 +9116,19 @@
         <v>27</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J210" s="0">
-        <v>399.44740000000002</v>
+        <v>376.71690000000001</v>
       </c>
     </row>
     <row r="211">
@@ -9148,19 +9148,19 @@
         <v>27</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J211" s="0">
-        <v>377.98289999999997</v>
+        <v>375.52019999999999</v>
       </c>
     </row>
     <row r="212">
@@ -9180,19 +9180,19 @@
         <v>27</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J212" s="0">
-        <v>376.71690000000001</v>
+        <v>370.8648</v>
       </c>
     </row>
     <row r="213">
@@ -9212,19 +9212,19 @@
         <v>27</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J213" s="0">
-        <v>375.52019999999999</v>
+        <v>342.89479999999998</v>
       </c>
     </row>
     <row r="214">
@@ -9244,19 +9244,19 @@
         <v>27</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J214" s="0">
-        <v>370.8648</v>
+        <v>307.26029999999997</v>
       </c>
     </row>
     <row r="215">
@@ -9276,19 +9276,19 @@
         <v>27</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J215" s="0">
-        <v>342.89479999999998</v>
+        <v>261.58179999999999</v>
       </c>
     </row>
     <row r="216">
@@ -9299,28 +9299,28 @@
         <v>4</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J216" s="0">
-        <v>307.26029999999997</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="217">
@@ -9331,28 +9331,28 @@
         <v>4</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J217" s="0">
-        <v>261.58179999999999</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="218">
@@ -9369,7 +9369,7 @@
         <v>14</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>29</v>
@@ -9378,13 +9378,13 @@
         <v>43</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J218" s="0">
-        <v>10466.208000000001</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="219">
@@ -9401,7 +9401,7 @@
         <v>14</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F219" s="0" t="s">
         <v>30</v>
@@ -9410,13 +9410,13 @@
         <v>44</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J219" s="0">
-        <v>7328.0029000000004</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="220">
@@ -9436,19 +9436,19 @@
         <v>26</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J220" s="0">
-        <v>1015.5606</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="221">
@@ -9468,19 +9468,19 @@
         <v>26</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J221" s="0">
-        <v>908.67830000000004</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="222">
@@ -9500,19 +9500,19 @@
         <v>26</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J222" s="0">
-        <v>520.97770000000003</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="223">
@@ -9532,19 +9532,19 @@
         <v>26</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J223" s="0">
-        <v>488.97149999999999</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9564,19 +9564,19 @@
         <v>26</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J224" s="0">
-        <v>484.75029999999998</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="225">
@@ -9596,19 +9596,19 @@
         <v>26</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J225" s="0">
-        <v>438.36930000000001</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="226">
@@ -9628,19 +9628,19 @@
         <v>26</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J226" s="0">
-        <v>369.10219999999998</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="227">
@@ -9660,19 +9660,19 @@
         <v>26</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J227" s="0">
-        <v>342.30680000000001</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="228">
@@ -9686,25 +9686,25 @@
         <v>7</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J228" s="0">
-        <v>280.75409999999999</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="229">
@@ -9718,25 +9718,25 @@
         <v>7</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J229" s="0">
-        <v>270.84679999999997</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="230">
@@ -9753,7 +9753,7 @@
         <v>15</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>29</v>
@@ -9762,13 +9762,13 @@
         <v>43</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J230" s="0">
-        <v>8934.2567999999992</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="231">
@@ -9785,22 +9785,22 @@
         <v>15</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J231" s="0">
-        <v>7192.2339000000002</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="232">
@@ -9817,22 +9817,22 @@
         <v>15</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J232" s="0">
-        <v>1017.6188</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="233">
@@ -9849,22 +9849,22 @@
         <v>15</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J233" s="0">
-        <v>892.98720000000003</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="234">
@@ -9884,19 +9884,19 @@
         <v>27</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J234" s="0">
-        <v>489.01900000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="235">
@@ -9916,19 +9916,19 @@
         <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J235" s="0">
-        <v>486.78719999999999</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="236">
@@ -9948,19 +9948,19 @@
         <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="J236" s="0">
-        <v>478.59969999999999</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="237">
@@ -9974,25 +9974,25 @@
         <v>7</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J237" s="0">
-        <v>456.38220000000001</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="238">
@@ -10006,10 +10006,10 @@
         <v>7</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>30</v>
@@ -10018,13 +10018,13 @@
         <v>44</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J238" s="0">
-        <v>361.197</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="239">
@@ -10038,25 +10038,25 @@
         <v>7</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="J239" s="0">
-        <v>350.10750000000002</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10070,25 +10070,25 @@
         <v>7</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J240" s="0">
-        <v>332.8802</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="241">
@@ -10105,7 +10105,7 @@
         <v>16</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>29</v>
@@ -10114,13 +10114,13 @@
         <v>43</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J241" s="0">
-        <v>9850.5967000000001</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="242">
@@ -10137,22 +10137,22 @@
         <v>16</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J242" s="0">
-        <v>8299.1229999999996</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="243">
@@ -10169,22 +10169,22 @@
         <v>16</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J243" s="0">
-        <v>1061.2550000000001</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="244">
@@ -10201,22 +10201,22 @@
         <v>16</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J244" s="0">
-        <v>863.95190000000002</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="245">
@@ -10236,19 +10236,19 @@
         <v>27</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J245" s="0">
-        <v>537.24440000000004</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="246">
@@ -10268,19 +10268,19 @@
         <v>27</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J246" s="0">
-        <v>512.39139999999998</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="247">
@@ -10300,19 +10300,19 @@
         <v>27</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G247" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J247" s="0">
-        <v>461.678</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="248">
@@ -10332,19 +10332,19 @@
         <v>27</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J248" s="0">
-        <v>446.13510000000002</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="249">
@@ -10358,25 +10358,25 @@
         <v>7</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="J249" s="0">
-        <v>416.1148</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="250">
@@ -10390,25 +10390,25 @@
         <v>7</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J250" s="0">
-        <v>385.80329999999998</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="251">
@@ -10422,25 +10422,25 @@
         <v>7</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="J251" s="0">
-        <v>376.43869999999998</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="252">
@@ -10454,25 +10454,25 @@
         <v>7</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J252" s="0">
-        <v>340.64490000000001</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="253">
@@ -10489,22 +10489,22 @@
         <v>17</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J253" s="0">
-        <v>9114.7715000000008</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="254">
@@ -10521,22 +10521,22 @@
         <v>17</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J254" s="0">
-        <v>7656.0316999999996</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="255">
@@ -10556,19 +10556,19 @@
         <v>26</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="J255" s="0">
-        <v>1088.5953</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="256">
@@ -10588,19 +10588,19 @@
         <v>26</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="J256" s="0">
-        <v>1085.6431</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="257">
@@ -10620,19 +10620,19 @@
         <v>26</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="J257" s="0">
-        <v>542.5788</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="258">
@@ -10652,19 +10652,19 @@
         <v>26</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J258" s="0">
-        <v>534.76580000000001</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="259">
@@ -10678,25 +10678,25 @@
         <v>7</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>123</v>
+        <v>197</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="J259" s="0">
-        <v>484.83710000000002</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="260">
@@ -10710,25 +10710,25 @@
         <v>7</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J260" s="0">
-        <v>468.87529999999998</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="261">
@@ -10742,25 +10742,25 @@
         <v>7</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E261" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="J261" s="0">
-        <v>398.83769999999998</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="262">
@@ -10774,25 +10774,25 @@
         <v>7</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E262" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="J262" s="0">
-        <v>337.36939999999999</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="263">
@@ -10806,25 +10806,25 @@
         <v>7</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="J263" s="0">
-        <v>311.84429999999998</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="264">
@@ -10838,25 +10838,25 @@
         <v>7</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G264" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J264" s="0">
-        <v>245.285</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="265">
@@ -10873,22 +10873,22 @@
         <v>23</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="J265" s="0">
-        <v>2887.6174000000001</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="266">
@@ -10905,22 +10905,22 @@
         <v>23</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J266" s="0">
-        <v>2872.1073999999999</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="267">
@@ -10937,22 +10937,22 @@
         <v>23</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="J267" s="0">
-        <v>975.3777</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="268">
@@ -10969,22 +10969,22 @@
         <v>23</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="J268" s="0">
-        <v>616.08360000000005</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="269">
@@ -11004,19 +11004,19 @@
         <v>27</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J269" s="0">
-        <v>465.53719999999999</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="270">
@@ -11036,19 +11036,19 @@
         <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="J270" s="0">
-        <v>436.18400000000003</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="271">
@@ -11059,28 +11059,28 @@
         <v>4</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>202</v>
+        <v>507</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>446</v>
+        <v>727</v>
       </c>
       <c r="J271" s="0">
-        <v>415.78980000000001</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="272">
@@ -11091,28 +11091,28 @@
         <v>4</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G272" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>203</v>
+        <v>508</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>447</v>
+        <v>728</v>
       </c>
       <c r="J272" s="0">
-        <v>391.16430000000003</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="273">
@@ -11123,28 +11123,28 @@
         <v>4</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>204</v>
+        <v>509</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>448</v>
+        <v>729</v>
       </c>
       <c r="J273" s="0">
-        <v>362.91770000000002</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="274">
@@ -11155,28 +11155,28 @@
         <v>4</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>205</v>
+        <v>510</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>449</v>
+        <v>730</v>
       </c>
       <c r="J274" s="0">
-        <v>315.58260000000001</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="275">
@@ -11187,28 +11187,28 @@
         <v>4</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E275" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>206</v>
+        <v>511</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>450</v>
+        <v>731</v>
       </c>
       <c r="J275" s="0">
-        <v>315.33229999999998</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11219,28 +11219,28 @@
         <v>4</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E276" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G276" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>207</v>
+        <v>512</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>451</v>
+        <v>732</v>
       </c>
       <c r="J276" s="0">
-        <v>254.02879999999999</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="277">
@@ -11257,22 +11257,22 @@
         <v>674</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="J277" s="0">
-        <v>10897.75</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="278">
@@ -11289,22 +11289,22 @@
         <v>674</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="J278" s="0">
-        <v>5963.8306000000002</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="279">
@@ -11321,22 +11321,22 @@
         <v>674</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="J279" s="0">
-        <v>1364.115</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="280">
@@ -11353,22 +11353,22 @@
         <v>674</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="J280" s="0">
-        <v>1002.6719000000001</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="281">
@@ -11388,19 +11388,19 @@
         <v>27</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="J281" s="0">
-        <v>557.97879999999998</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="282">
@@ -11420,19 +11420,19 @@
         <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="J282" s="0">
-        <v>511.4341</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="283">
@@ -11446,25 +11446,25 @@
         <v>501</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="J283" s="0">
-        <v>485.53699999999998</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="284">
@@ -11478,25 +11478,25 @@
         <v>501</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="J284" s="0">
-        <v>456.29579999999999</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="285">
@@ -11510,25 +11510,25 @@
         <v>501</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E285" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="J285" s="0">
-        <v>403.62130000000002</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="286">
@@ -11542,25 +11542,25 @@
         <v>501</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E286" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G286" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="J286" s="0">
-        <v>384.92849999999999</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="287">
@@ -11574,25 +11574,25 @@
         <v>501</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E287" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="J287" s="0">
-        <v>345.9332</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="288">
@@ -11606,25 +11606,25 @@
         <v>501</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E288" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="J288" s="0">
-        <v>329.33870000000002</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="289">
@@ -11641,22 +11641,22 @@
         <v>675</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="J289" s="0">
-        <v>9494.3554999999997</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="290">
@@ -11673,22 +11673,22 @@
         <v>675</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="J290" s="0">
-        <v>6959.3242</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="291">
@@ -11705,22 +11705,22 @@
         <v>675</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="J291" s="0">
-        <v>989.73109999999997</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="292">
@@ -11737,22 +11737,22 @@
         <v>675</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="J292" s="0">
-        <v>709.46839999999998</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="293">
@@ -11766,10 +11766,10 @@
         <v>501</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F293" s="0" t="s">
         <v>29</v>
@@ -11778,13 +11778,13 @@
         <v>43</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="J293" s="0">
-        <v>528.32619999999997</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="294">
@@ -11798,25 +11798,25 @@
         <v>501</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="J294" s="0">
-        <v>502.16129999999998</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="295">
@@ -11830,25 +11830,25 @@
         <v>501</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="J295" s="0">
-        <v>468.14839999999998</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="296">
@@ -11862,25 +11862,25 @@
         <v>501</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G296" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="J296" s="0">
-        <v>413.35890000000001</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="297">
@@ -11894,25 +11894,25 @@
         <v>501</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="J297" s="0">
-        <v>410.47199999999998</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="298">
@@ -11926,25 +11926,25 @@
         <v>501</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="J298" s="0">
-        <v>371.8809</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="299">
@@ -11958,25 +11958,25 @@
         <v>501</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E299" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="J299" s="0">
-        <v>347.0478</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="300">
@@ -11990,25 +11990,25 @@
         <v>501</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E300" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G300" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>530</v>
+        <v>64</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="J300" s="0">
-        <v>302.97559999999999</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="301">
@@ -12022,25 +12022,25 @@
         <v>501</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="J301" s="0">
-        <v>8923.2001999999993</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="302">
@@ -12054,25 +12054,25 @@
         <v>501</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="J302" s="0">
-        <v>7434.9364999999998</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="303">
@@ -12086,25 +12086,25 @@
         <v>501</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="J303" s="0">
-        <v>1198.5989</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="304">
@@ -12118,25 +12118,25 @@
         <v>501</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="J304" s="0">
-        <v>1016.6576</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="305">
@@ -12153,22 +12153,22 @@
         <v>677</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="J305" s="0">
-        <v>10363.415999999999</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="306">
@@ -12185,22 +12185,22 @@
         <v>677</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="J306" s="0">
-        <v>8731.0702999999994</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="307">
@@ -12214,10 +12214,10 @@
         <v>501</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F307" s="0" t="s">
         <v>29</v>
@@ -12226,13 +12226,13 @@
         <v>43</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="J307" s="0">
-        <v>848.39120000000003</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="308">
@@ -12246,10 +12246,10 @@
         <v>501</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>30</v>
@@ -12258,13 +12258,13 @@
         <v>44</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="J308" s="0">
-        <v>740.85990000000004</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="309">
@@ -12278,10 +12278,10 @@
         <v>501</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F309" s="0" t="s">
         <v>29</v>
@@ -12290,13 +12290,13 @@
         <v>43</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="J309" s="0">
-        <v>509.65910000000002</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="310">
@@ -12310,25 +12310,25 @@
         <v>501</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G310" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>64</v>
+        <v>557</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="J310" s="0">
-        <v>497.6062</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="311">
@@ -12342,25 +12342,25 @@
         <v>501</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E311" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="J311" s="0">
-        <v>473.81920000000002</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="312">
@@ -12374,25 +12374,25 @@
         <v>501</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E312" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="J312" s="0">
-        <v>386.12639999999999</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="313">
@@ -12406,25 +12406,25 @@
         <v>501</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E313" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="J313" s="0">
-        <v>381.40570000000002</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="314">
@@ -12438,25 +12438,25 @@
         <v>501</v>
       </c>
       <c r="D314" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E314" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="J314" s="0">
-        <v>371.59660000000002</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="315">
@@ -12470,25 +12470,25 @@
         <v>501</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="J315" s="0">
-        <v>364.02569999999997</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="316">
@@ -12502,25 +12502,25 @@
         <v>501</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E316" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="J316" s="0">
-        <v>331.7552</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="317">
@@ -12537,22 +12537,22 @@
         <v>678</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="J317" s="0">
-        <v>1621.762</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="318">
@@ -12569,22 +12569,22 @@
         <v>678</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="J318" s="0">
-        <v>1023.5883</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="319">
@@ -12595,13 +12595,13 @@
         <v>4</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F319" s="0" t="s">
         <v>29</v>
@@ -12610,13 +12610,13 @@
         <v>43</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>556</v>
+        <v>129</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>769</v>
+        <v>452</v>
       </c>
       <c r="J319" s="0">
-        <v>634.67409999999995</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="320">
@@ -12627,13 +12627,13 @@
         <v>4</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F320" s="0" t="s">
         <v>30</v>
@@ -12642,13 +12642,13 @@
         <v>44</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>557</v>
+        <v>130</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>770</v>
+        <v>453</v>
       </c>
       <c r="J320" s="0">
-        <v>589.45230000000004</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="321">
@@ -12659,13 +12659,13 @@
         <v>4</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F321" s="0" t="s">
         <v>29</v>
@@ -12674,13 +12674,13 @@
         <v>43</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>558</v>
+        <v>208</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>771</v>
+        <v>454</v>
       </c>
       <c r="J321" s="0">
-        <v>441.32260000000002</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="322">
@@ -12691,28 +12691,28 @@
         <v>4</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E322" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>559</v>
+        <v>133</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>772</v>
+        <v>456</v>
       </c>
       <c r="J322" s="0">
-        <v>406.00639999999999</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="323">
@@ -12723,28 +12723,28 @@
         <v>4</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E323" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>560</v>
+        <v>134</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>773</v>
+        <v>457</v>
       </c>
       <c r="J323" s="0">
-        <v>404.98939999999999</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="324">
@@ -12755,28 +12755,28 @@
         <v>4</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E324" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>561</v>
+        <v>135</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>774</v>
+        <v>458</v>
       </c>
       <c r="J324" s="0">
-        <v>356.87450000000001</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="325">
@@ -12787,28 +12787,28 @@
         <v>4</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E325" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>562</v>
+        <v>136</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>775</v>
+        <v>459</v>
       </c>
       <c r="J325" s="0">
-        <v>326.86750000000001</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="326">
@@ -12819,28 +12819,28 @@
         <v>4</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E326" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>563</v>
+        <v>137</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>776</v>
+        <v>460</v>
       </c>
       <c r="J326" s="0">
-        <v>313.15320000000003</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="327">
@@ -12851,28 +12851,28 @@
         <v>4</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E327" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>564</v>
+        <v>138</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>777</v>
+        <v>461</v>
       </c>
       <c r="J327" s="0">
-        <v>302.25330000000002</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="328">
@@ -12883,28 +12883,28 @@
         <v>4</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E328" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>565</v>
+        <v>139</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>778</v>
+        <v>462</v>
       </c>
       <c r="J328" s="0">
-        <v>241.7327</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="329">
@@ -12921,22 +12921,22 @@
         <v>18</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="J329" s="0">
-        <v>8389.2909999999993</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="330">
@@ -12950,25 +12950,25 @@
         <v>8</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E330" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="J330" s="0">
-        <v>8068.0429999999997</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="331">
@@ -12982,25 +12982,25 @@
         <v>8</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="J331" s="0">
-        <v>1304.9119000000001</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="332">
@@ -13014,25 +13014,25 @@
         <v>8</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E332" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="J332" s="0">
-        <v>981.88890000000004</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="333">
@@ -13046,25 +13046,25 @@
         <v>8</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="J333" s="0">
-        <v>528.16520000000003</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="334">
@@ -13078,25 +13078,25 @@
         <v>8</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E334" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="J334" s="0">
-        <v>464.43889999999999</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="335">
@@ -13110,25 +13110,25 @@
         <v>8</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E335" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="J335" s="0">
-        <v>449.87619999999998</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="336">
@@ -13142,25 +13142,25 @@
         <v>8</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E336" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="J336" s="0">
-        <v>447.66699999999997</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="337">
@@ -13174,25 +13174,25 @@
         <v>8</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E337" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="J337" s="0">
-        <v>391.69869999999997</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="338">
@@ -13206,25 +13206,25 @@
         <v>8</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E338" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="J338" s="0">
-        <v>372.4153</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="339">
@@ -13238,25 +13238,25 @@
         <v>8</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E339" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="J339" s="0">
-        <v>366.97289999999998</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="340">
@@ -13270,25 +13270,25 @@
         <v>8</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E340" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="J340" s="0">
-        <v>329.11259999999999</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="341">
@@ -13305,22 +13305,22 @@
         <v>19</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="J341" s="0">
-        <v>9741.5614999999998</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="342">
@@ -13331,28 +13331,28 @@
         <v>4</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E342" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="J342" s="0">
-        <v>8198.8974999999991</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="343">
@@ -13363,28 +13363,28 @@
         <v>4</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G343" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="J343" s="0">
-        <v>1259.1116</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="344">
@@ -13395,28 +13395,28 @@
         <v>4</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E344" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G344" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="J344" s="0">
-        <v>964.0145</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="345">
@@ -13427,10 +13427,10 @@
         <v>4</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E345" s="0" t="s">
         <v>27</v>
@@ -13442,13 +13442,13 @@
         <v>43</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="J345" s="0">
-        <v>539.45429999999999</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="346">
@@ -13459,10 +13459,10 @@
         <v>4</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E346" s="0" t="s">
         <v>27</v>
@@ -13474,13 +13474,13 @@
         <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="J346" s="0">
-        <v>485.64830000000001</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="347">
@@ -13491,10 +13491,10 @@
         <v>4</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E347" s="0" t="s">
         <v>27</v>
@@ -13506,13 +13506,13 @@
         <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="J347" s="0">
-        <v>457.39609999999999</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="348">
@@ -13523,10 +13523,10 @@
         <v>4</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E348" s="0" t="s">
         <v>27</v>
@@ -13538,13 +13538,13 @@
         <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="J348" s="0">
-        <v>454.66460000000001</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="349">
@@ -13555,10 +13555,10 @@
         <v>4</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E349" s="0" t="s">
         <v>27</v>
@@ -13570,13 +13570,13 @@
         <v>44</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="J349" s="0">
-        <v>368.51979999999998</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="350">
@@ -13587,10 +13587,10 @@
         <v>4</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E350" s="0" t="s">
         <v>27</v>
@@ -13602,13 +13602,13 @@
         <v>44</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="J350" s="0">
-        <v>342.74220000000003</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="351">
@@ -13619,10 +13619,10 @@
         <v>4</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E351" s="0" t="s">
         <v>27</v>
@@ -13634,13 +13634,13 @@
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="J351" s="0">
-        <v>302.46800000000002</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="352">
@@ -13651,10 +13651,10 @@
         <v>4</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E352" s="0" t="s">
         <v>27</v>
@@ -13666,13 +13666,13 @@
         <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="J352" s="0">
-        <v>300.47250000000003</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="353">
@@ -13686,7 +13686,7 @@
         <v>9</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E353" s="0" t="s">
         <v>25</v>
@@ -13698,13 +13698,13 @@
         <v>43</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="J353" s="0">
-        <v>10892.9414</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="354">
@@ -13718,7 +13718,7 @@
         <v>9</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E354" s="0" t="s">
         <v>25</v>
@@ -13730,13 +13730,13 @@
         <v>44</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="J354" s="0">
-        <v>5918.6806999999999</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="355">
@@ -13750,7 +13750,7 @@
         <v>9</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E355" s="0" t="s">
         <v>26</v>
@@ -13762,13 +13762,13 @@
         <v>43</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="J355" s="0">
-        <v>726.14110000000005</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="356">
@@ -13782,7 +13782,7 @@
         <v>9</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E356" s="0" t="s">
         <v>27</v>
@@ -13794,13 +13794,13 @@
         <v>43</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="J356" s="0">
-        <v>498.3132</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="357">
@@ -13814,7 +13814,7 @@
         <v>9</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E357" s="0" t="s">
         <v>27</v>
@@ -13826,13 +13826,13 @@
         <v>43</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="J357" s="0">
-        <v>487.10520000000002</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="358">
@@ -13846,7 +13846,7 @@
         <v>9</v>
       </c>
       <c r="D358" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E358" s="0" t="s">
         <v>27</v>
@@ -13858,13 +13858,13 @@
         <v>43</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="J358" s="0">
-        <v>485.66770000000002</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="359">
@@ -13878,7 +13878,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E359" s="0" t="s">
         <v>27</v>
@@ -13890,13 +13890,13 @@
         <v>43</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="J359" s="0">
-        <v>478.11529999999999</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="360">
@@ -13910,7 +13910,7 @@
         <v>9</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E360" s="0" t="s">
         <v>27</v>
@@ -13922,13 +13922,13 @@
         <v>44</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="J360" s="0">
-        <v>375.48970000000003</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="361">
@@ -13942,7 +13942,7 @@
         <v>9</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E361" s="0" t="s">
         <v>27</v>
@@ -13954,13 +13954,13 @@
         <v>44</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="J361" s="0">
-        <v>359.0838</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="362">
@@ -13974,7 +13974,7 @@
         <v>9</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E362" s="0" t="s">
         <v>27</v>
@@ -13986,13 +13986,13 @@
         <v>44</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="J362" s="0">
-        <v>338.9837</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="363">
@@ -14006,7 +14006,7 @@
         <v>9</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E363" s="0" t="s">
         <v>27</v>
@@ -14018,13 +14018,13 @@
         <v>44</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="J363" s="0">
-        <v>293.55579999999998</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="364">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="50784" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53971" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -4066,13 +4066,13 @@
         <v>43</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J52" s="0">
-        <v>1017.6188</v>
+        <v>892.98720000000003</v>
       </c>
     </row>
     <row r="53">
@@ -4089,22 +4089,22 @@
         <v>15</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J53" s="0">
-        <v>892.98720000000003</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4124,19 +4124,19 @@
         <v>27</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J54" s="0">
-        <v>489.01900000000001</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4156,19 +4156,19 @@
         <v>27</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J55" s="0">
-        <v>486.78719999999999</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4188,19 +4188,19 @@
         <v>27</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J56" s="0">
-        <v>478.59969999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4220,19 +4220,19 @@
         <v>27</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J57" s="0">
-        <v>456.38220000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="58">
@@ -4252,19 +4252,19 @@
         <v>27</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J58" s="0">
-        <v>361.197</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="59">
@@ -4284,19 +4284,19 @@
         <v>27</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J59" s="0">
-        <v>350.10750000000002</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="60">
@@ -4310,25 +4310,25 @@
         <v>7</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J60" s="0">
-        <v>332.8802</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4348,19 +4348,19 @@
         <v>25</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J61" s="0">
-        <v>9850.5967000000001</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="62">
@@ -4377,22 +4377,22 @@
         <v>16</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J62" s="0">
-        <v>8299.1229999999996</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4412,19 +4412,19 @@
         <v>26</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J63" s="0">
-        <v>1061.2550000000001</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="64">
@@ -4441,22 +4441,22 @@
         <v>16</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J64" s="0">
-        <v>863.95190000000002</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="65">
@@ -4476,19 +4476,19 @@
         <v>27</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J65" s="0">
-        <v>537.24440000000004</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="66">
@@ -4508,19 +4508,19 @@
         <v>27</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J66" s="0">
-        <v>512.39139999999998</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="67">
@@ -4540,19 +4540,19 @@
         <v>27</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J67" s="0">
-        <v>461.678</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="68">
@@ -4572,19 +4572,19 @@
         <v>27</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J68" s="0">
-        <v>446.13510000000002</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="69">
@@ -4604,19 +4604,19 @@
         <v>27</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J69" s="0">
-        <v>416.1148</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="70">
@@ -4636,19 +4636,19 @@
         <v>27</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J70" s="0">
-        <v>385.80329999999998</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="71">
@@ -4668,19 +4668,19 @@
         <v>27</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J71" s="0">
-        <v>376.43869999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4694,25 +4694,25 @@
         <v>7</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J72" s="0">
-        <v>340.64490000000001</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="73">
@@ -4732,19 +4732,19 @@
         <v>25</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J73" s="0">
-        <v>9114.7715000000008</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="74">
@@ -4761,22 +4761,22 @@
         <v>17</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J74" s="0">
-        <v>7656.0316999999996</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="75">
@@ -4796,19 +4796,19 @@
         <v>26</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J75" s="0">
-        <v>1088.5953</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4828,19 +4828,19 @@
         <v>26</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J76" s="0">
-        <v>1085.6431</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="77">
@@ -4860,19 +4860,19 @@
         <v>26</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J77" s="0">
-        <v>542.5788</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="78">
@@ -4892,19 +4892,19 @@
         <v>26</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J78" s="0">
-        <v>534.76580000000001</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="79">
@@ -4924,19 +4924,19 @@
         <v>26</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J79" s="0">
-        <v>484.83710000000002</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="80">
@@ -4956,19 +4956,19 @@
         <v>26</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J80" s="0">
-        <v>468.87529999999998</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="81">
@@ -4988,19 +4988,19 @@
         <v>26</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J81" s="0">
-        <v>398.83769999999998</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="82">
@@ -5011,28 +5011,28 @@
         <v>3</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>17</v>
+        <v>674</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>126</v>
+        <v>507</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>293</v>
+        <v>679</v>
       </c>
       <c r="J82" s="0">
-        <v>337.36939999999999</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="83">
@@ -5043,28 +5043,28 @@
         <v>3</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>17</v>
+        <v>674</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>127</v>
+        <v>508</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>294</v>
+        <v>680</v>
       </c>
       <c r="J83" s="0">
-        <v>311.84429999999998</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="84">
@@ -5075,28 +5075,28 @@
         <v>3</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>17</v>
+        <v>674</v>
       </c>
       <c r="E84" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>128</v>
+        <v>509</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>295</v>
+        <v>681</v>
       </c>
       <c r="J84" s="0">
-        <v>245.285</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="85">
@@ -5113,22 +5113,22 @@
         <v>674</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="J85" s="0">
-        <v>10897.75</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5145,22 +5145,22 @@
         <v>674</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="J86" s="0">
-        <v>5963.8306000000002</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="87">
@@ -5177,22 +5177,22 @@
         <v>674</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="J87" s="0">
-        <v>1364.115</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="88">
@@ -5209,22 +5209,22 @@
         <v>674</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="J88" s="0">
-        <v>1002.6719000000001</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="89">
@@ -5244,19 +5244,19 @@
         <v>27</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J89" s="0">
-        <v>557.97879999999998</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5276,19 +5276,19 @@
         <v>27</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J90" s="0">
-        <v>511.4341</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="91">
@@ -5308,19 +5308,19 @@
         <v>27</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="J91" s="0">
-        <v>485.53699999999998</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="92">
@@ -5340,19 +5340,19 @@
         <v>27</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="J92" s="0">
-        <v>456.29579999999999</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="93">
@@ -5372,19 +5372,19 @@
         <v>27</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="J93" s="0">
-        <v>403.62130000000002</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="94">
@@ -5398,25 +5398,25 @@
         <v>501</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="J94" s="0">
-        <v>384.92849999999999</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="95">
@@ -5430,25 +5430,25 @@
         <v>501</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J95" s="0">
-        <v>345.9332</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="96">
@@ -5462,25 +5462,25 @@
         <v>501</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E96" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="J96" s="0">
-        <v>329.33870000000002</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="97">
@@ -5497,22 +5497,22 @@
         <v>675</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="J97" s="0">
-        <v>9494.3554999999997</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="98">
@@ -5529,22 +5529,22 @@
         <v>675</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="J98" s="0">
-        <v>6959.3242</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="99">
@@ -5561,22 +5561,22 @@
         <v>675</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="J99" s="0">
-        <v>989.73109999999997</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="100">
@@ -5593,7 +5593,7 @@
         <v>675</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F100" s="0" t="s">
         <v>30</v>
@@ -5602,13 +5602,13 @@
         <v>44</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="J100" s="0">
-        <v>709.46839999999998</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="101">
@@ -5628,19 +5628,19 @@
         <v>27</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="J101" s="0">
-        <v>528.32619999999997</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="102">
@@ -5660,19 +5660,19 @@
         <v>27</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="J102" s="0">
-        <v>502.16129999999998</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="103">
@@ -5692,19 +5692,19 @@
         <v>27</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="J103" s="0">
-        <v>468.14839999999998</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="104">
@@ -5718,25 +5718,25 @@
         <v>501</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="J104" s="0">
-        <v>413.35890000000001</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="105">
@@ -5750,10 +5750,10 @@
         <v>501</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>30</v>
@@ -5762,13 +5762,13 @@
         <v>44</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="J105" s="0">
-        <v>410.47199999999998</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="106">
@@ -5782,25 +5782,25 @@
         <v>501</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="J106" s="0">
-        <v>371.8809</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="107">
@@ -5814,25 +5814,25 @@
         <v>501</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="J107" s="0">
-        <v>347.0478</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="108">
@@ -5846,25 +5846,25 @@
         <v>501</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="J108" s="0">
-        <v>302.97559999999999</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="109">
@@ -5878,25 +5878,25 @@
         <v>501</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E109" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="J109" s="0">
-        <v>8923.2001999999993</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="110">
@@ -5910,25 +5910,25 @@
         <v>501</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="J110" s="0">
-        <v>7434.9364999999998</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="111">
@@ -5942,25 +5942,25 @@
         <v>501</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
       <c r="J111" s="0">
-        <v>1198.5989</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="112">
@@ -5974,25 +5974,25 @@
         <v>501</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="J112" s="0">
-        <v>1016.6576</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6009,22 +6009,22 @@
         <v>677</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="J113" s="0">
-        <v>10363.415999999999</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="114">
@@ -6041,7 +6041,7 @@
         <v>677</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F114" s="0" t="s">
         <v>30</v>
@@ -6050,13 +6050,13 @@
         <v>44</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="J114" s="0">
-        <v>8731.0702999999994</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="115">
@@ -6073,22 +6073,22 @@
         <v>677</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="J115" s="0">
-        <v>848.39120000000003</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="116">
@@ -6105,22 +6105,22 @@
         <v>677</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>546</v>
+        <v>146</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="J116" s="0">
-        <v>740.85990000000004</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="117">
@@ -6140,19 +6140,19 @@
         <v>27</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="J117" s="0">
-        <v>509.65910000000002</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="118">
@@ -6163,28 +6163,28 @@
         <v>3</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>548</v>
+        <v>129</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>720</v>
+        <v>296</v>
       </c>
       <c r="J118" s="0">
-        <v>473.81920000000002</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="119">
@@ -6195,28 +6195,28 @@
         <v>3</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>549</v>
+        <v>130</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>721</v>
+        <v>297</v>
       </c>
       <c r="J119" s="0">
-        <v>386.12639999999999</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="120">
@@ -6227,28 +6227,28 @@
         <v>3</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E120" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>550</v>
+        <v>133</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>722</v>
+        <v>300</v>
       </c>
       <c r="J120" s="0">
-        <v>381.40570000000002</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="121">
@@ -6259,28 +6259,28 @@
         <v>3</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E121" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>551</v>
+        <v>134</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>723</v>
+        <v>301</v>
       </c>
       <c r="J121" s="0">
-        <v>371.59660000000002</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="122">
@@ -6291,28 +6291,28 @@
         <v>3</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E122" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>552</v>
+        <v>135</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>724</v>
+        <v>302</v>
       </c>
       <c r="J122" s="0">
-        <v>364.02569999999997</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="123">
@@ -6323,28 +6323,28 @@
         <v>3</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>725</v>
+        <v>303</v>
       </c>
       <c r="J123" s="0">
-        <v>342.74220000000003</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="124">
@@ -6355,28 +6355,28 @@
         <v>3</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>553</v>
+        <v>137</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>726</v>
+        <v>304</v>
       </c>
       <c r="J124" s="0">
-        <v>331.7552</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="125">
@@ -6393,22 +6393,22 @@
         <v>18</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="J125" s="0">
-        <v>8389.2909999999993</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="126">
@@ -6425,22 +6425,22 @@
         <v>18</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="J126" s="0">
-        <v>8068.0429999999997</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="127">
@@ -6460,19 +6460,19 @@
         <v>27</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="J127" s="0">
-        <v>528.16520000000003</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="128">
@@ -6486,25 +6486,25 @@
         <v>8</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="J128" s="0">
-        <v>464.43889999999999</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="129">
@@ -6518,25 +6518,25 @@
         <v>8</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="J129" s="0">
-        <v>449.87619999999998</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="130">
@@ -6550,25 +6550,25 @@
         <v>8</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="J130" s="0">
-        <v>447.66699999999997</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="131">
@@ -6582,10 +6582,10 @@
         <v>8</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>30</v>
@@ -6594,13 +6594,13 @@
         <v>44</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="J131" s="0">
-        <v>391.69869999999997</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="132">
@@ -6614,25 +6614,25 @@
         <v>8</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E132" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="J132" s="0">
-        <v>372.4153</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="133">
@@ -6646,25 +6646,25 @@
         <v>8</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="J133" s="0">
-        <v>366.97289999999998</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="134">
@@ -6678,25 +6678,25 @@
         <v>8</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E134" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="J134" s="0">
-        <v>329.11259999999999</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="135">
@@ -6713,22 +6713,22 @@
         <v>19</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="J135" s="0">
-        <v>9741.5614999999998</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="136">
@@ -6745,7 +6745,7 @@
         <v>19</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F136" s="0" t="s">
         <v>30</v>
@@ -6754,13 +6754,13 @@
         <v>44</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="J136" s="0">
-        <v>8198.8974999999991</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="137">
@@ -6777,22 +6777,22 @@
         <v>19</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="J137" s="0">
-        <v>1259.1116</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="138">
@@ -6809,22 +6809,22 @@
         <v>19</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="J138" s="0">
-        <v>863.95190000000002</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="139">
@@ -6844,19 +6844,19 @@
         <v>27</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="J139" s="0">
-        <v>539.45429999999999</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="140">
@@ -6867,28 +6867,28 @@
         <v>3</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="J140" s="0">
-        <v>485.64830000000001</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="141">
@@ -6899,28 +6899,28 @@
         <v>3</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J141" s="0">
-        <v>457.39609999999999</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="142">
@@ -6931,28 +6931,28 @@
         <v>3</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="J142" s="0">
-        <v>454.66460000000001</v>
+        <v>829.46619999999996</v>
       </c>
     </row>
     <row r="143">
@@ -6963,13 +6963,13 @@
         <v>3</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>30</v>
@@ -6978,13 +6978,13 @@
         <v>44</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="J143" s="0">
-        <v>368.51979999999998</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="144">
@@ -6995,28 +6995,28 @@
         <v>3</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E144" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J144" s="0">
-        <v>342.74220000000003</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="145">
@@ -7027,28 +7027,28 @@
         <v>3</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E145" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J145" s="0">
-        <v>302.46800000000002</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="146">
@@ -7059,28 +7059,28 @@
         <v>3</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E146" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="J146" s="0">
-        <v>300.47250000000003</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="147">
@@ -7097,22 +7097,22 @@
         <v>20</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J147" s="0">
-        <v>10892.9414</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="148">
@@ -7129,7 +7129,7 @@
         <v>20</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F148" s="0" t="s">
         <v>30</v>
@@ -7138,13 +7138,13 @@
         <v>44</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="J148" s="0">
-        <v>5918.6806999999999</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="149">
@@ -7161,22 +7161,22 @@
         <v>20</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="J149" s="0">
-        <v>829.46619999999996</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="150">
@@ -7193,22 +7193,22 @@
         <v>20</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="J150" s="0">
-        <v>726.14110000000005</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="151">
@@ -7228,19 +7228,19 @@
         <v>27</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="J151" s="0">
-        <v>498.3132</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="152">
@@ -7254,25 +7254,25 @@
         <v>9</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="J152" s="0">
-        <v>487.10520000000002</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="153">
@@ -7286,25 +7286,25 @@
         <v>9</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J153" s="0">
-        <v>485.66770000000002</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="154">
@@ -7318,25 +7318,25 @@
         <v>9</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="J154" s="0">
-        <v>478.11529999999999</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="155">
@@ -7350,25 +7350,25 @@
         <v>9</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E155" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="J155" s="0">
-        <v>375.48970000000003</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="156">
@@ -7382,25 +7382,25 @@
         <v>9</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E156" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="J156" s="0">
-        <v>359.0838</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="157">
@@ -7414,25 +7414,25 @@
         <v>9</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E157" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="J157" s="0">
-        <v>338.9837</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="158">
@@ -7446,25 +7446,25 @@
         <v>9</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E158" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="J158" s="0">
-        <v>293.55579999999998</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="159">
@@ -7481,22 +7481,22 @@
         <v>21</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="J159" s="0">
-        <v>9826.1103999999996</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="160">
@@ -7513,22 +7513,22 @@
         <v>21</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="J160" s="0">
-        <v>7957.9004000000004</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="161">
@@ -7545,22 +7545,22 @@
         <v>21</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="J161" s="0">
-        <v>1958.7829999999999</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="162">
@@ -7577,22 +7577,22 @@
         <v>21</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="J162" s="0">
-        <v>893.57759999999996</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="163">
@@ -7600,16 +7600,16 @@
         <v>1</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>29</v>
@@ -7618,13 +7618,13 @@
         <v>43</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="J163" s="0">
-        <v>574.80640000000005</v>
+        <v>9104.8721000000005</v>
       </c>
     </row>
     <row r="164">
@@ -7632,31 +7632,31 @@
         <v>1</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="J164" s="0">
-        <v>532.89999999999998</v>
+        <v>1438.8326</v>
       </c>
     </row>
     <row r="165">
@@ -7664,31 +7664,31 @@
         <v>1</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="J165" s="0">
-        <v>470.99040000000002</v>
+        <v>1210.5242000000001</v>
       </c>
     </row>
     <row r="166">
@@ -7696,31 +7696,31 @@
         <v>1</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E166" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="J166" s="0">
-        <v>428.05349999999999</v>
+        <v>542.07240000000002</v>
       </c>
     </row>
     <row r="167">
@@ -7728,31 +7728,31 @@
         <v>1</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E167" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="J167" s="0">
-        <v>370.83409999999998</v>
+        <v>528.39120000000003</v>
       </c>
     </row>
     <row r="168">
@@ -7760,31 +7760,31 @@
         <v>1</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E168" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="J168" s="0">
-        <v>361.65289999999999</v>
+        <v>519.83349999999996</v>
       </c>
     </row>
     <row r="169">
@@ -7792,31 +7792,31 @@
         <v>1</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E169" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="J169" s="0">
-        <v>328.18830000000003</v>
+        <v>465.38400000000001</v>
       </c>
     </row>
     <row r="170">
@@ -7824,31 +7824,31 @@
         <v>1</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E170" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="J170" s="0">
-        <v>313.28399999999999</v>
+        <v>387.42579999999998</v>
       </c>
     </row>
     <row r="171">
@@ -7865,22 +7865,22 @@
         <v>11</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="J171" s="0">
-        <v>9104.8721000000005</v>
+        <v>376.01639999999998</v>
       </c>
     </row>
     <row r="172">
@@ -7897,22 +7897,22 @@
         <v>11</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="J172" s="0">
-        <v>1438.8326</v>
+        <v>367.9187</v>
       </c>
     </row>
     <row r="173">
@@ -7929,22 +7929,22 @@
         <v>11</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="J173" s="0">
-        <v>1210.5242000000001</v>
+        <v>345.6712</v>
       </c>
     </row>
     <row r="174">
@@ -7958,10 +7958,10 @@
         <v>6</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>29</v>
@@ -7970,13 +7970,13 @@
         <v>43</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="J174" s="0">
-        <v>542.07240000000002</v>
+        <v>11026.299800000001</v>
       </c>
     </row>
     <row r="175">
@@ -7990,25 +7990,25 @@
         <v>6</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="J175" s="0">
-        <v>528.39120000000003</v>
+        <v>8759.9452999999994</v>
       </c>
     </row>
     <row r="176">
@@ -8022,25 +8022,25 @@
         <v>6</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="J176" s="0">
-        <v>519.83349999999996</v>
+        <v>1159.0046</v>
       </c>
     </row>
     <row r="177">
@@ -8054,25 +8054,25 @@
         <v>6</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="J177" s="0">
-        <v>465.38400000000001</v>
+        <v>1153.3887</v>
       </c>
     </row>
     <row r="178">
@@ -8086,25 +8086,25 @@
         <v>6</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E178" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="J178" s="0">
-        <v>387.42579999999998</v>
+        <v>531.56039999999996</v>
       </c>
     </row>
     <row r="179">
@@ -8118,25 +8118,25 @@
         <v>6</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E179" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="J179" s="0">
-        <v>376.01639999999998</v>
+        <v>513.93790000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8150,25 +8150,25 @@
         <v>6</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E180" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="J180" s="0">
-        <v>367.9187</v>
+        <v>499.63580000000002</v>
       </c>
     </row>
     <row r="181">
@@ -8182,25 +8182,25 @@
         <v>6</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="J181" s="0">
-        <v>345.6712</v>
+        <v>475.38760000000002</v>
       </c>
     </row>
     <row r="182">
@@ -8217,22 +8217,22 @@
         <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J182" s="0">
-        <v>11026.299800000001</v>
+        <v>357.59019999999998</v>
       </c>
     </row>
     <row r="183">
@@ -8249,22 +8249,22 @@
         <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="J183" s="0">
-        <v>8759.9452999999994</v>
+        <v>346.22629999999998</v>
       </c>
     </row>
     <row r="184">
@@ -8281,22 +8281,22 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="J184" s="0">
-        <v>1159.0046</v>
+        <v>331.46199999999999</v>
       </c>
     </row>
     <row r="185">
@@ -8313,22 +8313,22 @@
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="J185" s="0">
-        <v>1153.3887</v>
+        <v>308.1046</v>
       </c>
     </row>
     <row r="186">
@@ -8342,10 +8342,10 @@
         <v>6</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>29</v>
@@ -8354,13 +8354,13 @@
         <v>43</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="J186" s="0">
-        <v>531.56039999999996</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="187">
@@ -8374,25 +8374,25 @@
         <v>6</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="J187" s="0">
-        <v>513.93790000000001</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="188">
@@ -8406,25 +8406,25 @@
         <v>6</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E188" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="J188" s="0">
-        <v>499.63580000000002</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="189">
@@ -8438,25 +8438,25 @@
         <v>6</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E189" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="J189" s="0">
-        <v>475.38760000000002</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="190">
@@ -8470,25 +8470,25 @@
         <v>6</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E190" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J190" s="0">
-        <v>357.59019999999998</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="191">
@@ -8502,25 +8502,25 @@
         <v>6</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E191" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="J191" s="0">
-        <v>346.22629999999998</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="192">
@@ -8534,25 +8534,25 @@
         <v>6</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E192" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="J192" s="0">
-        <v>331.46199999999999</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="193">
@@ -8566,25 +8566,25 @@
         <v>6</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E193" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="J193" s="0">
-        <v>308.1046</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="194">
@@ -8601,22 +8601,22 @@
         <v>13</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="J194" s="0">
-        <v>901.9991</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="195">
@@ -8630,25 +8630,25 @@
         <v>6</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="J195" s="0">
-        <v>893.56960000000004</v>
+        <v>4307.7025999999996</v>
       </c>
     </row>
     <row r="196">
@@ -8662,25 +8662,25 @@
         <v>6</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="J196" s="0">
-        <v>549.74869999999999</v>
+        <v>1837.0477000000001</v>
       </c>
     </row>
     <row r="197">
@@ -8694,25 +8694,25 @@
         <v>6</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="J197" s="0">
-        <v>530.14729999999997</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="198">
@@ -8726,25 +8726,25 @@
         <v>6</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="J198" s="0">
-        <v>489.4966</v>
+        <v>552.42719999999997</v>
       </c>
     </row>
     <row r="199">
@@ -8758,25 +8758,25 @@
         <v>6</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E199" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="J199" s="0">
-        <v>482.49549999999999</v>
+        <v>399.44740000000002</v>
       </c>
     </row>
     <row r="200">
@@ -8790,25 +8790,25 @@
         <v>6</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E200" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="J200" s="0">
-        <v>378.9196</v>
+        <v>377.98289999999997</v>
       </c>
     </row>
     <row r="201">
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E201" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="J201" s="0">
-        <v>366.15300000000002</v>
+        <v>376.71690000000001</v>
       </c>
     </row>
     <row r="202">
@@ -8854,25 +8854,25 @@
         <v>6</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E202" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="J202" s="0">
-        <v>340.57749999999999</v>
+        <v>375.52019999999999</v>
       </c>
     </row>
     <row r="203">
@@ -8886,25 +8886,25 @@
         <v>6</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E203" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="J203" s="0">
-        <v>329.09449999999998</v>
+        <v>370.8648</v>
       </c>
     </row>
     <row r="204">
@@ -8921,22 +8921,22 @@
         <v>22</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="J204" s="0">
-        <v>4307.7025999999996</v>
+        <v>342.89479999999998</v>
       </c>
     </row>
     <row r="205">
@@ -8953,22 +8953,22 @@
         <v>22</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="J205" s="0">
-        <v>1837.0477000000001</v>
+        <v>307.26029999999997</v>
       </c>
     </row>
     <row r="206">
@@ -8985,22 +8985,22 @@
         <v>22</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="J206" s="0">
-        <v>616.08360000000005</v>
+        <v>261.58179999999999</v>
       </c>
     </row>
     <row r="207">
@@ -9011,28 +9011,28 @@
         <v>4</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="J207" s="0">
-        <v>552.42719999999997</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="208">
@@ -9043,28 +9043,28 @@
         <v>4</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="J208" s="0">
-        <v>399.44740000000002</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="209">
@@ -9075,28 +9075,28 @@
         <v>4</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="J209" s="0">
-        <v>377.98289999999997</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="210">
@@ -9107,28 +9107,28 @@
         <v>4</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="J210" s="0">
-        <v>376.71690000000001</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="211">
@@ -9139,28 +9139,28 @@
         <v>4</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="J211" s="0">
-        <v>375.52019999999999</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="212">
@@ -9171,28 +9171,28 @@
         <v>4</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="J212" s="0">
-        <v>370.8648</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="213">
@@ -9203,28 +9203,28 @@
         <v>4</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="J213" s="0">
-        <v>342.89479999999998</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="214">
@@ -9235,28 +9235,28 @@
         <v>4</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="J214" s="0">
-        <v>307.26029999999997</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="215">
@@ -9267,28 +9267,28 @@
         <v>4</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="J215" s="0">
-        <v>261.58179999999999</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="216">
@@ -9305,22 +9305,22 @@
         <v>14</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="J216" s="0">
-        <v>10466.208000000001</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="217">
@@ -9337,22 +9337,22 @@
         <v>14</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="J217" s="0">
-        <v>7328.0029000000004</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="218">
@@ -9372,19 +9372,19 @@
         <v>26</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="J218" s="0">
-        <v>1015.5606</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="219">
@@ -9398,25 +9398,25 @@
         <v>7</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="J219" s="0">
-        <v>908.67830000000004</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="220">
@@ -9430,25 +9430,25 @@
         <v>7</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="J220" s="0">
-        <v>520.97770000000003</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="221">
@@ -9462,25 +9462,25 @@
         <v>7</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="J221" s="0">
-        <v>488.97149999999999</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="222">
@@ -9494,25 +9494,25 @@
         <v>7</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="J222" s="0">
-        <v>484.75029999999998</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="223">
@@ -9526,25 +9526,25 @@
         <v>7</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="J223" s="0">
-        <v>438.36930000000001</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="224">
@@ -9558,25 +9558,25 @@
         <v>7</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="J224" s="0">
-        <v>369.10219999999998</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="225">
@@ -9590,25 +9590,25 @@
         <v>7</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="J225" s="0">
-        <v>342.30680000000001</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="226">
@@ -9622,25 +9622,25 @@
         <v>7</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="J226" s="0">
-        <v>280.75409999999999</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="227">
@@ -9654,25 +9654,25 @@
         <v>7</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="J227" s="0">
-        <v>270.84679999999997</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="228">
@@ -9686,7 +9686,7 @@
         <v>7</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E228" s="0" t="s">
         <v>25</v>
@@ -9698,13 +9698,13 @@
         <v>43</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="J228" s="0">
-        <v>8934.2567999999992</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="229">
@@ -9718,7 +9718,7 @@
         <v>7</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E229" s="0" t="s">
         <v>25</v>
@@ -9730,13 +9730,13 @@
         <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="J229" s="0">
-        <v>7192.2339000000002</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="230">
@@ -9750,10 +9750,10 @@
         <v>7</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>29</v>
@@ -9762,13 +9762,13 @@
         <v>43</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="J230" s="0">
-        <v>489.01900000000001</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="231">
@@ -9782,25 +9782,25 @@
         <v>7</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="J231" s="0">
-        <v>486.78719999999999</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="232">
@@ -9814,25 +9814,25 @@
         <v>7</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E232" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="J232" s="0">
-        <v>478.59969999999999</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="233">
@@ -9846,25 +9846,25 @@
         <v>7</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E233" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="J233" s="0">
-        <v>456.38220000000001</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="234">
@@ -9878,25 +9878,25 @@
         <v>7</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E234" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="J234" s="0">
-        <v>361.197</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="235">
@@ -9910,25 +9910,25 @@
         <v>7</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E235" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="J235" s="0">
-        <v>350.10750000000002</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="236">
@@ -9942,25 +9942,25 @@
         <v>7</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E236" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="J236" s="0">
-        <v>332.8802</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="237">
@@ -9977,22 +9977,22 @@
         <v>16</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="J237" s="0">
-        <v>9850.5967000000001</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="238">
@@ -10009,22 +10009,22 @@
         <v>16</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="J238" s="0">
-        <v>8299.1229999999996</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="239">
@@ -10041,22 +10041,22 @@
         <v>16</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="J239" s="0">
-        <v>1061.2550000000001</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10070,25 +10070,25 @@
         <v>7</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="J240" s="0">
-        <v>863.95190000000002</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="241">
@@ -10102,25 +10102,25 @@
         <v>7</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J241" s="0">
-        <v>537.24440000000004</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="242">
@@ -10134,25 +10134,25 @@
         <v>7</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="J242" s="0">
-        <v>512.39139999999998</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="243">
@@ -10166,25 +10166,25 @@
         <v>7</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="J243" s="0">
-        <v>461.678</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="244">
@@ -10198,25 +10198,25 @@
         <v>7</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="J244" s="0">
-        <v>446.13510000000002</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="245">
@@ -10230,25 +10230,25 @@
         <v>7</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="J245" s="0">
-        <v>416.1148</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="246">
@@ -10262,25 +10262,25 @@
         <v>7</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="J246" s="0">
-        <v>385.80329999999998</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="247">
@@ -10294,25 +10294,25 @@
         <v>7</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="J247" s="0">
-        <v>376.43869999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10326,25 +10326,25 @@
         <v>7</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="J248" s="0">
-        <v>340.64490000000001</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="249">
@@ -10361,22 +10361,22 @@
         <v>17</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="J249" s="0">
-        <v>9114.7715000000008</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="250">
@@ -10390,25 +10390,25 @@
         <v>7</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E250" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>118</v>
+        <v>197</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="J250" s="0">
-        <v>7656.0316999999996</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="251">
@@ -10422,25 +10422,25 @@
         <v>7</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="J251" s="0">
-        <v>542.5788</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10454,25 +10454,25 @@
         <v>7</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E252" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="J252" s="0">
-        <v>534.76580000000001</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="253">
@@ -10486,25 +10486,25 @@
         <v>7</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E253" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="J253" s="0">
-        <v>484.83710000000002</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="254">
@@ -10518,25 +10518,25 @@
         <v>7</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="J254" s="0">
-        <v>468.87529999999998</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="255">
@@ -10550,25 +10550,25 @@
         <v>7</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J255" s="0">
-        <v>398.83769999999998</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="256">
@@ -10582,25 +10582,25 @@
         <v>7</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="J256" s="0">
-        <v>337.36939999999999</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="257">
@@ -10614,25 +10614,25 @@
         <v>7</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="J257" s="0">
-        <v>311.84429999999998</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="258">
@@ -10646,25 +10646,25 @@
         <v>7</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="J258" s="0">
-        <v>245.285</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="259">
@@ -10681,22 +10681,22 @@
         <v>23</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J259" s="0">
-        <v>2887.6174000000001</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="260">
@@ -10713,22 +10713,22 @@
         <v>23</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="J260" s="0">
-        <v>2872.1073999999999</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="261">
@@ -10745,22 +10745,22 @@
         <v>23</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="J261" s="0">
-        <v>975.3777</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="262">
@@ -10771,28 +10771,28 @@
         <v>4</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>187</v>
+        <v>507</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>443</v>
+        <v>727</v>
       </c>
       <c r="J262" s="0">
-        <v>616.08360000000005</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="263">
@@ -10803,28 +10803,28 @@
         <v>4</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>200</v>
+        <v>508</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>444</v>
+        <v>728</v>
       </c>
       <c r="J263" s="0">
-        <v>465.53719999999999</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="264">
@@ -10835,28 +10835,28 @@
         <v>4</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>201</v>
+        <v>509</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>445</v>
+        <v>729</v>
       </c>
       <c r="J264" s="0">
-        <v>436.18400000000003</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="265">
@@ -10867,28 +10867,28 @@
         <v>4</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>202</v>
+        <v>510</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>446</v>
+        <v>730</v>
       </c>
       <c r="J265" s="0">
-        <v>415.78980000000001</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="266">
@@ -10899,28 +10899,28 @@
         <v>4</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E266" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>203</v>
+        <v>511</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>447</v>
+        <v>731</v>
       </c>
       <c r="J266" s="0">
-        <v>391.16430000000003</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="267">
@@ -10931,28 +10931,28 @@
         <v>4</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E267" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>204</v>
+        <v>512</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>448</v>
+        <v>732</v>
       </c>
       <c r="J267" s="0">
-        <v>362.91770000000002</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="268">
@@ -10963,28 +10963,28 @@
         <v>4</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E268" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>205</v>
+        <v>513</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>449</v>
+        <v>733</v>
       </c>
       <c r="J268" s="0">
-        <v>315.58260000000001</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="269">
@@ -10995,28 +10995,28 @@
         <v>4</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E269" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>450</v>
+        <v>734</v>
       </c>
       <c r="J269" s="0">
-        <v>315.33229999999998</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="270">
@@ -11027,28 +11027,28 @@
         <v>4</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E270" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>207</v>
+        <v>515</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>451</v>
+        <v>735</v>
       </c>
       <c r="J270" s="0">
-        <v>254.02879999999999</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="271">
@@ -11065,22 +11065,22 @@
         <v>674</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G271" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="J271" s="0">
-        <v>10897.75</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="272">
@@ -11097,22 +11097,22 @@
         <v>674</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="J272" s="0">
-        <v>5963.8306000000002</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="273">
@@ -11129,22 +11129,22 @@
         <v>674</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="J273" s="0">
-        <v>1364.115</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="274">
@@ -11158,25 +11158,25 @@
         <v>501</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="J274" s="0">
-        <v>1002.6719000000001</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="275">
@@ -11190,25 +11190,25 @@
         <v>501</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="J275" s="0">
-        <v>557.97879999999998</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="276">
@@ -11222,25 +11222,25 @@
         <v>501</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E276" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="J276" s="0">
-        <v>511.4341</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="277">
@@ -11254,25 +11254,25 @@
         <v>501</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E277" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="J277" s="0">
-        <v>485.53699999999998</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="278">
@@ -11286,25 +11286,25 @@
         <v>501</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E278" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="J278" s="0">
-        <v>456.29579999999999</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="279">
@@ -11318,25 +11318,25 @@
         <v>501</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E279" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="J279" s="0">
-        <v>403.62130000000002</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="280">
@@ -11350,25 +11350,25 @@
         <v>501</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E280" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="J280" s="0">
-        <v>384.92849999999999</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="281">
@@ -11382,25 +11382,25 @@
         <v>501</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E281" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="J281" s="0">
-        <v>345.9332</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="282">
@@ -11414,25 +11414,25 @@
         <v>501</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E282" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="J282" s="0">
-        <v>329.33870000000002</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="283">
@@ -11449,22 +11449,22 @@
         <v>675</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G283" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="J283" s="0">
-        <v>9494.3554999999997</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="284">
@@ -11478,25 +11478,25 @@
         <v>501</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E284" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="J284" s="0">
-        <v>6959.3242</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="285">
@@ -11510,25 +11510,25 @@
         <v>501</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="J285" s="0">
-        <v>528.32619999999997</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="286">
@@ -11542,25 +11542,25 @@
         <v>501</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="J286" s="0">
-        <v>502.16129999999998</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="287">
@@ -11574,25 +11574,25 @@
         <v>501</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="J287" s="0">
-        <v>468.14839999999998</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="288">
@@ -11606,25 +11606,25 @@
         <v>501</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="J288" s="0">
-        <v>413.35890000000001</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="289">
@@ -11638,10 +11638,10 @@
         <v>501</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F289" s="0" t="s">
         <v>30</v>
@@ -11650,13 +11650,13 @@
         <v>44</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="J289" s="0">
-        <v>410.47199999999998</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="290">
@@ -11670,25 +11670,25 @@
         <v>501</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E290" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="J290" s="0">
-        <v>371.8809</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="291">
@@ -11702,25 +11702,25 @@
         <v>501</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E291" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>529</v>
+        <v>64</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="J291" s="0">
-        <v>347.0478</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="292">
@@ -11734,25 +11734,25 @@
         <v>501</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E292" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="J292" s="0">
-        <v>302.97559999999999</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="293">
@@ -11766,25 +11766,25 @@
         <v>501</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="J293" s="0">
-        <v>8923.2001999999993</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="294">
@@ -11798,10 +11798,10 @@
         <v>501</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
         <v>30</v>
@@ -11810,13 +11810,13 @@
         <v>44</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="J294" s="0">
-        <v>7434.9364999999998</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="295">
@@ -11830,25 +11830,25 @@
         <v>501</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G295" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="J295" s="0">
-        <v>1198.5989</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="296">
@@ -11862,25 +11862,25 @@
         <v>501</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="J296" s="0">
-        <v>1016.6576</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="297">
@@ -11897,22 +11897,22 @@
         <v>677</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="J297" s="0">
-        <v>10363.415999999999</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="298">
@@ -11926,25 +11926,25 @@
         <v>501</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E298" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G298" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="J298" s="0">
-        <v>8731.0702999999994</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="299">
@@ -11958,25 +11958,25 @@
         <v>501</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="J299" s="0">
-        <v>509.65910000000002</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="300">
@@ -11990,25 +11990,25 @@
         <v>501</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>64</v>
+        <v>556</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="J300" s="0">
-        <v>497.6062</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="301">
@@ -12022,25 +12022,25 @@
         <v>501</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="J301" s="0">
-        <v>473.81920000000002</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="302">
@@ -12054,25 +12054,25 @@
         <v>501</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E302" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="J302" s="0">
-        <v>386.12639999999999</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="303">
@@ -12086,25 +12086,25 @@
         <v>501</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E303" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="J303" s="0">
-        <v>381.40570000000002</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="304">
@@ -12118,25 +12118,25 @@
         <v>501</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E304" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="J304" s="0">
-        <v>371.59660000000002</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="305">
@@ -12150,25 +12150,25 @@
         <v>501</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E305" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="J305" s="0">
-        <v>364.02569999999997</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="306">
@@ -12182,25 +12182,25 @@
         <v>501</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E306" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="J306" s="0">
-        <v>331.7552</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="307">
@@ -12217,22 +12217,22 @@
         <v>678</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G307" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="J307" s="0">
-        <v>1621.762</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="308">
@@ -12249,22 +12249,22 @@
         <v>678</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="J308" s="0">
-        <v>1023.5883</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="309">
@@ -12281,22 +12281,22 @@
         <v>678</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="J309" s="0">
-        <v>634.67409999999995</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="310">
@@ -12307,28 +12307,28 @@
         <v>4</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G310" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>557</v>
+        <v>129</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>770</v>
+        <v>452</v>
       </c>
       <c r="J310" s="0">
-        <v>589.45230000000004</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="311">
@@ -12339,28 +12339,28 @@
         <v>4</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>771</v>
+        <v>453</v>
       </c>
       <c r="J311" s="0">
-        <v>441.32260000000002</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="312">
@@ -12371,28 +12371,28 @@
         <v>4</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>559</v>
+        <v>208</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>772</v>
+        <v>454</v>
       </c>
       <c r="J312" s="0">
-        <v>406.00639999999999</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="313">
@@ -12403,28 +12403,28 @@
         <v>4</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E313" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>560</v>
+        <v>133</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>773</v>
+        <v>456</v>
       </c>
       <c r="J313" s="0">
-        <v>404.98939999999999</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="314">
@@ -12435,28 +12435,28 @@
         <v>4</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D314" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E314" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>561</v>
+        <v>134</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>774</v>
+        <v>457</v>
       </c>
       <c r="J314" s="0">
-        <v>356.87450000000001</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="315">
@@ -12467,28 +12467,28 @@
         <v>4</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>562</v>
+        <v>135</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>775</v>
+        <v>458</v>
       </c>
       <c r="J315" s="0">
-        <v>326.86750000000001</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="316">
@@ -12499,28 +12499,28 @@
         <v>4</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E316" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>563</v>
+        <v>136</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>776</v>
+        <v>459</v>
       </c>
       <c r="J316" s="0">
-        <v>313.15320000000003</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="317">
@@ -12531,28 +12531,28 @@
         <v>4</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E317" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>564</v>
+        <v>137</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>777</v>
+        <v>460</v>
       </c>
       <c r="J317" s="0">
-        <v>302.25330000000002</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="318">
@@ -12563,28 +12563,28 @@
         <v>4</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E318" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>565</v>
+        <v>138</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>778</v>
+        <v>461</v>
       </c>
       <c r="J318" s="0">
-        <v>241.7327</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="319">
@@ -12601,22 +12601,22 @@
         <v>18</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="J319" s="0">
-        <v>8389.2909999999993</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="320">
@@ -12633,22 +12633,22 @@
         <v>18</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="J320" s="0">
-        <v>8068.0429999999997</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="321">
@@ -12662,10 +12662,10 @@
         <v>8</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F321" s="0" t="s">
         <v>29</v>
@@ -12674,13 +12674,13 @@
         <v>43</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>208</v>
+        <v>58</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="J321" s="0">
-        <v>1304.9119000000001</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="322">
@@ -12694,25 +12694,25 @@
         <v>8</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="J322" s="0">
-        <v>528.16520000000003</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="323">
@@ -12726,25 +12726,25 @@
         <v>8</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="J323" s="0">
-        <v>464.43889999999999</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="324">
@@ -12758,25 +12758,25 @@
         <v>8</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="J324" s="0">
-        <v>449.87619999999998</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="325">
@@ -12790,25 +12790,25 @@
         <v>8</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E325" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="J325" s="0">
-        <v>447.66699999999997</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="326">
@@ -12822,25 +12822,25 @@
         <v>8</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E326" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="J326" s="0">
-        <v>391.69869999999997</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="327">
@@ -12854,25 +12854,25 @@
         <v>8</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E327" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="J327" s="0">
-        <v>372.4153</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="328">
@@ -12886,25 +12886,25 @@
         <v>8</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E328" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="J328" s="0">
-        <v>366.97289999999998</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="329">
@@ -12918,25 +12918,25 @@
         <v>8</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E329" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="J329" s="0">
-        <v>329.11259999999999</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="330">
@@ -12953,22 +12953,22 @@
         <v>19</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="J330" s="0">
-        <v>9741.5614999999998</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="331">
@@ -12985,22 +12985,22 @@
         <v>19</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="J331" s="0">
-        <v>8198.8974999999991</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="332">
@@ -13017,22 +13017,22 @@
         <v>19</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="J332" s="0">
-        <v>1259.1116</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="333">
@@ -13043,28 +13043,28 @@
         <v>4</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="J333" s="0">
-        <v>964.0145</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="334">
@@ -13075,28 +13075,28 @@
         <v>4</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G334" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="J334" s="0">
-        <v>539.45429999999999</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="335">
@@ -13107,28 +13107,28 @@
         <v>4</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="J335" s="0">
-        <v>485.64830000000001</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="336">
@@ -13139,28 +13139,28 @@
         <v>4</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E336" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="J336" s="0">
-        <v>457.39609999999999</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="337">
@@ -13171,28 +13171,28 @@
         <v>4</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E337" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="J337" s="0">
-        <v>454.66460000000001</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="338">
@@ -13203,28 +13203,28 @@
         <v>4</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E338" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="J338" s="0">
-        <v>368.51979999999998</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="339">
@@ -13235,28 +13235,28 @@
         <v>4</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E339" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="J339" s="0">
-        <v>342.74220000000003</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="340">
@@ -13267,28 +13267,28 @@
         <v>4</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E340" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="J340" s="0">
-        <v>302.46800000000002</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="341">
@@ -13299,28 +13299,28 @@
         <v>4</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E341" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="J341" s="0">
-        <v>300.47250000000003</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="342">
@@ -13337,22 +13337,22 @@
         <v>20</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="J342" s="0">
-        <v>10892.9414</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="343">
@@ -13369,22 +13369,22 @@
         <v>20</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="J343" s="0">
-        <v>5918.6806999999999</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="344">
@@ -13398,10 +13398,10 @@
         <v>9</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F344" s="0" t="s">
         <v>29</v>
@@ -13410,13 +13410,13 @@
         <v>43</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="J344" s="0">
-        <v>726.14110000000005</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="345">
@@ -13430,25 +13430,25 @@
         <v>9</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="J345" s="0">
-        <v>498.3132</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="346">
@@ -13462,25 +13462,25 @@
         <v>9</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="J346" s="0">
-        <v>487.10520000000002</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="347">
@@ -13494,25 +13494,25 @@
         <v>9</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E347" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="J347" s="0">
-        <v>485.66770000000002</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="348">
@@ -13526,25 +13526,25 @@
         <v>9</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E348" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="J348" s="0">
-        <v>478.11529999999999</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="349">
@@ -13558,25 +13558,25 @@
         <v>9</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E349" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="J349" s="0">
-        <v>375.48970000000003</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="350">
@@ -13590,25 +13590,25 @@
         <v>9</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E350" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="J350" s="0">
-        <v>359.0838</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="351">
@@ -13622,25 +13622,25 @@
         <v>9</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E351" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="J351" s="0">
-        <v>338.9837</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="352">
@@ -13654,25 +13654,25 @@
         <v>9</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E352" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="J352" s="0">
-        <v>293.55579999999998</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="353">
@@ -13689,22 +13689,22 @@
         <v>21</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="J353" s="0">
-        <v>9826.1103999999996</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="354">
@@ -13721,22 +13721,22 @@
         <v>21</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="J354" s="0">
-        <v>7957.9004000000004</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="355">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53971" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76163" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
@@ -3234,13 +3234,13 @@
         <v>43</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J26" s="0">
-        <v>8033.9306999999999</v>
+        <v>5932.7479999999996</v>
       </c>
     </row>
     <row r="27">
@@ -3257,22 +3257,22 @@
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J27" s="0">
-        <v>5932.7479999999996</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="28">
@@ -3292,19 +3292,19 @@
         <v>26</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J28" s="0">
-        <v>901.9991</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="29">
@@ -3321,22 +3321,22 @@
         <v>13</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J29" s="0">
-        <v>893.56960000000004</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3356,19 +3356,19 @@
         <v>27</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J30" s="0">
-        <v>549.74869999999999</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="31">
@@ -3388,19 +3388,19 @@
         <v>27</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J31" s="0">
-        <v>530.14729999999997</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="32">
@@ -3420,19 +3420,19 @@
         <v>27</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J32" s="0">
-        <v>489.4966</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3452,19 +3452,19 @@
         <v>27</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J33" s="0">
-        <v>482.49549999999999</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="34">
@@ -3484,19 +3484,19 @@
         <v>27</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J34" s="0">
-        <v>378.9196</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="35">
@@ -3516,19 +3516,19 @@
         <v>27</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J35" s="0">
-        <v>366.15300000000002</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3539,28 +3539,28 @@
         <v>3</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J36" s="0">
-        <v>340.57749999999999</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3571,28 +3571,28 @@
         <v>3</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J37" s="0">
-        <v>329.09449999999998</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="38">
@@ -3609,7 +3609,7 @@
         <v>14</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>29</v>
@@ -3618,13 +3618,13 @@
         <v>43</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J38" s="0">
-        <v>10466.208000000001</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="39">
@@ -3641,7 +3641,7 @@
         <v>14</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>30</v>
@@ -3650,13 +3650,13 @@
         <v>44</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J39" s="0">
-        <v>7328.0029000000004</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="40">
@@ -3676,19 +3676,19 @@
         <v>26</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J40" s="0">
-        <v>1015.5606</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="41">
@@ -3708,19 +3708,19 @@
         <v>26</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J41" s="0">
-        <v>908.67830000000004</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3740,19 +3740,19 @@
         <v>26</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J42" s="0">
-        <v>520.97770000000003</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="43">
@@ -3772,19 +3772,19 @@
         <v>26</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J43" s="0">
-        <v>488.97149999999999</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3804,19 +3804,19 @@
         <v>26</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J44" s="0">
-        <v>484.75029999999998</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="45">
@@ -3836,19 +3836,19 @@
         <v>26</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J45" s="0">
-        <v>438.36930000000001</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3868,19 +3868,19 @@
         <v>26</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J46" s="0">
-        <v>369.10219999999998</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3900,19 +3900,19 @@
         <v>26</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J47" s="0">
-        <v>342.30680000000001</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="48">
@@ -3926,25 +3926,25 @@
         <v>7</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J48" s="0">
-        <v>280.75409999999999</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="49">
@@ -3958,25 +3958,25 @@
         <v>7</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J49" s="0">
-        <v>270.84679999999997</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="50">
@@ -3993,7 +3993,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F50" s="0" t="s">
         <v>29</v>
@@ -4002,13 +4002,13 @@
         <v>43</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J50" s="0">
-        <v>8934.2567999999992</v>
+        <v>892.98720000000003</v>
       </c>
     </row>
     <row r="51">
@@ -4025,22 +4025,22 @@
         <v>15</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J51" s="0">
-        <v>7192.2339000000002</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4057,22 +4057,22 @@
         <v>15</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J52" s="0">
-        <v>892.98720000000003</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4092,19 +4092,19 @@
         <v>27</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J53" s="0">
-        <v>489.01900000000001</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4124,19 +4124,19 @@
         <v>27</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J54" s="0">
-        <v>486.78719999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4156,19 +4156,19 @@
         <v>27</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J55" s="0">
-        <v>478.59969999999999</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="56">
@@ -4188,19 +4188,19 @@
         <v>27</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J56" s="0">
-        <v>456.38220000000001</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="57">
@@ -4220,19 +4220,19 @@
         <v>27</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J57" s="0">
-        <v>361.197</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="58">
@@ -4246,25 +4246,25 @@
         <v>7</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J58" s="0">
-        <v>350.10750000000002</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4278,25 +4278,25 @@
         <v>7</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J59" s="0">
-        <v>332.8802</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="60">
@@ -4313,7 +4313,7 @@
         <v>16</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F60" s="0" t="s">
         <v>29</v>
@@ -4322,13 +4322,13 @@
         <v>43</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J60" s="0">
-        <v>9850.5967000000001</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4345,7 +4345,7 @@
         <v>16</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>30</v>
@@ -4354,13 +4354,13 @@
         <v>44</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J61" s="0">
-        <v>8299.1229999999996</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="62">
@@ -4377,7 +4377,7 @@
         <v>16</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>29</v>
@@ -4386,13 +4386,13 @@
         <v>43</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J62" s="0">
-        <v>1061.2550000000001</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="63">
@@ -4409,22 +4409,22 @@
         <v>16</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J63" s="0">
-        <v>863.95190000000002</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="64">
@@ -4444,19 +4444,19 @@
         <v>27</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J64" s="0">
-        <v>537.24440000000004</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="65">
@@ -4476,19 +4476,19 @@
         <v>27</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J65" s="0">
-        <v>512.39139999999998</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="66">
@@ -4508,19 +4508,19 @@
         <v>27</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J66" s="0">
-        <v>461.678</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="67">
@@ -4540,19 +4540,19 @@
         <v>27</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J67" s="0">
-        <v>446.13510000000002</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="68">
@@ -4572,19 +4572,19 @@
         <v>27</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J68" s="0">
-        <v>416.1148</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="69">
@@ -4604,19 +4604,19 @@
         <v>27</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J69" s="0">
-        <v>385.80329999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4630,25 +4630,25 @@
         <v>7</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J70" s="0">
-        <v>376.43869999999998</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="71">
@@ -4662,25 +4662,25 @@
         <v>7</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J71" s="0">
-        <v>340.64490000000001</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="72">
@@ -4697,7 +4697,7 @@
         <v>17</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F72" s="0" t="s">
         <v>29</v>
@@ -4706,13 +4706,13 @@
         <v>43</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J72" s="0">
-        <v>9114.7715000000008</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="73">
@@ -4729,7 +4729,7 @@
         <v>17</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>30</v>
@@ -4738,13 +4738,13 @@
         <v>44</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J73" s="0">
-        <v>7656.0316999999996</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4764,19 +4764,19 @@
         <v>26</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J74" s="0">
-        <v>542.5788</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="75">
@@ -4796,19 +4796,19 @@
         <v>26</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J75" s="0">
-        <v>534.76580000000001</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="76">
@@ -4828,19 +4828,19 @@
         <v>26</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J76" s="0">
-        <v>484.83710000000002</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="77">
@@ -4860,19 +4860,19 @@
         <v>26</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J77" s="0">
-        <v>468.87529999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="78">
@@ -4892,19 +4892,19 @@
         <v>26</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J78" s="0">
-        <v>398.83769999999998</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="79">
@@ -4924,19 +4924,19 @@
         <v>26</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J79" s="0">
-        <v>337.36939999999999</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="80">
@@ -4947,28 +4947,28 @@
         <v>3</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>17</v>
+        <v>674</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>127</v>
+        <v>507</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>294</v>
+        <v>679</v>
       </c>
       <c r="J80" s="0">
-        <v>311.84429999999998</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="81">
@@ -4979,28 +4979,28 @@
         <v>3</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>17</v>
+        <v>674</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>128</v>
+        <v>508</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>295</v>
+        <v>680</v>
       </c>
       <c r="J81" s="0">
-        <v>245.285</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="82">
@@ -5017,7 +5017,7 @@
         <v>674</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F82" s="0" t="s">
         <v>29</v>
@@ -5026,13 +5026,13 @@
         <v>43</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J82" s="0">
-        <v>10897.75</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="83">
@@ -5049,7 +5049,7 @@
         <v>674</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>30</v>
@@ -5058,13 +5058,13 @@
         <v>44</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="J83" s="0">
-        <v>5963.8306000000002</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5081,7 +5081,7 @@
         <v>674</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F84" s="0" t="s">
         <v>29</v>
@@ -5090,13 +5090,13 @@
         <v>43</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J84" s="0">
-        <v>1364.115</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="85">
@@ -5113,22 +5113,22 @@
         <v>674</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="J85" s="0">
-        <v>1002.6719000000001</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="86">
@@ -5148,19 +5148,19 @@
         <v>27</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J86" s="0">
-        <v>557.97879999999998</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="87">
@@ -5180,19 +5180,19 @@
         <v>27</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J87" s="0">
-        <v>511.4341</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5212,19 +5212,19 @@
         <v>27</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J88" s="0">
-        <v>485.53699999999998</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="89">
@@ -5244,19 +5244,19 @@
         <v>27</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="J89" s="0">
-        <v>456.29579999999999</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5276,19 +5276,19 @@
         <v>27</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J90" s="0">
-        <v>403.62130000000002</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="91">
@@ -5308,19 +5308,19 @@
         <v>27</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="J91" s="0">
-        <v>384.92849999999999</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="92">
@@ -5334,25 +5334,25 @@
         <v>501</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J92" s="0">
-        <v>345.9332</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="93">
@@ -5366,25 +5366,25 @@
         <v>501</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J93" s="0">
-        <v>329.33870000000002</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="94">
@@ -5401,7 +5401,7 @@
         <v>675</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>29</v>
@@ -5410,13 +5410,13 @@
         <v>43</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="J94" s="0">
-        <v>9494.3554999999997</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="95">
@@ -5433,22 +5433,22 @@
         <v>675</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="J95" s="0">
-        <v>6959.3242</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="96">
@@ -5468,19 +5468,19 @@
         <v>27</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J96" s="0">
-        <v>528.32619999999997</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="97">
@@ -5500,19 +5500,19 @@
         <v>27</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="J97" s="0">
-        <v>502.16129999999998</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5532,19 +5532,19 @@
         <v>27</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J98" s="0">
-        <v>468.14839999999998</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="99">
@@ -5564,19 +5564,19 @@
         <v>27</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="J99" s="0">
-        <v>413.35890000000001</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="100">
@@ -5596,19 +5596,19 @@
         <v>27</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J100" s="0">
-        <v>410.47199999999998</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="101">
@@ -5628,19 +5628,19 @@
         <v>27</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="J101" s="0">
-        <v>371.8809</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="102">
@@ -5654,25 +5654,25 @@
         <v>501</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J102" s="0">
-        <v>347.0478</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="103">
@@ -5686,25 +5686,25 @@
         <v>501</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="J103" s="0">
-        <v>302.97559999999999</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="104">
@@ -5721,7 +5721,7 @@
         <v>676</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F104" s="0" t="s">
         <v>29</v>
@@ -5730,13 +5730,13 @@
         <v>43</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J104" s="0">
-        <v>8923.2001999999993</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="105">
@@ -5753,7 +5753,7 @@
         <v>676</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>30</v>
@@ -5762,13 +5762,13 @@
         <v>44</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J105" s="0">
-        <v>7434.9364999999998</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="106">
@@ -5782,10 +5782,10 @@
         <v>501</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>29</v>
@@ -5794,13 +5794,13 @@
         <v>43</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="J106" s="0">
-        <v>1198.5989</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="107">
@@ -5814,10 +5814,10 @@
         <v>501</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F107" s="0" t="s">
         <v>30</v>
@@ -5826,13 +5826,13 @@
         <v>44</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="J107" s="0">
-        <v>1016.6576</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="108">
@@ -5849,7 +5849,7 @@
         <v>677</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F108" s="0" t="s">
         <v>29</v>
@@ -5858,13 +5858,13 @@
         <v>43</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="J108" s="0">
-        <v>10363.415999999999</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="109">
@@ -5881,22 +5881,22 @@
         <v>677</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="J109" s="0">
-        <v>8731.0702999999994</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="110">
@@ -5916,19 +5916,19 @@
         <v>27</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="J110" s="0">
-        <v>509.65910000000002</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="111">
@@ -5948,19 +5948,19 @@
         <v>27</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="J111" s="0">
-        <v>473.81920000000002</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="112">
@@ -5980,19 +5980,19 @@
         <v>27</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="J112" s="0">
-        <v>386.12639999999999</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="113">
@@ -6012,19 +6012,19 @@
         <v>27</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="J113" s="0">
-        <v>381.40570000000002</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="114">
@@ -6044,19 +6044,19 @@
         <v>27</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>551</v>
+        <v>146</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="J114" s="0">
-        <v>371.59660000000002</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="115">
@@ -6076,19 +6076,19 @@
         <v>27</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="J115" s="0">
-        <v>364.02569999999997</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="116">
@@ -6099,28 +6099,28 @@
         <v>3</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>725</v>
+        <v>296</v>
       </c>
       <c r="J116" s="0">
-        <v>342.74220000000003</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="117">
@@ -6131,28 +6131,28 @@
         <v>3</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>677</v>
+        <v>18</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>553</v>
+        <v>130</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>726</v>
+        <v>297</v>
       </c>
       <c r="J117" s="0">
-        <v>331.7552</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="118">
@@ -6169,7 +6169,7 @@
         <v>18</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F118" s="0" t="s">
         <v>29</v>
@@ -6178,13 +6178,13 @@
         <v>43</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J118" s="0">
-        <v>8389.2909999999993</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="119">
@@ -6201,22 +6201,22 @@
         <v>18</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J119" s="0">
-        <v>8068.0429999999997</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="120">
@@ -6236,19 +6236,19 @@
         <v>27</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J120" s="0">
-        <v>528.16520000000003</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="121">
@@ -6268,19 +6268,19 @@
         <v>27</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J121" s="0">
-        <v>464.43889999999999</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="122">
@@ -6300,19 +6300,19 @@
         <v>27</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J122" s="0">
-        <v>449.87619999999998</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="123">
@@ -6332,19 +6332,19 @@
         <v>27</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J123" s="0">
-        <v>447.66699999999997</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="124">
@@ -6364,19 +6364,19 @@
         <v>27</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J124" s="0">
-        <v>391.69869999999997</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="125">
@@ -6396,19 +6396,19 @@
         <v>27</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J125" s="0">
-        <v>372.4153</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="126">
@@ -6422,25 +6422,25 @@
         <v>8</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J126" s="0">
-        <v>366.97289999999998</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="127">
@@ -6454,25 +6454,25 @@
         <v>8</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J127" s="0">
-        <v>329.11259999999999</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="128">
@@ -6489,7 +6489,7 @@
         <v>19</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F128" s="0" t="s">
         <v>29</v>
@@ -6498,13 +6498,13 @@
         <v>43</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J128" s="0">
-        <v>9741.5614999999998</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="129">
@@ -6521,7 +6521,7 @@
         <v>19</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F129" s="0" t="s">
         <v>30</v>
@@ -6530,13 +6530,13 @@
         <v>44</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J129" s="0">
-        <v>8198.8974999999991</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="130">
@@ -6553,7 +6553,7 @@
         <v>19</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130" s="0" t="s">
         <v>29</v>
@@ -6562,13 +6562,13 @@
         <v>43</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J130" s="0">
-        <v>1259.1116</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="131">
@@ -6585,22 +6585,22 @@
         <v>19</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J131" s="0">
-        <v>863.95190000000002</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="132">
@@ -6620,19 +6620,19 @@
         <v>27</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J132" s="0">
-        <v>539.45429999999999</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="133">
@@ -6652,19 +6652,19 @@
         <v>27</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J133" s="0">
-        <v>485.64830000000001</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="134">
@@ -6684,19 +6684,19 @@
         <v>27</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J134" s="0">
-        <v>457.39609999999999</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="135">
@@ -6716,19 +6716,19 @@
         <v>27</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J135" s="0">
-        <v>454.66460000000001</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="136">
@@ -6748,19 +6748,19 @@
         <v>27</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J136" s="0">
-        <v>368.51979999999998</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="137">
@@ -6780,19 +6780,19 @@
         <v>27</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J137" s="0">
-        <v>342.74220000000003</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="138">
@@ -6803,28 +6803,28 @@
         <v>3</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J138" s="0">
-        <v>302.46800000000002</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="139">
@@ -6835,28 +6835,28 @@
         <v>3</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J139" s="0">
-        <v>300.47250000000003</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="140">
@@ -6873,7 +6873,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F140" s="0" t="s">
         <v>29</v>
@@ -6882,13 +6882,13 @@
         <v>43</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J140" s="0">
-        <v>10892.9414</v>
+        <v>829.46619999999996</v>
       </c>
     </row>
     <row r="141">
@@ -6905,7 +6905,7 @@
         <v>20</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>30</v>
@@ -6914,13 +6914,13 @@
         <v>44</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J141" s="0">
-        <v>5918.6806999999999</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="142">
@@ -6937,7 +6937,7 @@
         <v>20</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F142" s="0" t="s">
         <v>29</v>
@@ -6946,13 +6946,13 @@
         <v>43</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J142" s="0">
-        <v>829.46619999999996</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="143">
@@ -6969,22 +6969,22 @@
         <v>20</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J143" s="0">
-        <v>726.14110000000005</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="144">
@@ -7004,19 +7004,19 @@
         <v>27</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J144" s="0">
-        <v>498.3132</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="145">
@@ -7036,19 +7036,19 @@
         <v>27</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J145" s="0">
-        <v>487.10520000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="146">
@@ -7068,19 +7068,19 @@
         <v>27</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J146" s="0">
-        <v>485.66770000000002</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="147">
@@ -7100,19 +7100,19 @@
         <v>27</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J147" s="0">
-        <v>478.11529999999999</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="148">
@@ -7132,19 +7132,19 @@
         <v>27</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J148" s="0">
-        <v>375.48970000000003</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="149">
@@ -7164,19 +7164,19 @@
         <v>27</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J149" s="0">
-        <v>359.0838</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="150">
@@ -7190,25 +7190,25 @@
         <v>9</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J150" s="0">
-        <v>338.9837</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="151">
@@ -7222,25 +7222,25 @@
         <v>9</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J151" s="0">
-        <v>293.55579999999998</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="152">
@@ -7257,7 +7257,7 @@
         <v>21</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F152" s="0" t="s">
         <v>29</v>
@@ -7266,13 +7266,13 @@
         <v>43</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J152" s="0">
-        <v>9826.1103999999996</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="153">
@@ -7289,22 +7289,22 @@
         <v>21</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J153" s="0">
-        <v>7957.9004000000004</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="154">
@@ -7321,22 +7321,22 @@
         <v>21</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J154" s="0">
-        <v>1958.7829999999999</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="155">
@@ -7356,19 +7356,19 @@
         <v>27</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J155" s="0">
-        <v>574.80640000000005</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="156">
@@ -7388,19 +7388,19 @@
         <v>27</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J156" s="0">
-        <v>532.89999999999998</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="157">
@@ -7420,19 +7420,19 @@
         <v>27</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J157" s="0">
-        <v>470.99040000000002</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="158">
@@ -7452,19 +7452,19 @@
         <v>27</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J158" s="0">
-        <v>428.05349999999999</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="159">
@@ -7484,19 +7484,19 @@
         <v>27</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J159" s="0">
-        <v>370.83409999999998</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="160">
@@ -7516,19 +7516,19 @@
         <v>27</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J160" s="0">
-        <v>361.65289999999999</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="161">
@@ -7536,31 +7536,31 @@
         <v>1</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J161" s="0">
-        <v>328.18830000000003</v>
+        <v>9104.8721000000005</v>
       </c>
     </row>
     <row r="162">
@@ -7568,31 +7568,31 @@
         <v>1</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J162" s="0">
-        <v>313.28399999999999</v>
+        <v>1438.8326</v>
       </c>
     </row>
     <row r="163">
@@ -7609,22 +7609,22 @@
         <v>11</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J163" s="0">
-        <v>9104.8721000000005</v>
+        <v>1210.5242000000001</v>
       </c>
     </row>
     <row r="164">
@@ -7641,7 +7641,7 @@
         <v>11</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F164" s="0" t="s">
         <v>29</v>
@@ -7650,13 +7650,13 @@
         <v>43</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J164" s="0">
-        <v>1438.8326</v>
+        <v>542.07240000000002</v>
       </c>
     </row>
     <row r="165">
@@ -7673,22 +7673,22 @@
         <v>11</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J165" s="0">
-        <v>1210.5242000000001</v>
+        <v>528.39120000000003</v>
       </c>
     </row>
     <row r="166">
@@ -7708,19 +7708,19 @@
         <v>27</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J166" s="0">
-        <v>542.07240000000002</v>
+        <v>519.83349999999996</v>
       </c>
     </row>
     <row r="167">
@@ -7740,19 +7740,19 @@
         <v>27</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J167" s="0">
-        <v>528.39120000000003</v>
+        <v>465.38400000000001</v>
       </c>
     </row>
     <row r="168">
@@ -7772,19 +7772,19 @@
         <v>27</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J168" s="0">
-        <v>519.83349999999996</v>
+        <v>387.42579999999998</v>
       </c>
     </row>
     <row r="169">
@@ -7804,19 +7804,19 @@
         <v>27</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J169" s="0">
-        <v>465.38400000000001</v>
+        <v>376.01639999999998</v>
       </c>
     </row>
     <row r="170">
@@ -7836,19 +7836,19 @@
         <v>27</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J170" s="0">
-        <v>387.42579999999998</v>
+        <v>367.9187</v>
       </c>
     </row>
     <row r="171">
@@ -7868,19 +7868,19 @@
         <v>27</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J171" s="0">
-        <v>376.01639999999998</v>
+        <v>345.6712</v>
       </c>
     </row>
     <row r="172">
@@ -7894,25 +7894,25 @@
         <v>6</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J172" s="0">
-        <v>367.9187</v>
+        <v>11026.299800000001</v>
       </c>
     </row>
     <row r="173">
@@ -7926,25 +7926,25 @@
         <v>6</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J173" s="0">
-        <v>345.6712</v>
+        <v>8759.9452999999994</v>
       </c>
     </row>
     <row r="174">
@@ -7961,7 +7961,7 @@
         <v>12</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>29</v>
@@ -7970,13 +7970,13 @@
         <v>43</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J174" s="0">
-        <v>11026.299800000001</v>
+        <v>1159.0046</v>
       </c>
     </row>
     <row r="175">
@@ -7993,7 +7993,7 @@
         <v>12</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>30</v>
@@ -8002,13 +8002,13 @@
         <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J175" s="0">
-        <v>8759.9452999999994</v>
+        <v>1153.3887</v>
       </c>
     </row>
     <row r="176">
@@ -8025,7 +8025,7 @@
         <v>12</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F176" s="0" t="s">
         <v>29</v>
@@ -8034,13 +8034,13 @@
         <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J176" s="0">
-        <v>1159.0046</v>
+        <v>531.56039999999996</v>
       </c>
     </row>
     <row r="177">
@@ -8057,22 +8057,22 @@
         <v>12</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J177" s="0">
-        <v>1153.3887</v>
+        <v>513.93790000000001</v>
       </c>
     </row>
     <row r="178">
@@ -8092,19 +8092,19 @@
         <v>27</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J178" s="0">
-        <v>531.56039999999996</v>
+        <v>499.63580000000002</v>
       </c>
     </row>
     <row r="179">
@@ -8124,19 +8124,19 @@
         <v>27</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J179" s="0">
-        <v>513.93790000000001</v>
+        <v>475.38760000000002</v>
       </c>
     </row>
     <row r="180">
@@ -8156,19 +8156,19 @@
         <v>27</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J180" s="0">
-        <v>499.63580000000002</v>
+        <v>357.59019999999998</v>
       </c>
     </row>
     <row r="181">
@@ -8188,19 +8188,19 @@
         <v>27</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J181" s="0">
-        <v>475.38760000000002</v>
+        <v>346.22629999999998</v>
       </c>
     </row>
     <row r="182">
@@ -8220,19 +8220,19 @@
         <v>27</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J182" s="0">
-        <v>357.59019999999998</v>
+        <v>331.46199999999999</v>
       </c>
     </row>
     <row r="183">
@@ -8252,19 +8252,19 @@
         <v>27</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J183" s="0">
-        <v>346.22629999999998</v>
+        <v>308.1046</v>
       </c>
     </row>
     <row r="184">
@@ -8278,25 +8278,25 @@
         <v>6</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="J184" s="0">
-        <v>331.46199999999999</v>
+        <v>901.9991</v>
       </c>
     </row>
     <row r="185">
@@ -8310,25 +8310,25 @@
         <v>6</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J185" s="0">
-        <v>308.1046</v>
+        <v>893.56960000000004</v>
       </c>
     </row>
     <row r="186">
@@ -8345,7 +8345,7 @@
         <v>13</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>29</v>
@@ -8354,13 +8354,13 @@
         <v>43</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J186" s="0">
-        <v>901.9991</v>
+        <v>549.74869999999999</v>
       </c>
     </row>
     <row r="187">
@@ -8377,22 +8377,22 @@
         <v>13</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J187" s="0">
-        <v>893.56960000000004</v>
+        <v>530.14729999999997</v>
       </c>
     </row>
     <row r="188">
@@ -8412,19 +8412,19 @@
         <v>27</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J188" s="0">
-        <v>549.74869999999999</v>
+        <v>489.4966</v>
       </c>
     </row>
     <row r="189">
@@ -8444,19 +8444,19 @@
         <v>27</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J189" s="0">
-        <v>530.14729999999997</v>
+        <v>482.49549999999999</v>
       </c>
     </row>
     <row r="190">
@@ -8476,19 +8476,19 @@
         <v>27</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J190" s="0">
-        <v>489.4966</v>
+        <v>378.9196</v>
       </c>
     </row>
     <row r="191">
@@ -8508,19 +8508,19 @@
         <v>27</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J191" s="0">
-        <v>482.49549999999999</v>
+        <v>366.15300000000002</v>
       </c>
     </row>
     <row r="192">
@@ -8540,19 +8540,19 @@
         <v>27</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J192" s="0">
-        <v>378.9196</v>
+        <v>340.57749999999999</v>
       </c>
     </row>
     <row r="193">
@@ -8566,25 +8566,25 @@
         <v>6</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J193" s="0">
-        <v>366.15300000000002</v>
+        <v>4307.7025999999996</v>
       </c>
     </row>
     <row r="194">
@@ -8598,25 +8598,25 @@
         <v>6</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J194" s="0">
-        <v>340.57749999999999</v>
+        <v>1837.0477000000001</v>
       </c>
     </row>
     <row r="195">
@@ -8633,7 +8633,7 @@
         <v>22</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>29</v>
@@ -8642,13 +8642,13 @@
         <v>43</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J195" s="0">
-        <v>4307.7025999999996</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="196">
@@ -8665,7 +8665,7 @@
         <v>22</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>30</v>
@@ -8674,13 +8674,13 @@
         <v>44</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J196" s="0">
-        <v>1837.0477000000001</v>
+        <v>552.42719999999997</v>
       </c>
     </row>
     <row r="197">
@@ -8697,7 +8697,7 @@
         <v>22</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>29</v>
@@ -8706,13 +8706,13 @@
         <v>43</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J197" s="0">
-        <v>616.08360000000005</v>
+        <v>399.44740000000002</v>
       </c>
     </row>
     <row r="198">
@@ -8729,22 +8729,22 @@
         <v>22</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J198" s="0">
-        <v>552.42719999999997</v>
+        <v>377.98289999999997</v>
       </c>
     </row>
     <row r="199">
@@ -8764,19 +8764,19 @@
         <v>27</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J199" s="0">
-        <v>399.44740000000002</v>
+        <v>376.71690000000001</v>
       </c>
     </row>
     <row r="200">
@@ -8796,19 +8796,19 @@
         <v>27</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J200" s="0">
-        <v>377.98289999999997</v>
+        <v>375.52019999999999</v>
       </c>
     </row>
     <row r="201">
@@ -8828,19 +8828,19 @@
         <v>27</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J201" s="0">
-        <v>376.71690000000001</v>
+        <v>370.8648</v>
       </c>
     </row>
     <row r="202">
@@ -8860,19 +8860,19 @@
         <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J202" s="0">
-        <v>375.52019999999999</v>
+        <v>342.89479999999998</v>
       </c>
     </row>
     <row r="203">
@@ -8892,19 +8892,19 @@
         <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J203" s="0">
-        <v>370.8648</v>
+        <v>307.26029999999997</v>
       </c>
     </row>
     <row r="204">
@@ -8924,19 +8924,19 @@
         <v>27</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J204" s="0">
-        <v>342.89479999999998</v>
+        <v>261.58179999999999</v>
       </c>
     </row>
     <row r="205">
@@ -8947,28 +8947,28 @@
         <v>4</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J205" s="0">
-        <v>307.26029999999997</v>
+        <v>10466.208000000001</v>
       </c>
     </row>
     <row r="206">
@@ -8979,28 +8979,28 @@
         <v>4</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J206" s="0">
-        <v>261.58179999999999</v>
+        <v>7328.0029000000004</v>
       </c>
     </row>
     <row r="207">
@@ -9017,7 +9017,7 @@
         <v>14</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>29</v>
@@ -9026,13 +9026,13 @@
         <v>43</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J207" s="0">
-        <v>10466.208000000001</v>
+        <v>1015.5606</v>
       </c>
     </row>
     <row r="208">
@@ -9049,7 +9049,7 @@
         <v>14</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>30</v>
@@ -9058,13 +9058,13 @@
         <v>44</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J208" s="0">
-        <v>7328.0029000000004</v>
+        <v>908.67830000000004</v>
       </c>
     </row>
     <row r="209">
@@ -9084,19 +9084,19 @@
         <v>26</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J209" s="0">
-        <v>1015.5606</v>
+        <v>520.97770000000003</v>
       </c>
     </row>
     <row r="210">
@@ -9116,19 +9116,19 @@
         <v>26</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J210" s="0">
-        <v>908.67830000000004</v>
+        <v>488.97149999999999</v>
       </c>
     </row>
     <row r="211">
@@ -9148,19 +9148,19 @@
         <v>26</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J211" s="0">
-        <v>520.97770000000003</v>
+        <v>484.75029999999998</v>
       </c>
     </row>
     <row r="212">
@@ -9180,19 +9180,19 @@
         <v>26</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J212" s="0">
-        <v>488.97149999999999</v>
+        <v>438.36930000000001</v>
       </c>
     </row>
     <row r="213">
@@ -9212,19 +9212,19 @@
         <v>26</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J213" s="0">
-        <v>484.75029999999998</v>
+        <v>369.10219999999998</v>
       </c>
     </row>
     <row r="214">
@@ -9244,19 +9244,19 @@
         <v>26</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J214" s="0">
-        <v>438.36930000000001</v>
+        <v>342.30680000000001</v>
       </c>
     </row>
     <row r="215">
@@ -9276,19 +9276,19 @@
         <v>26</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J215" s="0">
-        <v>369.10219999999998</v>
+        <v>280.75409999999999</v>
       </c>
     </row>
     <row r="216">
@@ -9308,19 +9308,19 @@
         <v>26</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J216" s="0">
-        <v>342.30680000000001</v>
+        <v>270.84679999999997</v>
       </c>
     </row>
     <row r="217">
@@ -9334,25 +9334,25 @@
         <v>7</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J217" s="0">
-        <v>280.75409999999999</v>
+        <v>8934.2567999999992</v>
       </c>
     </row>
     <row r="218">
@@ -9366,25 +9366,25 @@
         <v>7</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J218" s="0">
-        <v>270.84679999999997</v>
+        <v>7192.2339000000002</v>
       </c>
     </row>
     <row r="219">
@@ -9401,7 +9401,7 @@
         <v>15</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F219" s="0" t="s">
         <v>29</v>
@@ -9410,13 +9410,13 @@
         <v>43</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J219" s="0">
-        <v>8934.2567999999992</v>
+        <v>489.01900000000001</v>
       </c>
     </row>
     <row r="220">
@@ -9433,22 +9433,22 @@
         <v>15</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J220" s="0">
-        <v>7192.2339000000002</v>
+        <v>486.78719999999999</v>
       </c>
     </row>
     <row r="221">
@@ -9468,19 +9468,19 @@
         <v>27</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J221" s="0">
-        <v>489.01900000000001</v>
+        <v>478.59969999999999</v>
       </c>
     </row>
     <row r="222">
@@ -9500,19 +9500,19 @@
         <v>27</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J222" s="0">
-        <v>486.78719999999999</v>
+        <v>456.38220000000001</v>
       </c>
     </row>
     <row r="223">
@@ -9532,19 +9532,19 @@
         <v>27</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J223" s="0">
-        <v>478.59969999999999</v>
+        <v>361.197</v>
       </c>
     </row>
     <row r="224">
@@ -9564,19 +9564,19 @@
         <v>27</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J224" s="0">
-        <v>456.38220000000001</v>
+        <v>350.10750000000002</v>
       </c>
     </row>
     <row r="225">
@@ -9596,19 +9596,19 @@
         <v>27</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J225" s="0">
-        <v>361.197</v>
+        <v>332.8802</v>
       </c>
     </row>
     <row r="226">
@@ -9622,25 +9622,25 @@
         <v>7</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J226" s="0">
-        <v>350.10750000000002</v>
+        <v>9850.5967000000001</v>
       </c>
     </row>
     <row r="227">
@@ -9654,25 +9654,25 @@
         <v>7</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J227" s="0">
-        <v>332.8802</v>
+        <v>8299.1229999999996</v>
       </c>
     </row>
     <row r="228">
@@ -9689,7 +9689,7 @@
         <v>16</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>29</v>
@@ -9698,13 +9698,13 @@
         <v>43</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J228" s="0">
-        <v>9850.5967000000001</v>
+        <v>1061.2550000000001</v>
       </c>
     </row>
     <row r="229">
@@ -9721,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F229" s="0" t="s">
         <v>30</v>
@@ -9730,13 +9730,13 @@
         <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J229" s="0">
-        <v>8299.1229999999996</v>
+        <v>863.95190000000002</v>
       </c>
     </row>
     <row r="230">
@@ -9753,7 +9753,7 @@
         <v>16</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>29</v>
@@ -9762,13 +9762,13 @@
         <v>43</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J230" s="0">
-        <v>1061.2550000000001</v>
+        <v>537.24440000000004</v>
       </c>
     </row>
     <row r="231">
@@ -9785,22 +9785,22 @@
         <v>16</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J231" s="0">
-        <v>863.95190000000002</v>
+        <v>512.39139999999998</v>
       </c>
     </row>
     <row r="232">
@@ -9820,19 +9820,19 @@
         <v>27</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J232" s="0">
-        <v>537.24440000000004</v>
+        <v>461.678</v>
       </c>
     </row>
     <row r="233">
@@ -9852,19 +9852,19 @@
         <v>27</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J233" s="0">
-        <v>512.39139999999998</v>
+        <v>446.13510000000002</v>
       </c>
     </row>
     <row r="234">
@@ -9884,19 +9884,19 @@
         <v>27</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J234" s="0">
-        <v>461.678</v>
+        <v>416.1148</v>
       </c>
     </row>
     <row r="235">
@@ -9916,19 +9916,19 @@
         <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J235" s="0">
-        <v>446.13510000000002</v>
+        <v>385.80329999999998</v>
       </c>
     </row>
     <row r="236">
@@ -9948,19 +9948,19 @@
         <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J236" s="0">
-        <v>416.1148</v>
+        <v>376.43869999999998</v>
       </c>
     </row>
     <row r="237">
@@ -9980,19 +9980,19 @@
         <v>27</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J237" s="0">
-        <v>385.80329999999998</v>
+        <v>340.64490000000001</v>
       </c>
     </row>
     <row r="238">
@@ -10006,25 +10006,25 @@
         <v>7</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J238" s="0">
-        <v>376.43869999999998</v>
+        <v>9114.7715000000008</v>
       </c>
     </row>
     <row r="239">
@@ -10038,25 +10038,25 @@
         <v>7</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J239" s="0">
-        <v>340.64490000000001</v>
+        <v>7656.0316999999996</v>
       </c>
     </row>
     <row r="240">
@@ -10073,7 +10073,7 @@
         <v>17</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>29</v>
@@ -10082,13 +10082,13 @@
         <v>43</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J240" s="0">
-        <v>9114.7715000000008</v>
+        <v>542.5788</v>
       </c>
     </row>
     <row r="241">
@@ -10105,7 +10105,7 @@
         <v>17</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>30</v>
@@ -10114,13 +10114,13 @@
         <v>44</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J241" s="0">
-        <v>7656.0316999999996</v>
+        <v>534.76580000000001</v>
       </c>
     </row>
     <row r="242">
@@ -10140,19 +10140,19 @@
         <v>26</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J242" s="0">
-        <v>542.5788</v>
+        <v>484.83710000000002</v>
       </c>
     </row>
     <row r="243">
@@ -10172,19 +10172,19 @@
         <v>26</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J243" s="0">
-        <v>534.76580000000001</v>
+        <v>468.87529999999998</v>
       </c>
     </row>
     <row r="244">
@@ -10204,19 +10204,19 @@
         <v>26</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J244" s="0">
-        <v>484.83710000000002</v>
+        <v>398.83769999999998</v>
       </c>
     </row>
     <row r="245">
@@ -10236,19 +10236,19 @@
         <v>26</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J245" s="0">
-        <v>468.87529999999998</v>
+        <v>337.36939999999999</v>
       </c>
     </row>
     <row r="246">
@@ -10268,19 +10268,19 @@
         <v>26</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J246" s="0">
-        <v>398.83769999999998</v>
+        <v>311.84429999999998</v>
       </c>
     </row>
     <row r="247">
@@ -10300,19 +10300,19 @@
         <v>26</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J247" s="0">
-        <v>337.36939999999999</v>
+        <v>245.285</v>
       </c>
     </row>
     <row r="248">
@@ -10326,25 +10326,25 @@
         <v>7</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J248" s="0">
-        <v>311.84429999999998</v>
+        <v>2887.6174000000001</v>
       </c>
     </row>
     <row r="249">
@@ -10358,25 +10358,25 @@
         <v>7</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J249" s="0">
-        <v>245.285</v>
+        <v>2872.1073999999999</v>
       </c>
     </row>
     <row r="250">
@@ -10393,7 +10393,7 @@
         <v>23</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F250" s="0" t="s">
         <v>29</v>
@@ -10402,13 +10402,13 @@
         <v>43</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J250" s="0">
-        <v>2887.6174000000001</v>
+        <v>975.3777</v>
       </c>
     </row>
     <row r="251">
@@ -10425,7 +10425,7 @@
         <v>23</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F251" s="0" t="s">
         <v>30</v>
@@ -10434,13 +10434,13 @@
         <v>44</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J251" s="0">
-        <v>2872.1073999999999</v>
+        <v>616.08360000000005</v>
       </c>
     </row>
     <row r="252">
@@ -10457,7 +10457,7 @@
         <v>23</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F252" s="0" t="s">
         <v>29</v>
@@ -10466,13 +10466,13 @@
         <v>43</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J252" s="0">
-        <v>975.3777</v>
+        <v>465.53719999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10489,22 +10489,22 @@
         <v>23</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J253" s="0">
-        <v>616.08360000000005</v>
+        <v>436.18400000000003</v>
       </c>
     </row>
     <row r="254">
@@ -10524,19 +10524,19 @@
         <v>27</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J254" s="0">
-        <v>465.53719999999999</v>
+        <v>415.78980000000001</v>
       </c>
     </row>
     <row r="255">
@@ -10556,19 +10556,19 @@
         <v>27</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J255" s="0">
-        <v>436.18400000000003</v>
+        <v>391.16430000000003</v>
       </c>
     </row>
     <row r="256">
@@ -10588,19 +10588,19 @@
         <v>27</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J256" s="0">
-        <v>415.78980000000001</v>
+        <v>362.91770000000002</v>
       </c>
     </row>
     <row r="257">
@@ -10620,19 +10620,19 @@
         <v>27</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J257" s="0">
-        <v>391.16430000000003</v>
+        <v>315.58260000000001</v>
       </c>
     </row>
     <row r="258">
@@ -10652,19 +10652,19 @@
         <v>27</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J258" s="0">
-        <v>362.91770000000002</v>
+        <v>315.33229999999998</v>
       </c>
     </row>
     <row r="259">
@@ -10684,19 +10684,19 @@
         <v>27</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J259" s="0">
-        <v>315.58260000000001</v>
+        <v>254.02879999999999</v>
       </c>
     </row>
     <row r="260">
@@ -10707,28 +10707,28 @@
         <v>4</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>206</v>
+        <v>507</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>450</v>
+        <v>727</v>
       </c>
       <c r="J260" s="0">
-        <v>315.33229999999998</v>
+        <v>10897.75</v>
       </c>
     </row>
     <row r="261">
@@ -10739,28 +10739,28 @@
         <v>4</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>7</v>
+        <v>501</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>207</v>
+        <v>508</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>451</v>
+        <v>728</v>
       </c>
       <c r="J261" s="0">
-        <v>254.02879999999999</v>
+        <v>5963.8306000000002</v>
       </c>
     </row>
     <row r="262">
@@ -10777,7 +10777,7 @@
         <v>674</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>29</v>
@@ -10786,13 +10786,13 @@
         <v>43</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J262" s="0">
-        <v>10897.75</v>
+        <v>1364.115</v>
       </c>
     </row>
     <row r="263">
@@ -10809,7 +10809,7 @@
         <v>674</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F263" s="0" t="s">
         <v>30</v>
@@ -10818,13 +10818,13 @@
         <v>44</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J263" s="0">
-        <v>5963.8306000000002</v>
+        <v>1002.6719000000001</v>
       </c>
     </row>
     <row r="264">
@@ -10841,7 +10841,7 @@
         <v>674</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F264" s="0" t="s">
         <v>29</v>
@@ -10850,13 +10850,13 @@
         <v>43</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="J264" s="0">
-        <v>1364.115</v>
+        <v>557.97879999999998</v>
       </c>
     </row>
     <row r="265">
@@ -10873,22 +10873,22 @@
         <v>674</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J265" s="0">
-        <v>1002.6719000000001</v>
+        <v>511.4341</v>
       </c>
     </row>
     <row r="266">
@@ -10908,19 +10908,19 @@
         <v>27</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="J266" s="0">
-        <v>557.97879999999998</v>
+        <v>485.53699999999998</v>
       </c>
     </row>
     <row r="267">
@@ -10940,19 +10940,19 @@
         <v>27</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="J267" s="0">
-        <v>511.4341</v>
+        <v>456.29579999999999</v>
       </c>
     </row>
     <row r="268">
@@ -10972,19 +10972,19 @@
         <v>27</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="J268" s="0">
-        <v>485.53699999999998</v>
+        <v>403.62130000000002</v>
       </c>
     </row>
     <row r="269">
@@ -11004,19 +11004,19 @@
         <v>27</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="J269" s="0">
-        <v>456.29579999999999</v>
+        <v>384.92849999999999</v>
       </c>
     </row>
     <row r="270">
@@ -11036,19 +11036,19 @@
         <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="J270" s="0">
-        <v>403.62130000000002</v>
+        <v>345.9332</v>
       </c>
     </row>
     <row r="271">
@@ -11068,19 +11068,19 @@
         <v>27</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="J271" s="0">
-        <v>384.92849999999999</v>
+        <v>329.33870000000002</v>
       </c>
     </row>
     <row r="272">
@@ -11094,25 +11094,25 @@
         <v>501</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G272" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="J272" s="0">
-        <v>345.9332</v>
+        <v>9494.3554999999997</v>
       </c>
     </row>
     <row r="273">
@@ -11126,25 +11126,25 @@
         <v>501</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="J273" s="0">
-        <v>329.33870000000002</v>
+        <v>6959.3242</v>
       </c>
     </row>
     <row r="274">
@@ -11161,7 +11161,7 @@
         <v>675</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>29</v>
@@ -11170,13 +11170,13 @@
         <v>43</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J274" s="0">
-        <v>9494.3554999999997</v>
+        <v>528.32619999999997</v>
       </c>
     </row>
     <row r="275">
@@ -11193,22 +11193,22 @@
         <v>675</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="J275" s="0">
-        <v>6959.3242</v>
+        <v>502.16129999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11228,19 +11228,19 @@
         <v>27</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="J276" s="0">
-        <v>528.32619999999997</v>
+        <v>468.14839999999998</v>
       </c>
     </row>
     <row r="277">
@@ -11260,19 +11260,19 @@
         <v>27</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J277" s="0">
-        <v>502.16129999999998</v>
+        <v>413.35890000000001</v>
       </c>
     </row>
     <row r="278">
@@ -11292,19 +11292,19 @@
         <v>27</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="J278" s="0">
-        <v>468.14839999999998</v>
+        <v>410.47199999999998</v>
       </c>
     </row>
     <row r="279">
@@ -11324,19 +11324,19 @@
         <v>27</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="J279" s="0">
-        <v>413.35890000000001</v>
+        <v>371.8809</v>
       </c>
     </row>
     <row r="280">
@@ -11356,19 +11356,19 @@
         <v>27</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="J280" s="0">
-        <v>410.47199999999998</v>
+        <v>347.0478</v>
       </c>
     </row>
     <row r="281">
@@ -11388,19 +11388,19 @@
         <v>27</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="J281" s="0">
-        <v>371.8809</v>
+        <v>302.97559999999999</v>
       </c>
     </row>
     <row r="282">
@@ -11414,25 +11414,25 @@
         <v>501</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="J282" s="0">
-        <v>347.0478</v>
+        <v>8923.2001999999993</v>
       </c>
     </row>
     <row r="283">
@@ -11446,25 +11446,25 @@
         <v>501</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J283" s="0">
-        <v>302.97559999999999</v>
+        <v>7434.9364999999998</v>
       </c>
     </row>
     <row r="284">
@@ -11481,7 +11481,7 @@
         <v>676</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F284" s="0" t="s">
         <v>29</v>
@@ -11490,13 +11490,13 @@
         <v>43</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="J284" s="0">
-        <v>8923.2001999999993</v>
+        <v>1198.5989</v>
       </c>
     </row>
     <row r="285">
@@ -11513,7 +11513,7 @@
         <v>676</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F285" s="0" t="s">
         <v>30</v>
@@ -11522,13 +11522,13 @@
         <v>44</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J285" s="0">
-        <v>7434.9364999999998</v>
+        <v>1016.6576</v>
       </c>
     </row>
     <row r="286">
@@ -11542,10 +11542,10 @@
         <v>501</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F286" s="0" t="s">
         <v>29</v>
@@ -11554,13 +11554,13 @@
         <v>43</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="J286" s="0">
-        <v>1198.5989</v>
+        <v>10363.415999999999</v>
       </c>
     </row>
     <row r="287">
@@ -11574,10 +11574,10 @@
         <v>501</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F287" s="0" t="s">
         <v>30</v>
@@ -11586,13 +11586,13 @@
         <v>44</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="J287" s="0">
-        <v>1016.6576</v>
+        <v>8731.0702999999994</v>
       </c>
     </row>
     <row r="288">
@@ -11609,7 +11609,7 @@
         <v>677</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F288" s="0" t="s">
         <v>29</v>
@@ -11618,13 +11618,13 @@
         <v>43</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J288" s="0">
-        <v>10363.415999999999</v>
+        <v>509.65910000000002</v>
       </c>
     </row>
     <row r="289">
@@ -11641,22 +11641,22 @@
         <v>677</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>544</v>
+        <v>64</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="J289" s="0">
-        <v>8731.0702999999994</v>
+        <v>497.6062</v>
       </c>
     </row>
     <row r="290">
@@ -11676,19 +11676,19 @@
         <v>27</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="J290" s="0">
-        <v>509.65910000000002</v>
+        <v>473.81920000000002</v>
       </c>
     </row>
     <row r="291">
@@ -11708,19 +11708,19 @@
         <v>27</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>64</v>
+        <v>549</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="J291" s="0">
-        <v>497.6062</v>
+        <v>386.12639999999999</v>
       </c>
     </row>
     <row r="292">
@@ -11740,19 +11740,19 @@
         <v>27</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="J292" s="0">
-        <v>473.81920000000002</v>
+        <v>381.40570000000002</v>
       </c>
     </row>
     <row r="293">
@@ -11772,19 +11772,19 @@
         <v>27</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J293" s="0">
-        <v>386.12639999999999</v>
+        <v>371.59660000000002</v>
       </c>
     </row>
     <row r="294">
@@ -11804,19 +11804,19 @@
         <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="J294" s="0">
-        <v>381.40570000000002</v>
+        <v>364.02569999999997</v>
       </c>
     </row>
     <row r="295">
@@ -11836,19 +11836,19 @@
         <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="J295" s="0">
-        <v>371.59660000000002</v>
+        <v>331.7552</v>
       </c>
     </row>
     <row r="296">
@@ -11862,25 +11862,25 @@
         <v>501</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G296" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="J296" s="0">
-        <v>364.02569999999997</v>
+        <v>1621.762</v>
       </c>
     </row>
     <row r="297">
@@ -11894,25 +11894,25 @@
         <v>501</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="J297" s="0">
-        <v>331.7552</v>
+        <v>1023.5883</v>
       </c>
     </row>
     <row r="298">
@@ -11929,7 +11929,7 @@
         <v>678</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F298" s="0" t="s">
         <v>29</v>
@@ -11938,13 +11938,13 @@
         <v>43</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="J298" s="0">
-        <v>1621.762</v>
+        <v>634.67409999999995</v>
       </c>
     </row>
     <row r="299">
@@ -11961,7 +11961,7 @@
         <v>678</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F299" s="0" t="s">
         <v>30</v>
@@ -11970,13 +11970,13 @@
         <v>44</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J299" s="0">
-        <v>1023.5883</v>
+        <v>589.45230000000004</v>
       </c>
     </row>
     <row r="300">
@@ -11993,7 +11993,7 @@
         <v>678</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F300" s="0" t="s">
         <v>29</v>
@@ -12002,13 +12002,13 @@
         <v>43</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="J300" s="0">
-        <v>634.67409999999995</v>
+        <v>441.32260000000002</v>
       </c>
     </row>
     <row r="301">
@@ -12025,22 +12025,22 @@
         <v>678</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="J301" s="0">
-        <v>589.45230000000004</v>
+        <v>406.00639999999999</v>
       </c>
     </row>
     <row r="302">
@@ -12060,19 +12060,19 @@
         <v>27</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="J302" s="0">
-        <v>441.32260000000002</v>
+        <v>404.98939999999999</v>
       </c>
     </row>
     <row r="303">
@@ -12092,19 +12092,19 @@
         <v>27</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="J303" s="0">
-        <v>406.00639999999999</v>
+        <v>356.87450000000001</v>
       </c>
     </row>
     <row r="304">
@@ -12124,19 +12124,19 @@
         <v>27</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J304" s="0">
-        <v>404.98939999999999</v>
+        <v>326.86750000000001</v>
       </c>
     </row>
     <row r="305">
@@ -12156,19 +12156,19 @@
         <v>27</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="J305" s="0">
-        <v>356.87450000000001</v>
+        <v>313.15320000000003</v>
       </c>
     </row>
     <row r="306">
@@ -12188,19 +12188,19 @@
         <v>27</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="J306" s="0">
-        <v>326.86750000000001</v>
+        <v>302.25330000000002</v>
       </c>
     </row>
     <row r="307">
@@ -12220,19 +12220,19 @@
         <v>27</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="J307" s="0">
-        <v>313.15320000000003</v>
+        <v>241.7327</v>
       </c>
     </row>
     <row r="308">
@@ -12243,28 +12243,28 @@
         <v>4</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G308" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>564</v>
+        <v>129</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>777</v>
+        <v>452</v>
       </c>
       <c r="J308" s="0">
-        <v>302.25330000000002</v>
+        <v>8389.2909999999993</v>
       </c>
     </row>
     <row r="309">
@@ -12275,28 +12275,28 @@
         <v>4</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>501</v>
+        <v>8</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>678</v>
+        <v>18</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>565</v>
+        <v>130</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>778</v>
+        <v>453</v>
       </c>
       <c r="J309" s="0">
-        <v>241.7327</v>
+        <v>8068.0429999999997</v>
       </c>
     </row>
     <row r="310">
@@ -12313,7 +12313,7 @@
         <v>18</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F310" s="0" t="s">
         <v>29</v>
@@ -12322,13 +12322,13 @@
         <v>43</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J310" s="0">
-        <v>8389.2909999999993</v>
+        <v>1304.9119000000001</v>
       </c>
     </row>
     <row r="311">
@@ -12345,22 +12345,22 @@
         <v>18</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J311" s="0">
-        <v>8068.0429999999997</v>
+        <v>528.16520000000003</v>
       </c>
     </row>
     <row r="312">
@@ -12377,22 +12377,22 @@
         <v>18</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="J312" s="0">
-        <v>1304.9119000000001</v>
+        <v>464.43889999999999</v>
       </c>
     </row>
     <row r="313">
@@ -12412,19 +12412,19 @@
         <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J313" s="0">
-        <v>528.16520000000003</v>
+        <v>449.87619999999998</v>
       </c>
     </row>
     <row r="314">
@@ -12444,19 +12444,19 @@
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J314" s="0">
-        <v>464.43889999999999</v>
+        <v>447.66699999999997</v>
       </c>
     </row>
     <row r="315">
@@ -12476,19 +12476,19 @@
         <v>27</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J315" s="0">
-        <v>449.87619999999998</v>
+        <v>391.69869999999997</v>
       </c>
     </row>
     <row r="316">
@@ -12508,19 +12508,19 @@
         <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J316" s="0">
-        <v>447.66699999999997</v>
+        <v>372.4153</v>
       </c>
     </row>
     <row r="317">
@@ -12540,19 +12540,19 @@
         <v>27</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J317" s="0">
-        <v>391.69869999999997</v>
+        <v>366.97289999999998</v>
       </c>
     </row>
     <row r="318">
@@ -12572,19 +12572,19 @@
         <v>27</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J318" s="0">
-        <v>372.4153</v>
+        <v>329.11259999999999</v>
       </c>
     </row>
     <row r="319">
@@ -12598,25 +12598,25 @@
         <v>8</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J319" s="0">
-        <v>366.97289999999998</v>
+        <v>9741.5614999999998</v>
       </c>
     </row>
     <row r="320">
@@ -12630,25 +12630,25 @@
         <v>8</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J320" s="0">
-        <v>329.11259999999999</v>
+        <v>8198.8974999999991</v>
       </c>
     </row>
     <row r="321">
@@ -12665,7 +12665,7 @@
         <v>19</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F321" s="0" t="s">
         <v>29</v>
@@ -12674,13 +12674,13 @@
         <v>43</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J321" s="0">
-        <v>9741.5614999999998</v>
+        <v>1259.1116</v>
       </c>
     </row>
     <row r="322">
@@ -12697,7 +12697,7 @@
         <v>19</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F322" s="0" t="s">
         <v>30</v>
@@ -12706,13 +12706,13 @@
         <v>44</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J322" s="0">
-        <v>8198.8974999999991</v>
+        <v>964.0145</v>
       </c>
     </row>
     <row r="323">
@@ -12729,7 +12729,7 @@
         <v>19</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F323" s="0" t="s">
         <v>29</v>
@@ -12738,13 +12738,13 @@
         <v>43</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J323" s="0">
-        <v>1259.1116</v>
+        <v>539.45429999999999</v>
       </c>
     </row>
     <row r="324">
@@ -12761,22 +12761,22 @@
         <v>19</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J324" s="0">
-        <v>964.0145</v>
+        <v>485.64830000000001</v>
       </c>
     </row>
     <row r="325">
@@ -12796,19 +12796,19 @@
         <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J325" s="0">
-        <v>539.45429999999999</v>
+        <v>457.39609999999999</v>
       </c>
     </row>
     <row r="326">
@@ -12828,19 +12828,19 @@
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J326" s="0">
-        <v>485.64830000000001</v>
+        <v>454.66460000000001</v>
       </c>
     </row>
     <row r="327">
@@ -12860,19 +12860,19 @@
         <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J327" s="0">
-        <v>457.39609999999999</v>
+        <v>368.51979999999998</v>
       </c>
     </row>
     <row r="328">
@@ -12892,19 +12892,19 @@
         <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J328" s="0">
-        <v>454.66460000000001</v>
+        <v>342.74220000000003</v>
       </c>
     </row>
     <row r="329">
@@ -12924,19 +12924,19 @@
         <v>27</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J329" s="0">
-        <v>368.51979999999998</v>
+        <v>302.46800000000002</v>
       </c>
     </row>
     <row r="330">
@@ -12956,19 +12956,19 @@
         <v>27</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J330" s="0">
-        <v>342.74220000000003</v>
+        <v>300.47250000000003</v>
       </c>
     </row>
     <row r="331">
@@ -12979,28 +12979,28 @@
         <v>4</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J331" s="0">
-        <v>302.46800000000002</v>
+        <v>10892.9414</v>
       </c>
     </row>
     <row r="332">
@@ -13011,28 +13011,28 @@
         <v>4</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J332" s="0">
-        <v>300.47250000000003</v>
+        <v>5918.6806999999999</v>
       </c>
     </row>
     <row r="333">
@@ -13049,7 +13049,7 @@
         <v>20</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F333" s="0" t="s">
         <v>29</v>
@@ -13058,13 +13058,13 @@
         <v>43</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J333" s="0">
-        <v>10892.9414</v>
+        <v>726.14110000000005</v>
       </c>
     </row>
     <row r="334">
@@ -13081,22 +13081,22 @@
         <v>20</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G334" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J334" s="0">
-        <v>5918.6806999999999</v>
+        <v>498.3132</v>
       </c>
     </row>
     <row r="335">
@@ -13113,22 +13113,22 @@
         <v>20</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J335" s="0">
-        <v>726.14110000000005</v>
+        <v>487.10520000000002</v>
       </c>
     </row>
     <row r="336">
@@ -13148,19 +13148,19 @@
         <v>27</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J336" s="0">
-        <v>498.3132</v>
+        <v>485.66770000000002</v>
       </c>
     </row>
     <row r="337">
@@ -13180,19 +13180,19 @@
         <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J337" s="0">
-        <v>487.10520000000002</v>
+        <v>478.11529999999999</v>
       </c>
     </row>
     <row r="338">
@@ -13212,19 +13212,19 @@
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J338" s="0">
-        <v>485.66770000000002</v>
+        <v>375.48970000000003</v>
       </c>
     </row>
     <row r="339">
@@ -13244,19 +13244,19 @@
         <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J339" s="0">
-        <v>478.11529999999999</v>
+        <v>359.0838</v>
       </c>
     </row>
     <row r="340">
@@ -13276,19 +13276,19 @@
         <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J340" s="0">
-        <v>375.48970000000003</v>
+        <v>338.9837</v>
       </c>
     </row>
     <row r="341">
@@ -13308,19 +13308,19 @@
         <v>27</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J341" s="0">
-        <v>359.0838</v>
+        <v>293.55579999999998</v>
       </c>
     </row>
     <row r="342">
@@ -13334,25 +13334,25 @@
         <v>9</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J342" s="0">
-        <v>338.9837</v>
+        <v>9826.1103999999996</v>
       </c>
     </row>
     <row r="343">
@@ -13366,25 +13366,25 @@
         <v>9</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J343" s="0">
-        <v>293.55579999999998</v>
+        <v>7957.9004000000004</v>
       </c>
     </row>
     <row r="344">
@@ -13401,7 +13401,7 @@
         <v>21</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F344" s="0" t="s">
         <v>29</v>
@@ -13410,13 +13410,13 @@
         <v>43</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J344" s="0">
-        <v>9826.1103999999996</v>
+        <v>1958.7829999999999</v>
       </c>
     </row>
     <row r="345">
@@ -13433,22 +13433,22 @@
         <v>21</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J345" s="0">
-        <v>7957.9004000000004</v>
+        <v>574.80640000000005</v>
       </c>
     </row>
     <row r="346">
@@ -13465,22 +13465,22 @@
         <v>21</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="J346" s="0">
-        <v>1958.7829999999999</v>
+        <v>532.89999999999998</v>
       </c>
     </row>
     <row r="347">
@@ -13500,19 +13500,19 @@
         <v>27</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J347" s="0">
-        <v>574.80640000000005</v>
+        <v>470.99040000000002</v>
       </c>
     </row>
     <row r="348">
@@ -13532,19 +13532,19 @@
         <v>27</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J348" s="0">
-        <v>532.89999999999998</v>
+        <v>428.05349999999999</v>
       </c>
     </row>
     <row r="349">
@@ -13564,19 +13564,19 @@
         <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J349" s="0">
-        <v>470.99040000000002</v>
+        <v>370.83409999999998</v>
       </c>
     </row>
     <row r="350">
@@ -13596,19 +13596,19 @@
         <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J350" s="0">
-        <v>428.05349999999999</v>
+        <v>361.65289999999999</v>
       </c>
     </row>
     <row r="351">
@@ -13628,19 +13628,19 @@
         <v>27</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J351" s="0">
-        <v>370.83409999999998</v>
+        <v>328.18830000000003</v>
       </c>
     </row>
     <row r="352">
@@ -13660,19 +13660,19 @@
         <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J352" s="0">
-        <v>361.65289999999999</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="353">
@@ -13692,19 +13692,19 @@
         <v>27</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J353" s="0">
-        <v>328.18830000000003</v>
+        <v>313.28399999999999</v>
       </c>
     </row>
     <row r="354">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76163" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79332" uniqueCount="779">
   <si>
     <t>Year</t>
   </si>
